--- a/kalkulator-nk38/Kalkulator_NK38_v1_przyklad_WAW.xlsx
+++ b/kalkulator-nk38/Kalkulator_NK38_v1_przyklad_WAW.xlsx
@@ -18,40 +18,39 @@
     <definedName function="false" hidden="false" name="c_agregat" vbProcedure="false">Cennik!$C$18</definedName>
     <definedName function="false" hidden="false" name="c_barierka" vbProcedure="false">Cennik!$C$28</definedName>
     <definedName function="false" hidden="false" name="c_cena_D" vbProcedure="false">Cennik!$C$6</definedName>
-    <definedName function="false" hidden="false" name="c_dieta" vbProcedure="false">Cennik!$C$63</definedName>
+    <definedName function="false" hidden="false" name="c_dieta" vbProcedure="false">Cennik!$C$62</definedName>
     <definedName function="false" hidden="false" name="c_dl_500" vbProcedure="false">Cennik!$C$14</definedName>
     <definedName function="false" hidden="false" name="c_dl_wsp" vbProcedure="false">Cennik!$C$15</definedName>
-    <definedName function="false" hidden="false" name="c_dni_tydzien" vbProcedure="false">Cennik!$C$50</definedName>
+    <definedName function="false" hidden="false" name="c_dni_tydzien" vbProcedure="false">Cennik!$C$49</definedName>
     <definedName function="false" hidden="false" name="c_doplata_NK37" vbProcedure="false">Cennik!$C$7</definedName>
     <definedName function="false" hidden="false" name="c_dzwig" vbProcedure="false">Cennik!$C$46</definedName>
-    <definedName function="false" hidden="false" name="c_dzwig_alt" vbProcedure="false">Cennik!$C$47</definedName>
-    <definedName function="false" hidden="false" name="c_dzwig_D" vbProcedure="false">Cennik!$C$48</definedName>
-    <definedName function="false" hidden="false" name="c_dzwig_wspS" vbProcedure="false">Cennik!$C$49</definedName>
-    <definedName function="false" hidden="false" name="c_gdw" vbProcedure="false">Cennik!$C$67</definedName>
-    <definedName function="false" hidden="false" name="c_hotel" vbProcedure="false">Cennik!$C$64</definedName>
+    <definedName function="false" hidden="false" name="c_dzwig_D" vbProcedure="false">Cennik!$C$47</definedName>
+    <definedName function="false" hidden="false" name="c_dzwig_wspS" vbProcedure="false">Cennik!$C$48</definedName>
+    <definedName function="false" hidden="false" name="c_gdw" vbProcedure="false">Cennik!$C$66</definedName>
+    <definedName function="false" hidden="false" name="c_hotel" vbProcedure="false">Cennik!$C$63</definedName>
     <definedName function="false" hidden="false" name="c_hydr_drobne" vbProcedure="false">Cennik!$C$20</definedName>
-    <definedName function="false" hidden="false" name="c_km_dodatek" vbProcedure="false">Cennik!$C$52</definedName>
-    <definedName function="false" hidden="false" name="c_km_dzien" vbProcedure="false">Cennik!$C$54</definedName>
-    <definedName function="false" hidden="false" name="c_km_krakow" vbProcedure="false">Cennik!$C$53</definedName>
-    <definedName function="false" hidden="false" name="c_kob" vbProcedure="false">Cennik!$C$66</definedName>
-    <definedName function="false" hidden="false" name="c_konserw" vbProcedure="false">Cennik!$C$70</definedName>
-    <definedName function="false" hidden="false" name="c_konserw2" vbProcedure="false">Cennik!$C$71</definedName>
-    <definedName function="false" hidden="false" name="c_konserw3" vbProcedure="false">Cennik!$C$72</definedName>
+    <definedName function="false" hidden="false" name="c_km_dodatek" vbProcedure="false">Cennik!$C$51</definedName>
+    <definedName function="false" hidden="false" name="c_km_dzien" vbProcedure="false">Cennik!$C$53</definedName>
+    <definedName function="false" hidden="false" name="c_km_krakow" vbProcedure="false">Cennik!$C$52</definedName>
+    <definedName function="false" hidden="false" name="c_kob" vbProcedure="false">Cennik!$C$65</definedName>
+    <definedName function="false" hidden="false" name="c_konserw" vbProcedure="false">Cennik!$C$69</definedName>
+    <definedName function="false" hidden="false" name="c_konserw2" vbProcedure="false">Cennik!$C$70</definedName>
+    <definedName function="false" hidden="false" name="c_konserw3" vbProcedure="false">Cennik!$C$71</definedName>
     <definedName function="false" hidden="false" name="c_magistrala" vbProcedure="false">Cennik!$C$26</definedName>
     <definedName function="false" hidden="false" name="c_mal_bar" vbProcedure="false">Cennik!$C$35</definedName>
     <definedName function="false" hidden="false" name="c_mal_D" vbProcedure="false">Cennik!$C$34</definedName>
     <definedName function="false" hidden="false" name="c_mal_S" vbProcedure="false">Cennik!$C$33</definedName>
     <definedName function="false" hidden="false" name="c_maskownica" vbProcedure="false">Cennik!$C$29</definedName>
-    <definedName function="false" hidden="false" name="c_odbiory_osoby" vbProcedure="false">Cennik!$C$58</definedName>
+    <definedName function="false" hidden="false" name="c_odbiory_osoby" vbProcedure="false">Cennik!$C$57</definedName>
     <definedName function="false" hidden="false" name="c_olej" vbProcedure="false">Cennik!$C$19</definedName>
     <definedName function="false" hidden="false" name="c_osd_barierka" vbProcedure="false">Cennik!$C$44</definedName>
     <definedName function="false" hidden="false" name="c_osd_D" vbProcedure="false">Cennik!$C$41</definedName>
     <definedName function="false" hidden="false" name="c_osd_magistrala" vbProcedure="false">Cennik!$C$43</definedName>
     <definedName function="false" hidden="false" name="c_osd_NP" vbProcedure="false">Cennik!$C$42</definedName>
     <definedName function="false" hidden="false" name="c_osd_S" vbProcedure="false">Cennik!$C$40</definedName>
-    <definedName function="false" hidden="false" name="c_paliwo" vbProcedure="false">Cennik!$C$56</definedName>
-    <definedName function="false" hidden="false" name="c_podatek" vbProcedure="false">Cennik!$C$68</definedName>
-    <definedName function="false" hidden="false" name="c_pomiary_osoby" vbProcedure="false">Cennik!$C$57</definedName>
+    <definedName function="false" hidden="false" name="c_paliwo" vbProcedure="false">Cennik!$C$55</definedName>
+    <definedName function="false" hidden="false" name="c_podatek" vbProcedure="false">Cennik!$C$67</definedName>
+    <definedName function="false" hidden="false" name="c_pomiary_osoby" vbProcedure="false">Cennik!$C$56</definedName>
     <definedName function="false" hidden="false" name="c_q2500" vbProcedure="false">Cennik!$C$16</definedName>
     <definedName function="false" hidden="false" name="c_rozl_TIR" vbProcedure="false">Cennik!$C$45</definedName>
     <definedName function="false" hidden="false" name="c_sil_1700" vbProcedure="false">Cennik!$C$23</definedName>
@@ -61,10 +60,10 @@
     <definedName function="false" hidden="false" name="c_slupek" vbProcedure="false">Cennik!$C$36</definedName>
     <definedName function="false" hidden="false" name="c_slupek22" vbProcedure="false">Cennik!$C$37</definedName>
     <definedName function="false" hidden="false" name="c_slupek_rbd" vbProcedure="false">Cennik!$C$38</definedName>
-    <definedName function="false" hidden="false" name="c_spalanie" vbProcedure="false">Cennik!$C$55</definedName>
-    <definedName function="false" hidden="false" name="c_stawka_1" vbProcedure="false">Cennik!$C$60</definedName>
-    <definedName function="false" hidden="false" name="c_stawka_2" vbProcedure="false">Cennik!$C$61</definedName>
-    <definedName function="false" hidden="false" name="c_stawka_n" vbProcedure="false">Cennik!$C$62</definedName>
+    <definedName function="false" hidden="false" name="c_spalanie" vbProcedure="false">Cennik!$C$54</definedName>
+    <definedName function="false" hidden="false" name="c_stawka_1" vbProcedure="false">Cennik!$C$59</definedName>
+    <definedName function="false" hidden="false" name="c_stawka_2" vbProcedure="false">Cennik!$C$60</definedName>
+    <definedName function="false" hidden="false" name="c_stawka_n" vbProcedure="false">Cennik!$C$61</definedName>
     <definedName function="false" hidden="false" name="c_szer_260" vbProcedure="false">Cennik!$C$10</definedName>
     <definedName function="false" hidden="false" name="c_szer_270" vbProcedure="false">Cennik!$C$11</definedName>
     <definedName function="false" hidden="false" name="c_szer_520" vbProcedure="false">Cennik!$C$12</definedName>
@@ -120,7 +119,7 @@
     <definedName function="false" hidden="false" name="in_wyjazdy" vbProcedure="false">Dane!$C$52</definedName>
     <definedName function="false" hidden="false" name="in_wzor" vbProcedure="false">Dane!$C$53</definedName>
     <definedName function="false" hidden="false" name="in_zysk" vbProcedure="false">Dane!$C$56</definedName>
-    <definedName function="false" hidden="false" name="in_zysk_min" vbProcedure="false">Dane!$C$57</definedName>
+    <definedName function="false" hidden="false" name="in_zysk2" vbProcedure="false">Dane!$C$57</definedName>
     <definedName function="false" hidden="false" name="m_barierki" vbProcedure="false">Obliczenia!$C$18</definedName>
     <definedName function="false" hidden="false" name="m_cena_D" vbProcedure="false">Obliczenia!$C$5</definedName>
     <definedName function="false" hidden="false" name="m_cena_NP" vbProcedure="false">Obliczenia!$C$7</definedName>
@@ -142,12 +141,12 @@
     <definedName function="false" hidden="false" name="m_suma_2500" vbProcedure="false">Obliczenia!$C$22</definedName>
     <definedName function="false" hidden="false" name="m_utr" vbProcedure="false">Obliczenia!$C$25</definedName>
     <definedName function="false" hidden="false" name="m_utr_auto" vbProcedure="false">Obliczenia!$C$24</definedName>
-    <definedName function="false" hidden="false" name="t_gl_doplata" vbProcedure="false">Cennik!$C$76:$C$84</definedName>
-    <definedName function="false" hidden="false" name="t_gl_silownik" vbProcedure="false">Cennik!$D$76:$D$84</definedName>
-    <definedName function="false" hidden="false" name="t_sk_cena" vbProcedure="false">Cennik!$C$88:$C$114</definedName>
-    <definedName function="false" hidden="false" name="t_sk_D" vbProcedure="false">Cennik!$E$88:$E$114</definedName>
-    <definedName function="false" hidden="false" name="t_sk_grupa" vbProcedure="false">Cennik!$F$88:$F$114</definedName>
-    <definedName function="false" hidden="false" name="t_sk_S" vbProcedure="false">Cennik!$D$88:$D$114</definedName>
+    <definedName function="false" hidden="false" name="t_gl_doplata" vbProcedure="false">Cennik!$C$75:$C$83</definedName>
+    <definedName function="false" hidden="false" name="t_gl_silownik" vbProcedure="false">Cennik!$D$75:$D$83</definedName>
+    <definedName function="false" hidden="false" name="t_sk_cena" vbProcedure="false">Cennik!$C$87:$C$113</definedName>
+    <definedName function="false" hidden="false" name="t_sk_D" vbProcedure="false">Cennik!$E$87:$E$113</definedName>
+    <definedName function="false" hidden="false" name="t_sk_grupa" vbProcedure="false">Cennik!$F$87:$F$113</definedName>
+    <definedName function="false" hidden="false" name="t_sk_S" vbProcedure="false">Cennik!$D$87:$D$113</definedName>
     <definedName function="false" hidden="false" name="t_wymiary" vbProcedure="false">Dane!$F$46</definedName>
     <definedName function="false" hidden="false" name="t_zaglebienia" vbProcedure="false">Dane!$F$45</definedName>
   </definedNames>
@@ -161,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="363">
   <si>
     <t xml:space="preserve">KALKULATOR NK38 - DANE WEJŚCIOWE</t>
   </si>
@@ -364,10 +363,10 @@
     <t xml:space="preserve">6. Narzuty i kurs</t>
   </si>
   <si>
-    <t xml:space="preserve">Zysk (udział w cenie)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zysk do sprawdzenia 'do ilu zejdziemy' (cena minimalna)</t>
+    <t xml:space="preserve">Zysk A (udział w cenie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zysk B - do porównania, do ilu możemy zejść</t>
   </si>
   <si>
     <t xml:space="preserve">Dopłata za Q=2500 kg</t>
@@ -403,847 +402,853 @@
     <t xml:space="preserve">2500 kg + słupki</t>
   </si>
   <si>
-    <t xml:space="preserve">CENA KONTRAKTU NETTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cena za miejsce postojowe</t>
+    <t xml:space="preserve">Cena za MP - zysk A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cena za MP - zysk B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cena za MP [EUR] - zysk A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zysk A [zł]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zysk B [zł]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koszt rzeczywisty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urządzenia (materiały)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Słupki e-ładowarek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport, dźwig, rozładunek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robocizna (montaż, rozładunek, dojazdy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel, diety, paliwo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOB + GDW + podatek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dni pracy ekipy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tygodnie montażu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osobodni razem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opcje do oferty (cena z narzutami)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q=2000 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q=2500 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Słupki e-ładowarek 3,7 kW (z robocizną)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Słupki e-ładowarek 22 kW (z robocizną)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malowanie proszkowe RAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liczba osób</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 os.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 os.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 os.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 os.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 os.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 os.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cena kontraktu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cena za MP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tygodnie (Kraków: dni)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel + diety</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zielone = najtańsza liczba osób</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zestawienie do oferty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urządzenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zagłębienia niestandardowe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wymiary niestandardowe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magistrala EXTRA / barierki / maskownice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utrudnienia [osobodni]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Km pomiary / montaż</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ekipa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dźwig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czas montażu (bez słupków)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czas montażu (ze słupkami)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zysk A / zysk B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dopłata Q=2500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konserwacja roczna (40 / 45 / 50 zł/MP/mies.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opis / wariant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontrola danych:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uwagi do sprawdzenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Hotel liczony jako (dni pracy + 1) x osoby - do sprawdzenia (może zapas na przyjazd na odbiór).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Podatek 14% od robocizny, diet, GDW i zysku = wartość efektywna; 'koszt ludzki' w starym arkuszu używał x1,19 - do sprawdzenia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Systemy N.P. liczone jak D (siłowniki, składowe, dźwig, 7 osobodni), cena 85% D, 2 MP - do potwierdzenia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Czas podróży: wzór 'Stary (poprawiony)' = stary dla &lt; 800 km, dla &gt;= 800 km uwzględnia liczbę wyjazdów. 'Uproszczony' = 2 x km / 650 km dziennie na wyjazd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Zysk B liczony od tych samych kosztów co zysk A (dawna kolumna N, bez zmiany ceny dźwigu).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENNIK I STAŁE KALKULACYJNE NK38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zmiana ceny tutaj działa we wszystkich formułach. Kolumna E = skąd wartość pochodzi w starym arkuszu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platformy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platforma podwójna NK38-500-170-530 (4 MP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dopłata za NK37 / system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cena S jako ułamek ceny D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!F3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cena systemu N.P. jako ułamek ceny D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szerokość S 260 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szerokość S 270 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szerokość D 520 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szerokość D 540 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E21/E47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dopłata za 1 cm długości (ułamek ceny platformy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E22 (4 kg/cm z 3150 kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dopłata Q=2500 kg (domyślna)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!D90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydraulika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agregat 11,5 l/min (do 6 platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olej 150 l / agregat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!D134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elementy drobne / agregat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!D135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport agregatu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!F57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport siłowników / platformę</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siłownik standard (zagł. 170)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!D130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siłownik do zagł. 2000 (też 175 cm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!D129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siłownik do zagł. 2250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!D128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magistrala EXTRA / 6 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!D133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barierki, elektryka, administracja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barierka na stronę (Metazet 538 zł)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maskownica / bariera tylna (Metazet 608 zł)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elektryka - skrzynka zasilająca / agregat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!D121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administracja, koszty biura / agregat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!D125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opcje oferty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malowanie proszkowe RAL - system S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malowanie proszkowe RAL - system D / NP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malowanie barierki na stronę</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Słupek e-ładowarki do 3,7 kW / MP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E97, KAL!O55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Słupek e-ładowarki do 22 kW / MP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NK38!E98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robocizna słupka (roboczodni / MP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!B49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaż - pracochłonność</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osobodni montażu / system S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!F16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osobodni montażu / system D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osobodni montażu / system NP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!F17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utrudnienia: osobodni / magistrala 6 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!B48 ('tonaż')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utrudnienia: osobodni / barierka lub maskownica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dni rozładunku / TIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!E55 (komentarz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider Crane / dzień</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!I25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systemów D (i NP) na 1 dzień dźwigu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!J25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Współczynnik S względem D (dźwig)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dni montażu w tygodniu (wyjazd co tydzień)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B55 = J39/5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaż - dojazdy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaż: km dodane do odległości (nocleg, sklep)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAW: 280 -&gt; 330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kraków: km na pomiary i montaż</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KRK: 20 / 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wzór uproszczony: km dziennie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propozycja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spalanie auta ekipy l/100 km (1 auto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!I19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cena paliwa zł/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pomiary - liczba osób (1 wyjazd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!F53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odbiory - liczba osób (1 wyjazd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!F58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaż - koszty ekipy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stawka dzienna - 1. osoba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!I47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stawka dzienna - 2. osoba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!I48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stawka dzienna - każda kolejna osoba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!I49:I53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dieta dzienna (za granicą 49 €)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!J57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel / doba / osoba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!J58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narzuty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOB (udział w cenie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!J35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDW (udział w cenie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!J36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podatek efektywny od robocizny, diet, GDW i zysku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!J37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serwis (informacyjnie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konserwacja zł / MP / miesiąc (wariant 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!I45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konserwacja zł / MP / miesiąc (wariant 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!L45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konserwacja zł / MP / miesiąc (wariant 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAL!N45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zagłębienia (standard 170 cm: bez dopłaty, siłownik 1700)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zagłębienie [cm]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dopłata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siłownik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Składowe platformy (na 1 platformę; N.P. liczone jak D)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pozycja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cena jedn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ilość na S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ilość na D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grupa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Łańcuch 20B-1 (mb)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mechanika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ogniwo złączne proste 20B-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koło łańcuchowe z piastą 20B-1 Z10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koło łańcuchowe z piastą 20B-1 Z16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listwa zębata M4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koło zębate z piastą M4 Z20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuleja PAF40x260P10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuleja PAF 5025 P10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuleja TBR40x44x50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podkładka PTFE 50,5x69x2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podkładka PTFE 42x66x1,5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuleja PAF40x400P10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podkładki gumowe pod stopę siłownika i słup (kpl)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Śruby i elementy złączne - kpl S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Śruby i elementy złączne - kpl D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tulejki podłogi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kotwa M16 + ampułka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podkładki gumowe pod kotwy (kpl)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport materiałów (bez MTZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ogranicznik koła</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rurki gotowe na platformie - S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rurki gotowe na platformie - D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elementy złączne Argo Hytos + magistrala 5 mb + wąż</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elektryka - skrzynka krosowa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elektryka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elektryka - przewody + rurki S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elektryka - przewody + rurki D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elektryka - sterownia (puszka+stac+przyc+notaus+szyld)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBLICZENIA (nie edytować)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. Materiały i urządzenia (dawny arkusz 'NK38 ...')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cena platformy D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cena platformy S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cena systemu N.P.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platformy D + N.P. (N.P. jak D)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razem platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miejsca postojowe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platformy S z dopłatami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platformy D z dopłatami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platformy N.P.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siłowniki 2000 [pary]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siłowniki 2250 [pary]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siłowniki standard [pary] (z N.P.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barierki i maskownice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mechanika zakupowa i pozostałe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMA STANDARD Q=2000 (dawne F87)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMA Q=2500 (dawne F90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opcja: malowanie proszkowe RAL (koszt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utrudnienia z magistrali i barierek [osobodni]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utrudnienia razem [osobodni] (dawny 'tonaż')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. Parametry montażu wspólne dla wariantów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kraków?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Km na pomiary / odbiory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Km na montaż</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dni rozładunku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podróże pomiary + odbiory [osobodni]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dni dźwigu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mnożnik kosztu materiałowego na cenę (opcje)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. Montaż i cena (dawny arkusz '&lt;Inwestycja&gt;-NK38')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analiza liczby osób (wariant z Dane)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wariant / liczba osób</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q=2500? (1/0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Słupki e-ładowarek? (1/0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Średnia stawka dzienna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osobodni montażu (dawne F50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iteracja 1: tygodnie / dni montażu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iteracja 2: tygodnie / dni montażu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iteracja 3: tygodnie / dni montażu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iteracja 4: tygodnie / dni montażu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iteracja 5: tygodnie / dni montażu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tygodnie (Kraków: dni) montażu (dawne B55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osobodni podróży i rozładunku (dawne G59)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dni pracy ekipy (dawne J39)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tygodnie montażu (do oferty)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilometry razem (1 auto ekipy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paliwo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport TIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider Crane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rozładunek (sprzęt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rozładunek (ludzie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dojazdy (ludzie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaż</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diety</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suma kosztów przed narzutami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podstawa narzutów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zysk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podatek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENA KONTRAKTU NETTO (dawne K39)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koszt rzeczywisty (dawne K43)</t>
   </si>
   <si>
     <t xml:space="preserve">Cena za MP [EUR]</t>
   </si>
   <si>
-    <t xml:space="preserve">Cena minimalna (zysk do sprawdzenia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zysk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koszt rzeczywisty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urządzenia (materiały)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Słupki e-ładowarek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport, dźwig, rozładunek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robocizna (montaż, rozładunek, dojazdy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel, diety, paliwo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOB + GDW + podatek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dni pracy ekipy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tygodnie (Kraków: dni) montażu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Osobodni razem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opcje do oferty (cena z narzutami)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q=2000 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q=2500 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Słupki e-ładowarek 3,7 kW (z robocizną)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Słupki e-ładowarek 22 kW (z robocizną)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malowanie proszkowe RAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liczba osób</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 os.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 os.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 os.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 os.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 os.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 os.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cena kontraktu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cena za MP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tygodnie (Kraków: dni)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel + diety</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zielone = najtańsza liczba osób</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zestawienie do oferty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urządzenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zagłębienia niestandardowe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wymiary niestandardowe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magistrala EXTRA / barierki / maskownice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utrudnienia [osobodni]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Km pomiary / montaż</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ekipa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dźwig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czas montażu (bez słupków)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czas montażu (ze słupkami)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zysk / cena minimalna przy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dopłata Q=2500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konserwacja roczna (40 / 45 / 50 zł/MP/mies.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opis / wariant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontrola danych:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uwagi do sprawdzenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Hotel liczony jako (dni pracy + 1) x osoby - do sprawdzenia (może zapas na przyjazd na odbiór).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Podatek 14% od robocizny, diet, GDW i zysku = wartość efektywna; 'koszt ludzki' w starym arkuszu używał x1,19 - do sprawdzenia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Systemy N.P. liczone jak D (siłowniki, składowe, dźwig, 7 osobodni), cena 85% D, 2 MP - do potwierdzenia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Czas podróży: wzór 'Stary (poprawiony)' = stary dla &lt; 800 km, dla &gt;= 800 km uwzględnia liczbę wyjazdów. 'Uproszczony' = 2 x km / 650 km dziennie na wyjazd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Cena minimalna liczona z dźwigiem 2000 zł/dzień (jak w starej kolumnie N).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENNIK I STAŁE KALKULACYJNE NK38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zmiana ceny tutaj działa we wszystkich formułach. Kolumna E = skąd wartość pochodzi w starym arkuszu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platformy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platforma podwójna NK38-500-170-530 (4 MP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dopłata za NK37 / system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!F1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cena S jako ułamek ceny D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!F3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cena systemu N.P. jako ułamek ceny D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Szerokość S 260 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Szerokość S 270 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Szerokość D 520 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Szerokość D 540 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E21/E47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dopłata za 1 cm długości (ułamek ceny platformy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E22 (4 kg/cm z 3150 kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dopłata Q=2500 kg (domyślna)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!D90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hydraulika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agregat 11,5 l/min (do 6 platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olej 150 l / agregat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!D134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elementy drobne / agregat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!D135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport agregatu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!F57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport siłowników / platformę</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siłownik standard (zagł. 170)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!D130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siłownik do zagł. 2000 (też 175 cm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!D129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siłownik do zagł. 2250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!D128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magistrala EXTRA / 6 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!D133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barierki, elektryka, administracja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barierka na stronę (Metazet 538 zł)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maskownica / bariera tylna (Metazet 608 zł)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elektryka - skrzynka zasilająca / agregat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!D121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Administracja, koszty biura / agregat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!D125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opcje oferty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malowanie proszkowe RAL - system S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malowanie proszkowe RAL - system D / NP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malowanie barierki na stronę</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Słupek e-ładowarki do 3,7 kW / MP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E97, KAL!O55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Słupek e-ładowarki do 22 kW / MP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NK38!E98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robocizna słupka (roboczodni / MP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!B49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaż - pracochłonność</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Osobodni montażu / system S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!F16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Osobodni montażu / system D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Osobodni montażu / system NP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!F17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utrudnienia: osobodni / magistrala 6 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!B48 ('tonaż')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utrudnienia: osobodni / barierka lub maskownica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dni rozładunku / TIR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!E55 (komentarz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider Crane / dzień</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!I25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider Crane / dzień - cena minimalna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!M25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systemów D (i NP) na 1 dzień dźwigu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!J25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Współczynnik S względem D (dźwig)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dni montażu w tygodniu (wyjazd co tydzień)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B55 = J39/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaż - dojazdy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaż: km dodane do odległości (nocleg, sklep)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAW: 280 -&gt; 330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kraków: km na pomiary i montaż</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRK: 20 / 20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wzór uproszczony: km dziennie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">propozycja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spalanie auta ekipy l/100 km (1 auto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!I19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cena paliwa zł/l</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pomiary - liczba osób (1 wyjazd)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!F53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Odbiory - liczba osób (1 wyjazd)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!F58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaż - koszty ekipy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stawka dzienna - 1. osoba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!I47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stawka dzienna - 2. osoba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!I48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stawka dzienna - każda kolejna osoba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!I49:I53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dieta dzienna (za granicą 49 €)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!J57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel / doba / osoba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!J58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narzuty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOB (udział w cenie)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!J35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDW (udział w cenie)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!J36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Podatek efektywny od robocizny, diet, GDW i zysku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!J37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serwis (informacyjnie)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konserwacja zł / MP / miesiąc (wariant 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!I45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konserwacja zł / MP / miesiąc (wariant 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!L45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konserwacja zł / MP / miesiąc (wariant 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!N45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zagłębienia (standard 170 cm: bez dopłaty, siłownik 1700)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zagłębienie [cm]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dopłata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siłownik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Składowe platformy (na 1 platformę; N.P. liczone jak D)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pozycja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cena jedn.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ilość na S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ilość na D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grupa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Łańcuch 20B-1 (mb)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mechanika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ogniwo złączne proste 20B-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koło łańcuchowe z piastą 20B-1 Z10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koło łańcuchowe z piastą 20B-1 Z16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Listwa zębata M4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koło zębate z piastą M4 Z20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuleja PAF40x260P10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuleja PAF 5025 P10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuleja TBR40x44x50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Podkładka PTFE 50,5x69x2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Podkładka PTFE 42x66x1,5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuleja PAF40x400P10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Podkładki gumowe pod stopę siłownika i słup (kpl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Śruby i elementy złączne - kpl S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Śruby i elementy złączne - kpl D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tulejki podłogi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotwa M16 + ampułka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Podkładki gumowe pod kotwy (kpl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport materiałów (bez MTZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ogranicznik koła</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rurki gotowe na platformie - S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rurki gotowe na platformie - D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elementy złączne Argo Hytos + magistrala 5 mb + wąż</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elektryka - skrzynka krosowa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elektryka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elektryka - przewody + rurki S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elektryka - przewody + rurki D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elektryka - sterownia (puszka+stac+przyc+notaus+szyld)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBLICZENIA (nie edytować)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A. Materiały i urządzenia (dawny arkusz 'NK38 ...')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cena platformy D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cena platformy S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cena systemu N.P.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platformy D + N.P. (N.P. jak D)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razem platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miejsca postojowe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platformy S z dopłatami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platformy D z dopłatami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platformy N.P.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siłowniki 2000 [pary]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siłowniki 2250 [pary]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siłowniki standard [pary] (z N.P.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barierki i maskownice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mechanika zakupowa i pozostałe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUMA STANDARD Q=2000 (dawne F87)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUMA Q=2500 (dawne F90)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opcja: malowanie proszkowe RAL (koszt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utrudnienia z magistrali i barierek [osobodni]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utrudnienia razem [osobodni] (dawny 'tonaż')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B. Parametry montażu wspólne dla wariantów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kraków?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Km na pomiary / odbiory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Km na montaż</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dni rozładunku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Podróże pomiary + odbiory [osobodni]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dni dźwigu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mnożnik kosztu materiałowego na cenę (opcje)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C. Montaż i cena (dawny arkusz '&lt;Inwestycja&gt;-NK38')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analiza liczby osób (wariant z Dane)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wariant / liczba osób</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q=2500? (1/0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Słupki e-ładowarek? (1/0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Średnia stawka dzienna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Osobodni montażu (dawne F50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iteracja 1: tygodnie / dni montażu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iteracja 2: tygodnie / dni montażu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iteracja 3: tygodnie / dni montażu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iteracja 4: tygodnie / dni montażu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iteracja 5: tygodnie / dni montażu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tygodnie (Kraków: dni) montażu (dawne B55)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Osobodni podróży i rozładunku (dawne G59)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dni pracy ekipy (dawne J39)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilometry razem (1 auto ekipy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paliwo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport TIR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider Crane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rozładunek (sprzęt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rozładunek (ludzie)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dojazdy (ludzie)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaż</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diety</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suma kosztów przed narzutami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Podstawa narzutów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Podatek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENA KONTRAKTU NETTO (dawne K39)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koszt rzeczywisty (dawne K43)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cena minimalna: podstawa narzutów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENA MINIMALNA (zysk do sprawdzenia, dźwig 2000)</t>
+    <t xml:space="preserve">Zysk B: podstawa narzutów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zysk B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENA KONTRAKTU NETTO - ZYSK B</t>
   </si>
 </sst>
 </file>
@@ -2532,7 +2537,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:H66"/>
+  <dimension ref="B2:H68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -2582,593 +2587,609 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11" t="s">
-        <v>80</v>
+      <c r="B7" s="11" t="str">
+        <f aca="false">"CENA NETTO - ZYSK A "&amp;TEXT(in_zysk,"0.0%")</f>
+        <v>CENA NETTO - ZYSK A 12.5%</v>
       </c>
       <c r="C7" s="18" t="n">
-        <f aca="false">Obliczenia!D70</f>
+        <f aca="false">Obliczenia!D71</f>
         <v>951980.820675503</v>
       </c>
       <c r="D7" s="18" t="n">
-        <f aca="false">Obliczenia!E70</f>
+        <f aca="false">Obliczenia!E71</f>
         <v>999035.721380829</v>
       </c>
       <c r="E7" s="18" t="n">
-        <f aca="false">Obliczenia!F70</f>
+        <f aca="false">Obliczenia!F71</f>
         <v>1095544.9005226</v>
       </c>
       <c r="F7" s="18" t="n">
-        <f aca="false">Obliczenia!G70</f>
+        <f aca="false">Obliczenia!G71</f>
         <v>1142599.80122793</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="19" t="n">
-        <f aca="false">Obliczenia!D72</f>
-        <v>15866.3470112584</v>
-      </c>
-      <c r="D8" s="19" t="n">
-        <f aca="false">Obliczenia!E72</f>
-        <v>16650.5953563471</v>
-      </c>
-      <c r="E8" s="19" t="n">
-        <f aca="false">Obliczenia!F72</f>
-        <v>18259.0816753767</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <f aca="false">Obliczenia!G72</f>
-        <v>19043.3300204655</v>
+      <c r="B8" s="11" t="str">
+        <f aca="false">"CENA NETTO - ZYSK B "&amp;TEXT(in_zysk2,"0.0%")</f>
+        <v>CENA NETTO - ZYSK B 10.0%</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <f aca="false">Obliczenia!D77</f>
+        <v>921791.99146069</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <f aca="false">Obliczenia!E77</f>
+        <v>967338.070288276</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <f aca="false">Obliczenia!F77</f>
+        <v>1060804.76981793</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <f aca="false">Obliczenia!G77</f>
+        <v>1106350.84864552</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="C9" s="19" t="n">
         <f aca="false">Obliczenia!D73</f>
-        <v>3668.51954017535</v>
-      </c>
-      <c r="D9" s="20" t="n">
+        <v>15866.3470112584</v>
+      </c>
+      <c r="D9" s="19" t="n">
         <f aca="false">Obliczenia!E73</f>
-        <v>3849.8486373057</v>
-      </c>
-      <c r="E9" s="20" t="n">
+        <v>16650.5953563471</v>
+      </c>
+      <c r="E9" s="19" t="n">
         <f aca="false">Obliczenia!F73</f>
-        <v>4221.75298852641</v>
-      </c>
-      <c r="F9" s="20" t="n">
+        <v>18259.0816753767</v>
+      </c>
+      <c r="F9" s="19" t="n">
         <f aca="false">Obliczenia!G73</f>
-        <v>4403.08208565676</v>
+        <v>19043.3300204655</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C10" s="19" t="n">
-        <f aca="false">Obliczenia!D75</f>
-        <v>920388.543184828</v>
+        <f aca="false">Obliczenia!D78</f>
+        <v>15363.1998576782</v>
       </c>
       <c r="D10" s="19" t="n">
-        <f aca="false">Obliczenia!E75</f>
-        <v>965934.622012414</v>
+        <f aca="false">Obliczenia!E78</f>
+        <v>16122.3011714713</v>
       </c>
       <c r="E10" s="19" t="n">
-        <f aca="false">Obliczenia!F75</f>
-        <v>1059401.32154207</v>
+        <f aca="false">Obliczenia!F78</f>
+        <v>17680.0794969655</v>
       </c>
       <c r="F10" s="19" t="n">
-        <f aca="false">Obliczenia!G75</f>
-        <v>1104947.40036966</v>
+        <f aca="false">Obliczenia!G78</f>
+        <v>18439.1808107586</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="19" t="n">
-        <f aca="false">Obliczenia!D68</f>
-        <v>115264.993491124</v>
-      </c>
-      <c r="D11" s="19" t="n">
-        <f aca="false">Obliczenia!E68</f>
-        <v>121025.877514793</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <f aca="false">Obliczenia!F68</f>
-        <v>132642.472189349</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <f aca="false">Obliczenia!G68</f>
-        <v>138403.356213018</v>
+        <v>82</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <f aca="false">Obliczenia!D74</f>
+        <v>3668.51954017535</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <f aca="false">Obliczenia!E74</f>
+        <v>3849.8486373057</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <f aca="false">Obliczenia!F74</f>
+        <v>4221.75298852641</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <f aca="false">Obliczenia!G74</f>
+        <v>4403.08208565676</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C12" s="19" t="n">
-        <f aca="false">Obliczenia!D71</f>
-        <v>836715.827184379</v>
+        <f aca="false">Obliczenia!D69</f>
+        <v>115264.993491124</v>
       </c>
       <c r="D12" s="19" t="n">
-        <f aca="false">Obliczenia!E71</f>
-        <v>878009.843866036</v>
+        <f aca="false">Obliczenia!E69</f>
+        <v>121025.877514793</v>
       </c>
       <c r="E12" s="19" t="n">
-        <f aca="false">Obliczenia!F71</f>
-        <v>962902.428333255</v>
+        <f aca="false">Obliczenia!F69</f>
+        <v>132642.472189349</v>
       </c>
       <c r="F12" s="19" t="n">
-        <f aca="false">Obliczenia!G71</f>
-        <v>1004196.44501491</v>
+        <f aca="false">Obliczenia!G69</f>
+        <v>138403.356213018</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <f aca="false">Obliczenia!D76</f>
+        <v>89562.2248275862</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <f aca="false">Obliczenia!E76</f>
+        <v>94038.4979310345</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <f aca="false">Obliczenia!F76</f>
+        <v>103064.725517241</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <f aca="false">Obliczenia!G76</f>
+        <v>107540.99862069</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14" s="19" t="n">
-        <f aca="false">Obliczenia!D53</f>
-        <v>649059.6</v>
+        <f aca="false">Obliczenia!D72</f>
+        <v>836715.827184379</v>
       </c>
       <c r="D14" s="19" t="n">
-        <f aca="false">Obliczenia!E53</f>
-        <v>688003.176</v>
+        <f aca="false">Obliczenia!E72</f>
+        <v>878009.843866036</v>
       </c>
       <c r="E14" s="19" t="n">
-        <f aca="false">Obliczenia!F53</f>
-        <v>649059.6</v>
+        <f aca="false">Obliczenia!F72</f>
+        <v>962902.428333255</v>
       </c>
       <c r="F14" s="19" t="n">
-        <f aca="false">Obliczenia!G53</f>
-        <v>688003.176</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="19" t="n">
-        <f aca="false">Obliczenia!D54</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="19" t="n">
-        <f aca="false">Obliczenia!E54</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <f aca="false">Obliczenia!F54</f>
-        <v>102000</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <f aca="false">Obliczenia!G54</f>
-        <v>102000</v>
+        <f aca="false">Obliczenia!G72</f>
+        <v>1004196.44501491</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C16" s="19" t="n">
-        <f aca="false">Obliczenia!D57+Obliczenia!D58+Obliczenia!D59</f>
-        <v>24300</v>
+        <f aca="false">Obliczenia!D54</f>
+        <v>649059.6</v>
       </c>
       <c r="D16" s="19" t="n">
-        <f aca="false">Obliczenia!E57+Obliczenia!E58+Obliczenia!E59</f>
-        <v>24300</v>
+        <f aca="false">Obliczenia!E54</f>
+        <v>688003.176</v>
       </c>
       <c r="E16" s="19" t="n">
-        <f aca="false">Obliczenia!F57+Obliczenia!F58+Obliczenia!F59</f>
-        <v>24300</v>
+        <f aca="false">Obliczenia!F54</f>
+        <v>649059.6</v>
       </c>
       <c r="F16" s="19" t="n">
-        <f aca="false">Obliczenia!G57+Obliczenia!G58+Obliczenia!G59</f>
-        <v>24300</v>
+        <f aca="false">Obliczenia!G54</f>
+        <v>688003.176</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C17" s="19" t="n">
-        <f aca="false">Obliczenia!D62+Obliczenia!D60+Obliczenia!D61</f>
-        <v>67392.32</v>
+        <f aca="false">Obliczenia!D55</f>
+        <v>0</v>
       </c>
       <c r="D17" s="19" t="n">
-        <f aca="false">Obliczenia!E62+Obliczenia!E60+Obliczenia!E61</f>
-        <v>67392.32</v>
+        <f aca="false">Obliczenia!E55</f>
+        <v>0</v>
       </c>
       <c r="E17" s="19" t="n">
-        <f aca="false">Obliczenia!F62+Obliczenia!F60+Obliczenia!F61</f>
-        <v>77824.64</v>
+        <f aca="false">Obliczenia!F55</f>
+        <v>102000</v>
       </c>
       <c r="F17" s="19" t="n">
-        <f aca="false">Obliczenia!G62+Obliczenia!G60+Obliczenia!G61</f>
-        <v>77824.64</v>
+        <f aca="false">Obliczenia!G55</f>
+        <v>102000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C18" s="19" t="n">
-        <f aca="false">Obliczenia!D56+Obliczenia!D63+Obliczenia!D55</f>
-        <v>38439.436</v>
+        <f aca="false">Obliczenia!D58+Obliczenia!D59+Obliczenia!D60</f>
+        <v>24300</v>
       </c>
       <c r="D18" s="19" t="n">
-        <f aca="false">Obliczenia!E56+Obliczenia!E63+Obliczenia!E55</f>
-        <v>38439.436</v>
+        <f aca="false">Obliczenia!E58+Obliczenia!E59+Obliczenia!E60</f>
+        <v>24300</v>
       </c>
       <c r="E18" s="19" t="n">
-        <f aca="false">Obliczenia!F56+Obliczenia!F63+Obliczenia!F55</f>
-        <v>43478.872</v>
+        <f aca="false">Obliczenia!F58+Obliczenia!F59+Obliczenia!F60</f>
+        <v>24300</v>
       </c>
       <c r="F18" s="19" t="n">
-        <f aca="false">Obliczenia!G56+Obliczenia!G63+Obliczenia!G55</f>
-        <v>43478.872</v>
+        <f aca="false">Obliczenia!G58+Obliczenia!G59+Obliczenia!G60</f>
+        <v>24300</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <f aca="false">Obliczenia!D63+Obliczenia!D61+Obliczenia!D62</f>
+        <v>67392.32</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <f aca="false">Obliczenia!E63+Obliczenia!E61+Obliczenia!E62</f>
+        <v>67392.32</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <f aca="false">Obliczenia!F63+Obliczenia!F61+Obliczenia!F62</f>
+        <v>77824.64</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <f aca="false">Obliczenia!G63+Obliczenia!G61+Obliczenia!G62</f>
+        <v>77824.64</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <f aca="false">Obliczenia!D57+Obliczenia!D64+Obliczenia!D56</f>
+        <v>38439.436</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <f aca="false">Obliczenia!E57+Obliczenia!E64+Obliczenia!E56</f>
+        <v>38439.436</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <f aca="false">Obliczenia!F57+Obliczenia!F64+Obliczenia!F56</f>
+        <v>43478.872</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <f aca="false">Obliczenia!G57+Obliczenia!G64+Obliczenia!G56</f>
+        <v>43478.872</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="19" t="n">
-        <f aca="false">Obliczenia!D66+Obliczenia!D67+Obliczenia!D69</f>
+      <c r="C21" s="19" t="n">
+        <f aca="false">Obliczenia!D67+Obliczenia!D68+Obliczenia!D70</f>
         <v>57524.4711843787</v>
       </c>
-      <c r="D19" s="19" t="n">
-        <f aca="false">Obliczenia!E66+Obliczenia!E67+Obliczenia!E69</f>
+      <c r="D21" s="19" t="n">
+        <f aca="false">Obliczenia!E67+Obliczenia!E68+Obliczenia!E70</f>
         <v>59874.9118660355</v>
       </c>
-      <c r="E19" s="19" t="n">
-        <f aca="false">Obliczenia!F66+Obliczenia!F67+Obliczenia!F69</f>
+      <c r="E21" s="19" t="n">
+        <f aca="false">Obliczenia!F67+Obliczenia!F68+Obliczenia!F70</f>
         <v>66239.3163332545</v>
       </c>
-      <c r="F19" s="19" t="n">
-        <f aca="false">Obliczenia!G66+Obliczenia!G67+Obliczenia!G69</f>
+      <c r="F21" s="19" t="n">
+        <f aca="false">Obliczenia!G67+Obliczenia!G68+Obliczenia!G70</f>
         <v>68589.7570149112</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C23" s="21" t="n">
         <f aca="false">Obliczenia!D51</f>
         <v>43</v>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D23" s="21" t="n">
         <f aca="false">Obliczenia!E51</f>
         <v>43</v>
       </c>
-      <c r="E21" s="21" t="n">
+      <c r="E23" s="21" t="n">
         <f aca="false">Obliczenia!F51</f>
         <v>49</v>
       </c>
-      <c r="F21" s="21" t="n">
+      <c r="F23" s="21" t="n">
         <f aca="false">Obliczenia!G51</f>
         <v>49</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="11" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="21" t="n">
-        <f aca="false">Obliczenia!D48</f>
+      <c r="C24" s="21" t="n">
+        <f aca="false">Obliczenia!D52</f>
         <v>9</v>
       </c>
-      <c r="D22" s="21" t="n">
-        <f aca="false">Obliczenia!E48</f>
+      <c r="D24" s="21" t="n">
+        <f aca="false">Obliczenia!E52</f>
         <v>9</v>
       </c>
-      <c r="E22" s="21" t="n">
-        <f aca="false">Obliczenia!F48</f>
+      <c r="E24" s="21" t="n">
+        <f aca="false">Obliczenia!F52</f>
         <v>10</v>
       </c>
-      <c r="F22" s="21" t="n">
-        <f aca="false">Obliczenia!G48</f>
+      <c r="F24" s="21" t="n">
+        <f aca="false">Obliczenia!G52</f>
         <v>10</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="C25" s="22" t="n">
         <f aca="false">Obliczenia!D50</f>
         <v>168.4808</v>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="D25" s="22" t="n">
         <f aca="false">Obliczenia!E50</f>
         <v>168.4808</v>
       </c>
-      <c r="E23" s="22" t="n">
+      <c r="E25" s="22" t="n">
         <f aca="false">Obliczenia!F50</f>
         <v>194.5616</v>
       </c>
-      <c r="F23" s="22" t="n">
+      <c r="F25" s="22" t="n">
         <f aca="false">Obliczenia!G50</f>
         <v>194.5616</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="4" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="C26" s="19" t="n">
-        <f aca="false">Obliczenia!F70-Obliczenia!D70</f>
-        <v>143564.079847101</v>
-      </c>
-      <c r="D26" s="19" t="n">
-        <f aca="false">Obliczenia!G70-Obliczenia!E70</f>
-        <v>143564.0798471</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="C27" s="19" t="n">
-        <f aca="false">Obliczenia!F70-Obliczenia!D70+(c_slupek22-c_slupek)*m_MP*e_mnoznik</f>
-        <v>477050.470379645</v>
-      </c>
-      <c r="D27" s="19" t="n">
-        <f aca="false">Obliczenia!G70-Obliczenia!E70+(c_slupek22-c_slupek)*m_MP*e_mnoznik</f>
-        <v>477050.470379645</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="19" t="n">
+        <f aca="false">Obliczenia!F71-Obliczenia!D71</f>
+        <v>143564.079847101</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <f aca="false">Obliczenia!G71-Obliczenia!E71</f>
+        <v>143564.0798471</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="19" t="n">
+        <f aca="false">Obliczenia!F71-Obliczenia!D71+(c_slupek22-c_slupek)*m_MP*e_mnoznik</f>
+        <v>477050.470379645</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <f aca="false">Obliczenia!G71-Obliczenia!E71+(c_slupek22-c_slupek)*m_MP*e_mnoznik</f>
+        <v>477050.470379645</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="19" t="n">
+      <c r="C30" s="19" t="n">
         <f aca="false">m_malowanie*e_mnoznik</f>
         <v>251927.218934911</v>
       </c>
-      <c r="D28" s="19" t="n">
+      <c r="D30" s="19" t="n">
         <f aca="false">m_malowanie*e_mnoznik</f>
         <v>251927.218934911</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="11" t="str">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="11" t="str">
         <f aca="false">"Analiza liczby osób - wariant: "&amp;in_analiza</f>
         <v>Analiza liczby osób - wariant: 2000 kg</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="4" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C33" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D33" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E33" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="F31" s="17" t="s">
+      <c r="F33" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="G31" s="17" t="s">
+      <c r="G33" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="H31" s="17" t="s">
+      <c r="H33" s="17" t="s">
         <v>107</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="C32" s="19" t="n">
-        <f aca="false">Obliczenia!I70</f>
-        <v>965679.929906982</v>
-      </c>
-      <c r="D32" s="19" t="n">
-        <f aca="false">Obliczenia!J70</f>
-        <v>953567.068923511</v>
-      </c>
-      <c r="E32" s="19" t="n">
-        <f aca="false">Obliczenia!K70</f>
-        <v>951980.820675503</v>
-      </c>
-      <c r="F32" s="19" t="n">
-        <f aca="false">Obliczenia!L70</f>
-        <v>948060.597174319</v>
-      </c>
-      <c r="G32" s="19" t="n">
-        <f aca="false">Obliczenia!M70</f>
-        <v>947852.259148087</v>
-      </c>
-      <c r="H32" s="19" t="n">
-        <f aca="false">Obliczenia!N70</f>
-        <v>946466.865335537</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="C33" s="19" t="n">
-        <f aca="false">Obliczenia!I72</f>
-        <v>16094.6654984497</v>
-      </c>
-      <c r="D33" s="19" t="n">
-        <f aca="false">Obliczenia!J72</f>
-        <v>15892.7844820585</v>
-      </c>
-      <c r="E33" s="19" t="n">
-        <f aca="false">Obliczenia!K72</f>
-        <v>15866.3470112584</v>
-      </c>
-      <c r="F33" s="19" t="n">
-        <f aca="false">Obliczenia!L72</f>
-        <v>15801.0099529053</v>
-      </c>
-      <c r="G33" s="19" t="n">
-        <f aca="false">Obliczenia!M72</f>
-        <v>15797.5376524681</v>
-      </c>
-      <c r="H33" s="19" t="n">
-        <f aca="false">Obliczenia!N72</f>
-        <v>15774.4477555923</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="19" t="n">
+        <f aca="false">Obliczenia!I71</f>
+        <v>965679.929906982</v>
+      </c>
+      <c r="D34" s="19" t="n">
+        <f aca="false">Obliczenia!J71</f>
+        <v>953567.068923511</v>
+      </c>
+      <c r="E34" s="19" t="n">
+        <f aca="false">Obliczenia!K71</f>
+        <v>951980.820675503</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <f aca="false">Obliczenia!L71</f>
+        <v>948060.597174319</v>
+      </c>
+      <c r="G34" s="19" t="n">
+        <f aca="false">Obliczenia!M71</f>
+        <v>947852.259148087</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <f aca="false">Obliczenia!N71</f>
+        <v>946466.865335537</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="19" t="n">
+        <f aca="false">Obliczenia!I73</f>
+        <v>16094.6654984497</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <f aca="false">Obliczenia!J73</f>
+        <v>15892.7844820585</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <f aca="false">Obliczenia!K73</f>
+        <v>15866.3470112584</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <f aca="false">Obliczenia!L73</f>
+        <v>15801.0099529053</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <f aca="false">Obliczenia!M73</f>
+        <v>15797.5376524681</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <f aca="false">Obliczenia!N73</f>
+        <v>15774.4477555923</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="0" t="s">
         <v>92</v>
       </c>
-      <c r="C34" s="23" t="n">
+      <c r="C36" s="23" t="n">
         <f aca="false">Obliczenia!I51</f>
         <v>82</v>
       </c>
-      <c r="D34" s="23" t="n">
+      <c r="D36" s="23" t="n">
         <f aca="false">Obliczenia!J51</f>
         <v>55</v>
       </c>
-      <c r="E34" s="23" t="n">
+      <c r="E36" s="23" t="n">
         <f aca="false">Obliczenia!K51</f>
         <v>43</v>
       </c>
-      <c r="F34" s="23" t="n">
+      <c r="F36" s="23" t="n">
         <f aca="false">Obliczenia!L51</f>
         <v>34</v>
       </c>
-      <c r="G34" s="23" t="n">
+      <c r="G36" s="23" t="n">
         <f aca="false">Obliczenia!M51</f>
         <v>29</v>
       </c>
-      <c r="H34" s="23" t="n">
+      <c r="H36" s="23" t="n">
         <f aca="false">Obliczenia!N51</f>
         <v>25</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="0" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="23" t="n">
+      <c r="C37" s="23" t="n">
         <f aca="false">Obliczenia!I48</f>
         <v>17</v>
       </c>
-      <c r="D35" s="23" t="n">
+      <c r="D37" s="23" t="n">
         <f aca="false">Obliczenia!J48</f>
         <v>11</v>
       </c>
-      <c r="E35" s="23" t="n">
+      <c r="E37" s="23" t="n">
         <f aca="false">Obliczenia!K48</f>
         <v>9</v>
       </c>
-      <c r="F35" s="23" t="n">
+      <c r="F37" s="23" t="n">
         <f aca="false">Obliczenia!L48</f>
         <v>7</v>
       </c>
-      <c r="G35" s="23" t="n">
+      <c r="G37" s="23" t="n">
         <f aca="false">Obliczenia!M48</f>
         <v>6</v>
       </c>
-      <c r="H35" s="23" t="n">
+      <c r="H37" s="23" t="n">
         <f aca="false">Obliczenia!N48</f>
         <v>5</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="0" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="0" t="s">
         <v>111</v>
       </c>
-      <c r="C36" s="19" t="n">
-        <f aca="false">Obliczenia!I56+Obliczenia!I63</f>
+      <c r="C38" s="19" t="n">
+        <f aca="false">Obliczenia!I57+Obliczenia!I64</f>
         <v>28939.318</v>
       </c>
-      <c r="D36" s="19" t="n">
-        <f aca="false">Obliczenia!J56+Obliczenia!J63</f>
+      <c r="D38" s="19" t="n">
+        <f aca="false">Obliczenia!J57+Obliczenia!J64</f>
         <v>29223.159</v>
       </c>
-      <c r="E36" s="19" t="n">
-        <f aca="false">Obliczenia!K56+Obliczenia!K63</f>
+      <c r="E38" s="19" t="n">
+        <f aca="false">Obliczenia!K57+Obliczenia!K64</f>
         <v>30461.636</v>
       </c>
-      <c r="F36" s="19" t="n">
-        <f aca="false">Obliczenia!L56+Obliczenia!L63</f>
+      <c r="F38" s="19" t="n">
+        <f aca="false">Obliczenia!L57+Obliczenia!L64</f>
         <v>30355.477</v>
       </c>
-      <c r="G36" s="19" t="n">
-        <f aca="false">Obliczenia!M56+Obliczenia!M63</f>
+      <c r="G38" s="19" t="n">
+        <f aca="false">Obliczenia!M57+Obliczenia!M64</f>
         <v>31116.636</v>
       </c>
-      <c r="H36" s="19" t="n">
-        <f aca="false">Obliczenia!N56+Obliczenia!N63</f>
+      <c r="H38" s="19" t="n">
+        <f aca="false">Obliczenia!N57+Obliczenia!N64</f>
         <v>31400.477</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="8" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="8" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="4" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="0" t="s">
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="C40" s="16" t="str">
+      <c r="C42" s="16" t="str">
         <f aca="false">in_typ&amp;": "&amp;IF(in_S&gt;0,in_S&amp;" x S (2 MP)  ","")&amp;IF(in_D&gt;0,in_D&amp;" x D (4 MP)  ","")&amp;IF(in_NP&gt;0,in_NP&amp;" x N.P.  ","")&amp;"= "&amp;m_MP&amp;" MP"</f>
         <v>NK38: 15 x D (4 MP)  = 60 MP</v>
-      </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="16" t="str">
-        <f aca="false">in_agregaty&amp;" szt."</f>
-        <v>3 szt.</v>
-      </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="C42" s="16" t="str">
-        <f aca="false">IF(t_zaglebienia="","standard 170 cm",t_zaglebienia)</f>
-        <v>200 cm: 15D</v>
       </c>
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
@@ -3178,11 +3199,11 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="0" t="s">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="C43" s="16" t="str">
-        <f aca="false">IF(t_wymiary="","standard",t_wymiary)</f>
-        <v>standard</v>
+        <f aca="false">in_agregaty&amp;" szt."</f>
+        <v>3 szt.</v>
       </c>
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
@@ -3192,11 +3213,11 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="0" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C44" s="16" t="str">
-        <f aca="false">in_magistrala&amp;" x 6 m  /  "&amp;in_barierki&amp;" szt.  /  "&amp;in_maskownice&amp;" szt."</f>
-        <v>4 x 6 m  /  30 szt.  /  5 szt.</v>
+        <f aca="false">IF(t_zaglebienia="","standard 170 cm",t_zaglebienia)</f>
+        <v>200 cm: 15D</v>
       </c>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
@@ -3206,11 +3227,11 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="0" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C45" s="16" t="str">
-        <f aca="false">m_utr&amp;" (z magistrali i barierek "&amp;m_utr_auto&amp;", ręcznie "&amp;in_utr_dod&amp;")"</f>
-        <v>20 (z magistrali i barierek 20, ręcznie 0)</v>
+        <f aca="false">IF(t_wymiary="","standard",t_wymiary)</f>
+        <v>standard</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
@@ -3220,11 +3241,11 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="0" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="C46" s="16" t="str">
-        <f aca="false">in_lok&amp;IF(e_krk,"","  ("&amp;in_km&amp;" km od Krakowa)")</f>
-        <v>Poza Krakowem  (280 km od Krakowa)</v>
+        <f aca="false">in_magistrala&amp;" x 6 m  /  "&amp;in_barierki&amp;" szt.  /  "&amp;in_maskownice&amp;" szt."</f>
+        <v>4 x 6 m  /  30 szt.  /  5 szt.</v>
       </c>
       <c r="D46" s="16"/>
       <c r="E46" s="16"/>
@@ -3234,11 +3255,11 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C47" s="16" t="str">
-        <f aca="false">e_km_pom&amp;" / "&amp;e_km_mon&amp;" km"</f>
-        <v>280 / 330 km</v>
+        <f aca="false">m_utr&amp;" (z magistrali i barierek "&amp;m_utr_auto&amp;", ręcznie "&amp;in_utr_dod&amp;")"</f>
+        <v>20 (z magistrali i barierek 20, ręcznie 0)</v>
       </c>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
@@ -3248,11 +3269,11 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="0" t="s">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="C48" s="16" t="str">
-        <f aca="false">in_tir&amp;" TIR x "&amp;TEXT(in_tir_cena,"#,##0")&amp;" zł, rozładunek "&amp;TEXT(in_rozl_cena,"#,##0")&amp;" zł/TIR, "&amp;e_rozl_dni&amp;" dni"</f>
-        <v>3 TIR x 4,000 zł, rozładunek 1,700 zł/TIR, 1.5 dni</v>
+        <f aca="false">in_lok&amp;IF(e_krk,"","  ("&amp;in_km&amp;" km od Krakowa)")</f>
+        <v>Poza Krakowem  (280 km od Krakowa)</v>
       </c>
       <c r="D48" s="16"/>
       <c r="E48" s="16"/>
@@ -3262,11 +3283,11 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="0" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C49" s="16" t="str">
-        <f aca="false">in_osoby&amp;" osób, średnia stawka "&amp;TEXT(Obliczenia!D41,"#,##0")&amp;" zł/dzień"</f>
-        <v>4 osób, średnia stawka 400 zł/dzień</v>
+        <f aca="false">e_km_pom&amp;" / "&amp;e_km_mon&amp;" km"</f>
+        <v>280 / 330 km</v>
       </c>
       <c r="D49" s="16"/>
       <c r="E49" s="16"/>
@@ -3276,11 +3297,11 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="0" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C50" s="16" t="str">
-        <f aca="false">e_dzw_dni&amp;" dni"</f>
-        <v>3 dni</v>
+        <f aca="false">in_tir&amp;" TIR x "&amp;TEXT(in_tir_cena,"#,##0")&amp;" zł, rozładunek "&amp;TEXT(in_rozl_cena,"#,##0")&amp;" zł/TIR, "&amp;e_rozl_dni&amp;" dni"</f>
+        <v>3 TIR x 4,000 zł, rozładunek 1,700 zł/TIR, 1.5 dni</v>
       </c>
       <c r="D50" s="16"/>
       <c r="E50" s="16"/>
@@ -3290,11 +3311,11 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="0" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C51" s="16" t="str">
-        <f aca="false">Obliczenia!D51&amp;" dni pracy = "&amp;Obliczenia!D48&amp;IF(e_krk," dni"," tyg.")&amp;", "&amp;TEXT(Obliczenia!D50,"0.0")&amp;" osobodni"</f>
-        <v>43 dni pracy = 9 tyg., 168.5 osobodni</v>
+        <f aca="false">in_osoby&amp;" osób, średnia stawka "&amp;TEXT(Obliczenia!D41,"#,##0")&amp;" zł/dzień"</f>
+        <v>4 osób, średnia stawka 400 zł/dzień</v>
       </c>
       <c r="D51" s="16"/>
       <c r="E51" s="16"/>
@@ -3304,11 +3325,11 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="0" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C52" s="16" t="str">
-        <f aca="false">Obliczenia!F51&amp;" dni pracy = "&amp;Obliczenia!F48&amp;IF(e_krk," dni"," tyg.")&amp;", "&amp;TEXT(Obliczenia!F50,"0.0")&amp;" osobodni"</f>
-        <v>49 dni pracy = 10 tyg., 194.6 osobodni</v>
+        <f aca="false">e_dzw_dni&amp;" dni"</f>
+        <v>3 dni</v>
       </c>
       <c r="D52" s="16"/>
       <c r="E52" s="16"/>
@@ -3318,11 +3339,11 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="0" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C53" s="16" t="str">
-        <f aca="false">TEXT(in_zysk,"0.0%")&amp;" / "&amp;TEXT(in_zysk_min,"0.0%")</f>
-        <v>12.5% / 10.0%</v>
+        <f aca="false">Obliczenia!D51&amp;" dni pracy = "&amp;Obliczenia!D48&amp;IF(e_krk," dni"," tyg.")&amp;", "&amp;TEXT(Obliczenia!D50,"0.0")&amp;" osobodni"</f>
+        <v>43 dni pracy = 9 tyg., 168.5 osobodni</v>
       </c>
       <c r="D53" s="16"/>
       <c r="E53" s="16"/>
@@ -3332,11 +3353,11 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="0" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C54" s="16" t="str">
-        <f aca="false">TEXT(in_q2500,"0.0%")</f>
-        <v>6.0%</v>
+        <f aca="false">Obliczenia!F51&amp;" dni pracy = "&amp;Obliczenia!F48&amp;IF(e_krk," dni"," tyg.")&amp;", "&amp;TEXT(Obliczenia!F50,"0.0")&amp;" osobodni"</f>
+        <v>49 dni pracy = 10 tyg., 194.6 osobodni</v>
       </c>
       <c r="D54" s="16"/>
       <c r="E54" s="16"/>
@@ -3346,11 +3367,11 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="0" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="C55" s="16" t="str">
-        <f aca="false">in_wzor</f>
-        <v>Stary (poprawiony)</v>
+        <f aca="false">TEXT(in_zysk,"0.0%")&amp;" / "&amp;TEXT(in_zysk2,"0.0%")</f>
+        <v>12.5% / 10.0%</v>
       </c>
       <c r="D55" s="16"/>
       <c r="E55" s="16"/>
@@ -3360,11 +3381,11 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="0" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C56" s="16" t="str">
-        <f aca="false">TEXT(c_konserw*m_MP*12,"#,##0")&amp;" / "&amp;TEXT(c_konserw2*m_MP*12,"#,##0")&amp;" / "&amp;TEXT(c_konserw3*m_MP*12,"#,##0")&amp;" zł"</f>
-        <v>28,800 / 32,400 / 36,000 zł</v>
+        <f aca="false">TEXT(in_q2500,"0.0%")</f>
+        <v>6.0%</v>
       </c>
       <c r="D56" s="16"/>
       <c r="E56" s="16"/>
@@ -3374,11 +3395,11 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="0" t="s">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="C57" s="16" t="str">
-        <f aca="false">in_opis&amp;""</f>
-        <v>H-195/202 | L-530-544-584 | P-380 | Hpoj. G-180. D-180 | 1A4+1A5+1A6 | Bok-30 Tył-5 | mgstrl-4</v>
+        <f aca="false">in_wzor</f>
+        <v>Stary (poprawiony)</v>
       </c>
       <c r="D57" s="16"/>
       <c r="E57" s="16"/>
@@ -3386,51 +3407,57 @@
       <c r="G57" s="16"/>
       <c r="H57" s="16"/>
     </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="C58" s="16" t="str">
+        <f aca="false">TEXT(c_konserw*m_MP*12,"#,##0")&amp;" / "&amp;TEXT(c_konserw2*m_MP*12,"#,##0")&amp;" / "&amp;TEXT(c_konserw3*m_MP*12,"#,##0")&amp;" zł"</f>
+        <v>28,800 / 32,400 / 36,000 zł</v>
+      </c>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
+    </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" s="16" t="str">
+        <f aca="false">in_opis&amp;""</f>
+        <v>H-195/202 | L-530-544-584 | P-380 | Hpoj. G-180. D-180 | 1A4+1A5+1A6 | Bok-30 Tył-5 | mgstrl-4</v>
+      </c>
+      <c r="D59" s="16"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="16"/>
+      <c r="H59" s="16"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C59" s="0" t="str">
+      <c r="C61" s="0" t="str">
         <f aca="false">IF(COUNTIF(Dane!B63:B68,"ok")=6,"wszystko ok","sprawdź arkusz Dane")</f>
         <v>wszystko ok</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="4" t="s">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-    </row>
-    <row r="62" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B62" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="C62" s="24"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="24"/>
-    </row>
-    <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B63" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="24"/>
-      <c r="H63" s="24"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
     </row>
     <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="24" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C64" s="24"/>
       <c r="D64" s="24"/>
@@ -3441,7 +3468,7 @@
     </row>
     <row r="65" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="24" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C65" s="24"/>
       <c r="D65" s="24"/>
@@ -3452,7 +3479,7 @@
     </row>
     <row r="66" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="24" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C66" s="24"/>
       <c r="D66" s="24"/>
@@ -3461,10 +3488,30 @@
       <c r="G66" s="24"/>
       <c r="H66" s="24"/>
     </row>
+    <row r="67" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B67" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" s="24"/>
+      <c r="D67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="24"/>
+    </row>
+    <row r="68" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B68" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="C68" s="24"/>
+      <c r="D68" s="24"/>
+      <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+    </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C41:H41"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C43:H43"/>
     <mergeCell ref="C44:H44"/>
@@ -3481,20 +3528,22 @@
     <mergeCell ref="C55:H55"/>
     <mergeCell ref="C56:H56"/>
     <mergeCell ref="C57:H57"/>
-    <mergeCell ref="B62:H62"/>
-    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="C58:H58"/>
+    <mergeCell ref="C59:H59"/>
     <mergeCell ref="B64:H64"/>
     <mergeCell ref="B65:H65"/>
     <mergeCell ref="B66:H66"/>
+    <mergeCell ref="B67:H67"/>
+    <mergeCell ref="B68:H68"/>
   </mergeCells>
-  <conditionalFormatting sqref="C32:H32">
+  <conditionalFormatting sqref="C34:H34">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>C32=MIN($C$32:$H$32)</formula>
+      <formula>C34=MIN($C$34:$H$34)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C59">
+  <conditionalFormatting sqref="C61">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>C59&lt;&gt;"wszystko ok"</formula>
+      <formula>C61&lt;&gt;"wszystko ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3512,7 +3561,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:F114"/>
+  <dimension ref="B2:F113"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -3988,8 +4037,8 @@
       <c r="B47" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="C47" s="13" t="n">
-        <v>2000</v>
+      <c r="C47" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>214</v>
@@ -4000,48 +4049,48 @@
         <v>215</v>
       </c>
       <c r="C48" s="9" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="C49" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>216</v>
-      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C50" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E50" s="8" t="s">
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="0" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="4" t="s">
+      <c r="C51" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E51" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="0" t="s">
         <v>221</v>
       </c>
       <c r="C52" s="9" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>222</v>
@@ -4052,7 +4101,7 @@
         <v>223</v>
       </c>
       <c r="C53" s="9" t="n">
-        <v>20</v>
+        <v>650</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>224</v>
@@ -4063,7 +4112,7 @@
         <v>225</v>
       </c>
       <c r="C54" s="9" t="n">
-        <v>650</v>
+        <v>12</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>226</v>
@@ -4073,22 +4122,22 @@
       <c r="B55" s="0" t="s">
         <v>227</v>
       </c>
-      <c r="C55" s="9" t="n">
-        <v>12</v>
+      <c r="C55" s="26" t="n">
+        <v>9.4</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="8" t="s">
         <v>229</v>
-      </c>
-      <c r="C56" s="26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4096,37 +4145,37 @@
         <v>230</v>
       </c>
       <c r="C57" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C58" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E58" s="8" t="s">
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="0" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="4" t="s">
+      <c r="C59" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="E59" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="0" t="s">
         <v>235</v>
       </c>
       <c r="C60" s="13" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>236</v>
@@ -4137,7 +4186,7 @@
         <v>237</v>
       </c>
       <c r="C61" s="13" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>238</v>
@@ -4148,7 +4197,7 @@
         <v>239</v>
       </c>
       <c r="C62" s="13" t="n">
-        <v>350</v>
+        <v>45</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>240</v>
@@ -4159,37 +4208,37 @@
         <v>241</v>
       </c>
       <c r="C63" s="13" t="n">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="0" t="s">
+      <c r="B64" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C64" s="13" t="n">
-        <v>130</v>
-      </c>
-      <c r="E64" s="8" t="s">
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="0" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="4" t="s">
+      <c r="C65" s="14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E65" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="0" t="s">
         <v>246</v>
       </c>
       <c r="C66" s="14" t="n">
-        <v>0.005</v>
+        <v>0.025</v>
       </c>
       <c r="E66" s="8" t="s">
         <v>247</v>
@@ -4200,37 +4249,37 @@
         <v>248</v>
       </c>
       <c r="C67" s="14" t="n">
-        <v>0.025</v>
+        <v>0.14</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C68" s="14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E68" s="8" t="s">
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="0" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="4" t="s">
+      <c r="C69" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E69" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="0" t="s">
         <v>253</v>
       </c>
       <c r="C70" s="13" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>254</v>
@@ -4241,48 +4290,48 @@
         <v>255</v>
       </c>
       <c r="C71" s="13" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="0" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C72" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E72" s="8" t="s">
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="11" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="4" t="s">
+      <c r="C74" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
+      <c r="D74" s="11" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="D75" s="11" t="s">
-        <v>262</v>
+      <c r="B75" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="C75" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="28" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="0" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C76" s="27" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D76" s="28" t="n">
         <v>2000</v>
@@ -4290,10 +4339,10 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="0" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C77" s="27" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="D77" s="28" t="n">
         <v>2000</v>
@@ -4301,10 +4350,10 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="0" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C78" s="27" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="D78" s="28" t="n">
         <v>2000</v>
@@ -4312,10 +4361,10 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="0" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C79" s="27" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="D79" s="28" t="n">
         <v>2000</v>
@@ -4323,10 +4372,10 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="0" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C80" s="27" t="n">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="D80" s="28" t="n">
         <v>2000</v>
@@ -4334,21 +4383,21 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="0" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C81" s="27" t="n">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="D81" s="28" t="n">
-        <v>2000</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="0" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C82" s="27" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="D82" s="28" t="n">
         <v>2250</v>
@@ -4356,49 +4405,55 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="0" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C83" s="27" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="D83" s="28" t="n">
         <v>2250</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="0" t="n">
-        <v>225</v>
-      </c>
-      <c r="C84" s="27" t="n">
-        <v>850</v>
-      </c>
-      <c r="D84" s="28" t="n">
-        <v>2250</v>
-      </c>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="5"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="C86" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="C86" s="5"/>
-      <c r="D86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
+      <c r="D86" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="E86" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="D87" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="E87" s="11" t="s">
+      <c r="B87" s="0" t="s">
         <v>267</v>
       </c>
-      <c r="F87" s="11" t="s">
+      <c r="C87" s="29" t="n">
+        <v>45</v>
+      </c>
+      <c r="D87" s="28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E87" s="28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F87" s="30" t="s">
         <v>268</v>
       </c>
     </row>
@@ -4407,41 +4462,41 @@
         <v>269</v>
       </c>
       <c r="C88" s="29" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D88" s="28" t="n">
-        <v>9.6</v>
+        <v>4</v>
       </c>
       <c r="E88" s="28" t="n">
-        <v>9.6</v>
+        <v>4</v>
       </c>
       <c r="F88" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="0" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C89" s="29" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D89" s="28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E89" s="28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F89" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="0" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C90" s="29" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="D90" s="28" t="n">
         <v>2</v>
@@ -4450,15 +4505,15 @@
         <v>2</v>
       </c>
       <c r="F90" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="0" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C91" s="29" t="n">
-        <v>90</v>
+        <v>207.28</v>
       </c>
       <c r="D91" s="28" t="n">
         <v>2</v>
@@ -4467,15 +4522,15 @@
         <v>2</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="0" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C92" s="29" t="n">
-        <v>207.28</v>
+        <v>40.14</v>
       </c>
       <c r="D92" s="28" t="n">
         <v>2</v>
@@ -4484,15 +4539,15 @@
         <v>2</v>
       </c>
       <c r="F92" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="0" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C93" s="29" t="n">
-        <v>40.14</v>
+        <v>3.3</v>
       </c>
       <c r="D93" s="28" t="n">
         <v>2</v>
@@ -4501,15 +4556,15 @@
         <v>2</v>
       </c>
       <c r="F93" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="0" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C94" s="29" t="n">
-        <v>3.3</v>
+        <v>10.8</v>
       </c>
       <c r="D94" s="28" t="n">
         <v>2</v>
@@ -4518,15 +4573,15 @@
         <v>2</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="0" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C95" s="29" t="n">
-        <v>10.8</v>
+        <v>10.95</v>
       </c>
       <c r="D95" s="28" t="n">
         <v>2</v>
@@ -4535,15 +4590,15 @@
         <v>2</v>
       </c>
       <c r="F95" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="0" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C96" s="29" t="n">
-        <v>10.95</v>
+        <v>3.81</v>
       </c>
       <c r="D96" s="28" t="n">
         <v>2</v>
@@ -4552,32 +4607,32 @@
         <v>2</v>
       </c>
       <c r="F96" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="0" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C97" s="29" t="n">
-        <v>3.81</v>
+        <v>2.84</v>
       </c>
       <c r="D97" s="28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E97" s="28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F97" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="0" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C98" s="29" t="n">
-        <v>2.84</v>
+        <v>4.4</v>
       </c>
       <c r="D98" s="28" t="n">
         <v>4</v>
@@ -4586,119 +4641,119 @@
         <v>4</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="0" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C99" s="29" t="n">
-        <v>4.4</v>
+        <f aca="false">2*25.71+2*22.85</f>
+        <v>97.12</v>
       </c>
       <c r="D99" s="28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E99" s="28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="0" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C100" s="29" t="n">
-        <f aca="false">2*25.71+2*22.85</f>
-        <v>97.12</v>
+        <v>345</v>
       </c>
       <c r="D100" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E100" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="0" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C101" s="29" t="n">
-        <v>345</v>
+        <v>546</v>
       </c>
       <c r="D101" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="E101" s="28" t="n">
-        <v>0</v>
-      </c>
       <c r="F101" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="0" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C102" s="29" t="n">
-        <v>546</v>
+        <v>2.98</v>
       </c>
       <c r="D102" s="28" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E102" s="28" t="n">
-        <v>1</v>
+        <v>208</v>
       </c>
       <c r="F102" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="0" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C103" s="29" t="n">
-        <v>2.98</v>
+        <f aca="false">3.09+4.99</f>
+        <v>8.08</v>
       </c>
       <c r="D103" s="28" t="n">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="E103" s="28" t="n">
-        <v>208</v>
+        <v>20</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="0" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C104" s="29" t="n">
-        <f aca="false">3.09+4.99</f>
-        <v>8.08</v>
+        <v>5.4</v>
       </c>
       <c r="D104" s="28" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E104" s="28" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F104" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="0" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C105" s="29" t="n">
-        <v>5.4</v>
+        <v>300</v>
       </c>
       <c r="D105" s="28" t="n">
         <v>1</v>
@@ -4707,15 +4762,15 @@
         <v>1</v>
       </c>
       <c r="F105" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="0" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C106" s="29" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="D106" s="28" t="n">
         <v>1</v>
@@ -4724,38 +4779,38 @@
         <v>1</v>
       </c>
       <c r="F106" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="0" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C107" s="29" t="n">
-        <v>40</v>
+        <v>172</v>
       </c>
       <c r="D107" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E107" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" s="30" t="s">
-        <v>270</v>
+        <v>160</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="0" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C108" s="29" t="n">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="D108" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="28" t="n">
         <v>1</v>
-      </c>
-      <c r="E108" s="28" t="n">
-        <v>0</v>
       </c>
       <c r="F108" s="30" t="s">
         <v>160</v>
@@ -4763,13 +4818,14 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="0" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C109" s="29" t="n">
-        <v>207</v>
+        <f aca="false">120+55+65</f>
+        <v>240</v>
       </c>
       <c r="D109" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" s="28" t="n">
         <v>1</v>
@@ -4780,11 +4836,11 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B110" s="0" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C110" s="29" t="n">
-        <f aca="false">120+55+65</f>
-        <v>240</v>
+        <f aca="false">50+40</f>
+        <v>90</v>
       </c>
       <c r="D110" s="28" t="n">
         <v>1</v>
@@ -4793,7 +4849,7 @@
         <v>1</v>
       </c>
       <c r="F110" s="30" t="s">
-        <v>160</v>
+        <v>292</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4801,71 +4857,53 @@
         <v>293</v>
       </c>
       <c r="C111" s="29" t="n">
-        <f aca="false">50+40</f>
-        <v>90</v>
+        <f aca="false">14+9+25+5+9+30</f>
+        <v>92</v>
       </c>
       <c r="D111" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E111" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" s="30" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="0" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C112" s="29" t="n">
-        <f aca="false">14+9+25+5+9+30</f>
-        <v>92</v>
+        <f aca="false">14+18+25+7+18+30</f>
+        <v>112</v>
       </c>
       <c r="D112" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="E112" s="28" t="n">
-        <v>0</v>
-      </c>
       <c r="F112" s="30" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="0" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C113" s="29" t="n">
-        <f aca="false">14+18+25+7+18+30</f>
-        <v>112</v>
+        <f aca="false">70+14+34+32+20</f>
+        <v>170</v>
       </c>
       <c r="D113" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" s="28" t="n">
         <v>1</v>
       </c>
       <c r="F113" s="30" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="0" t="s">
-        <v>297</v>
-      </c>
-      <c r="C114" s="29" t="n">
-        <f aca="false">70+14+34+32+20</f>
-        <v>170</v>
-      </c>
-      <c r="D114" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" s="30" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -4884,7 +4922,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:N75"/>
+  <dimension ref="B2:N78"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -4896,7 +4934,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -4913,13 +4951,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C5" s="31" t="n">
         <f aca="false">c_cena_D+IF(in_typ="NK37",c_doplata_NK37,0)</f>
@@ -4928,7 +4966,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C6" s="31" t="n">
         <f aca="false">c_wsp_S*m_cena_D</f>
@@ -4937,7 +4975,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C7" s="31" t="n">
         <f aca="false">c_wsp_NP*m_cena_D</f>
@@ -4946,7 +4984,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C8" s="32" t="n">
         <f aca="false">in_D+in_NP</f>
@@ -4955,7 +4993,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C9" s="32" t="n">
         <f aca="false">in_S+in_D+in_NP</f>
@@ -4964,7 +5002,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C10" s="32" t="n">
         <f aca="false">2*in_S+2*in_NP+4*in_D</f>
@@ -4973,7 +5011,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C11" s="31" t="n">
         <f aca="false">m_cena_S*in_S+c_szer_260*in_szer1_S+c_szer_270*in_szer2_S+SUMPRODUCT(in_gl_S,t_gl_doplata)+c_dl_500*in_dl500_S+CEILING(m_cena_S*c_dl_wsp*10,100)*in_dl540_S+CEILING(m_cena_S*c_dl_wsp*20,100)*in_dl550_S</f>
@@ -4982,7 +5020,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C12" s="31" t="n">
         <f aca="false">m_cena_D*in_D+c_szer_520*in_szer1_D+c_szer_540*in_szer2_D+SUMPRODUCT(in_gl_D,t_gl_doplata)+c_dl_500*in_dl500_D+m_cena_D*c_dl_wsp*10*in_dl540_D+m_cena_D*c_dl_wsp*20*in_dl550_D</f>
@@ -4991,7 +5029,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C13" s="31" t="n">
         <f aca="false">m_cena_NP*in_NP</f>
@@ -5000,7 +5038,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C14" s="32" t="n">
         <f aca="false">SUMPRODUCT((t_gl_silownik=2000)*(in_gl_S+in_gl_D))</f>
@@ -5009,7 +5047,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C15" s="32" t="n">
         <f aca="false">SUMPRODUCT((t_gl_silownik=2250)*(in_gl_S+in_gl_D))</f>
@@ -5018,7 +5056,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C16" s="32" t="n">
         <f aca="false">m_platformy-m_sil_2000-m_sil_2250</f>
@@ -5036,7 +5074,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C18" s="31" t="n">
         <f aca="false">in_barierki*c_barierka+in_maskownice*c_maskownica</f>
@@ -5045,7 +5083,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C19" s="31" t="n">
         <f aca="false">in_agregaty*c_skrzynka_zasil+SUMPRODUCT((t_sk_grupa="Elektryka")*t_sk_cena*(t_sk_S*in_S+t_sk_D*m_DN))</f>
@@ -5054,7 +5092,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C20" s="31" t="n">
         <f aca="false">in_agregaty*c_admin+SUMPRODUCT((t_sk_grupa="Mechanika")*t_sk_cena*(t_sk_S*in_S+t_sk_D*m_DN))</f>
@@ -5063,7 +5101,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="11" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C21" s="33" t="n">
         <f aca="false">m_plat_S+m_plat_D+m_plat_NP+m_hydraulika+m_barierki+m_elektryka+m_mechanika</f>
@@ -5072,7 +5110,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="11" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C22" s="33" t="n">
         <f aca="false">m_suma_2000*(1+in_q2500)</f>
@@ -5081,7 +5119,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C23" s="31" t="n">
         <f aca="false">c_mal_S*in_S+c_mal_D*m_DN+c_mal_bar*in_barierki</f>
@@ -5090,7 +5128,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C24" s="34" t="n">
         <f aca="false">ROUNDUP(in_magistrala*c_osd_magistrala+(in_barierki+in_maskownice)*c_osd_barierka,0)</f>
@@ -5099,7 +5137,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C25" s="34" t="n">
         <f aca="false">m_utr_auto+in_utr_dod</f>
@@ -5108,13 +5146,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C28" s="35" t="b">
         <f aca="false">in_lok="Kraków"</f>
@@ -5123,7 +5161,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C29" s="34" t="n">
         <f aca="false">IF(ISBLANK(in_km_pom),IF(e_krk,c_km_krakow,in_km),in_km_pom)</f>
@@ -5132,7 +5170,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C30" s="34" t="n">
         <f aca="false">IF(ISBLANK(in_km_mon),IF(e_krk,c_km_krakow,in_km+c_km_dodatek),in_km_mon)</f>
@@ -5141,7 +5179,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="0" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C31" s="34" t="n">
         <f aca="false">IF(ISBLANK(in_rozl_dni),c_rozl_TIR*in_tir,in_rozl_dni)</f>
@@ -5150,7 +5188,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="0" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C32" s="34" t="n">
         <f aca="false">(c_pomiary_osoby+c_odbiory_osoby)*IF(in_wzor="Uproszczony",2*e_km_pom/c_km_dzien*1,(1+0.1*MAX(0,800-e_km_pom)/100)*e_km_pom*1/500)</f>
@@ -5159,7 +5197,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="0" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">ROUNDUP(m_DN/c_dzwig_D+in_S*c_dzwig_wspS/c_dzwig_D,0)</f>
@@ -5168,7 +5206,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C34" s="36" t="n">
         <f aca="false">(1+c_podatek*(c_gdw+in_zysk))/(1-(c_kob+c_gdw+in_zysk))</f>
@@ -5177,7 +5215,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -5186,7 +5224,7 @@
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
@@ -5196,7 +5234,7 @@
     </row>
     <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="11" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D37" s="37" t="s">
         <v>73</v>
@@ -5231,7 +5269,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D38" s="32" t="n">
         <v>0</v>
@@ -5272,7 +5310,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="0" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D39" s="32" t="n">
         <v>0</v>
@@ -5352,7 +5390,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="0" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D41" s="31" t="n">
         <f aca="false">(c_stawka_1+IF(D40&gt;=2,c_stawka_2,0)+MAX(0,D40-2)*c_stawka_n)/D40</f>
@@ -5397,7 +5435,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="0" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D42" s="34" t="n">
         <f aca="false">c_osd_S*in_S+c_osd_D*in_D+c_osd_NP*in_NP+m_utr+D39*c_slupek_rbd*m_MP</f>
@@ -5442,7 +5480,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="0" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D43" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*1,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*1/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*1,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*1/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5487,7 +5525,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="0" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D44" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D43,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D43/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D43,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D43/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5532,7 +5570,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="0" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D45" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D44,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D44/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D44,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D44/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5577,7 +5615,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="0" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D46" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D45,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D45/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D45,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D45/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5622,7 +5660,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="0" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D47" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D46,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D46/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D46,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D46/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5667,7 +5705,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="11" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D48" s="38" t="n">
         <f aca="false">IF(ISBLANK(in_wyjazdy),D47,in_wyjazdy)</f>
@@ -5712,7 +5750,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="0" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D49" s="34" t="n">
         <f aca="false">(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D48,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D48/500)))</f>
@@ -5802,7 +5840,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="11" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D51" s="38" t="n">
         <f aca="false">CEILING(D50/D40,1)</f>
@@ -5846,1083 +5884,1218 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="0" t="s">
-        <v>342</v>
-      </c>
-      <c r="D52" s="34" t="n">
+      <c r="B52" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="D52" s="38" t="n">
+        <f aca="false">IF(e_krk,CEILING(D51/c_dni_tydzien,1),D48)</f>
+        <v>9</v>
+      </c>
+      <c r="E52" s="38" t="n">
+        <f aca="false">IF(e_krk,CEILING(E51/c_dni_tydzien,1),E48)</f>
+        <v>9</v>
+      </c>
+      <c r="F52" s="38" t="n">
+        <f aca="false">IF(e_krk,CEILING(F51/c_dni_tydzien,1),F48)</f>
+        <v>10</v>
+      </c>
+      <c r="G52" s="38" t="n">
+        <f aca="false">IF(e_krk,CEILING(G51/c_dni_tydzien,1),G48)</f>
+        <v>10</v>
+      </c>
+      <c r="I52" s="38" t="n">
+        <f aca="false">IF(e_krk,CEILING(I51/c_dni_tydzien,1),I48)</f>
+        <v>17</v>
+      </c>
+      <c r="J52" s="38" t="n">
+        <f aca="false">IF(e_krk,CEILING(J51/c_dni_tydzien,1),J48)</f>
+        <v>11</v>
+      </c>
+      <c r="K52" s="38" t="n">
+        <f aca="false">IF(e_krk,CEILING(K51/c_dni_tydzien,1),K48)</f>
+        <v>9</v>
+      </c>
+      <c r="L52" s="38" t="n">
+        <f aca="false">IF(e_krk,CEILING(L51/c_dni_tydzien,1),L48)</f>
+        <v>7</v>
+      </c>
+      <c r="M52" s="38" t="n">
+        <f aca="false">IF(e_krk,CEILING(M51/c_dni_tydzien,1),M48)</f>
+        <v>6</v>
+      </c>
+      <c r="N52" s="38" t="n">
+        <f aca="false">IF(e_krk,CEILING(N51/c_dni_tydzien,1),N48)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="0" t="s">
+        <v>341</v>
+      </c>
+      <c r="D53" s="34" t="n">
         <f aca="false">2*(e_km_mon*D48+2*e_km_pom)</f>
         <v>7060</v>
       </c>
-      <c r="E52" s="34" t="n">
+      <c r="E53" s="34" t="n">
         <f aca="false">2*(e_km_mon*E48+2*e_km_pom)</f>
         <v>7060</v>
       </c>
-      <c r="F52" s="34" t="n">
+      <c r="F53" s="34" t="n">
         <f aca="false">2*(e_km_mon*F48+2*e_km_pom)</f>
         <v>7720</v>
       </c>
-      <c r="G52" s="34" t="n">
+      <c r="G53" s="34" t="n">
         <f aca="false">2*(e_km_mon*G48+2*e_km_pom)</f>
         <v>7720</v>
       </c>
-      <c r="I52" s="34" t="n">
+      <c r="I53" s="34" t="n">
         <f aca="false">2*(e_km_mon*I48+2*e_km_pom)</f>
         <v>12340</v>
       </c>
-      <c r="J52" s="34" t="n">
+      <c r="J53" s="34" t="n">
         <f aca="false">2*(e_km_mon*J48+2*e_km_pom)</f>
         <v>8380</v>
       </c>
-      <c r="K52" s="34" t="n">
+      <c r="K53" s="34" t="n">
         <f aca="false">2*(e_km_mon*K48+2*e_km_pom)</f>
         <v>7060</v>
       </c>
-      <c r="L52" s="34" t="n">
+      <c r="L53" s="34" t="n">
         <f aca="false">2*(e_km_mon*L48+2*e_km_pom)</f>
         <v>5740</v>
       </c>
-      <c r="M52" s="34" t="n">
+      <c r="M53" s="34" t="n">
         <f aca="false">2*(e_km_mon*M48+2*e_km_pom)</f>
         <v>5080</v>
       </c>
-      <c r="N52" s="34" t="n">
+      <c r="N53" s="34" t="n">
         <f aca="false">2*(e_km_mon*N48+2*e_km_pom)</f>
         <v>4420</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="0" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="D53" s="31" t="n">
+      <c r="D54" s="31" t="n">
         <f aca="false">IF(D38=1,m_suma_2500,m_suma_2000)</f>
         <v>649059.6</v>
       </c>
-      <c r="E53" s="31" t="n">
+      <c r="E54" s="31" t="n">
         <f aca="false">IF(E38=1,m_suma_2500,m_suma_2000)</f>
         <v>688003.176</v>
       </c>
-      <c r="F53" s="31" t="n">
+      <c r="F54" s="31" t="n">
         <f aca="false">IF(F38=1,m_suma_2500,m_suma_2000)</f>
         <v>649059.6</v>
       </c>
-      <c r="G53" s="31" t="n">
+      <c r="G54" s="31" t="n">
         <f aca="false">IF(G38=1,m_suma_2500,m_suma_2000)</f>
         <v>688003.176</v>
       </c>
-      <c r="I53" s="31" t="n">
+      <c r="I54" s="31" t="n">
         <f aca="false">IF(I38=1,m_suma_2500,m_suma_2000)</f>
         <v>649059.6</v>
       </c>
-      <c r="J53" s="31" t="n">
+      <c r="J54" s="31" t="n">
         <f aca="false">IF(J38=1,m_suma_2500,m_suma_2000)</f>
         <v>649059.6</v>
       </c>
-      <c r="K53" s="31" t="n">
+      <c r="K54" s="31" t="n">
         <f aca="false">IF(K38=1,m_suma_2500,m_suma_2000)</f>
         <v>649059.6</v>
       </c>
-      <c r="L53" s="31" t="n">
+      <c r="L54" s="31" t="n">
         <f aca="false">IF(L38=1,m_suma_2500,m_suma_2000)</f>
         <v>649059.6</v>
       </c>
-      <c r="M53" s="31" t="n">
+      <c r="M54" s="31" t="n">
         <f aca="false">IF(M38=1,m_suma_2500,m_suma_2000)</f>
         <v>649059.6</v>
       </c>
-      <c r="N53" s="31" t="n">
+      <c r="N54" s="31" t="n">
         <f aca="false">IF(N38=1,m_suma_2500,m_suma_2000)</f>
         <v>649059.6</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="0" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="0" t="s">
         <v>87</v>
       </c>
-      <c r="D54" s="31" t="n">
+      <c r="D55" s="31" t="n">
         <f aca="false">D39*c_slupek*m_MP</f>
         <v>0</v>
       </c>
-      <c r="E54" s="31" t="n">
+      <c r="E55" s="31" t="n">
         <f aca="false">E39*c_slupek*m_MP</f>
         <v>0</v>
       </c>
-      <c r="F54" s="31" t="n">
+      <c r="F55" s="31" t="n">
         <f aca="false">F39*c_slupek*m_MP</f>
         <v>102000</v>
       </c>
-      <c r="G54" s="31" t="n">
+      <c r="G55" s="31" t="n">
         <f aca="false">G39*c_slupek*m_MP</f>
         <v>102000</v>
       </c>
-      <c r="I54" s="31" t="n">
+      <c r="I55" s="31" t="n">
         <f aca="false">I39*c_slupek*m_MP</f>
         <v>0</v>
       </c>
-      <c r="J54" s="31" t="n">
+      <c r="J55" s="31" t="n">
         <f aca="false">J39*c_slupek*m_MP</f>
         <v>0</v>
       </c>
-      <c r="K54" s="31" t="n">
+      <c r="K55" s="31" t="n">
         <f aca="false">K39*c_slupek*m_MP</f>
         <v>0</v>
       </c>
-      <c r="L54" s="31" t="n">
+      <c r="L55" s="31" t="n">
         <f aca="false">L39*c_slupek*m_MP</f>
         <v>0</v>
       </c>
-      <c r="M54" s="31" t="n">
+      <c r="M55" s="31" t="n">
         <f aca="false">M39*c_slupek*m_MP</f>
         <v>0</v>
       </c>
-      <c r="N54" s="31" t="n">
+      <c r="N55" s="31" t="n">
         <f aca="false">N39*c_slupek*m_MP</f>
         <v>0</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="0" t="s">
-        <v>343</v>
-      </c>
-      <c r="D55" s="31" t="n">
-        <f aca="false">D52/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
-        <v>7977.8</v>
-      </c>
-      <c r="E55" s="31" t="n">
-        <f aca="false">E52/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
-        <v>7977.8</v>
-      </c>
-      <c r="F55" s="31" t="n">
-        <f aca="false">F52/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
-        <v>8723.6</v>
-      </c>
-      <c r="G55" s="31" t="n">
-        <f aca="false">G52/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
-        <v>8723.6</v>
-      </c>
-      <c r="I55" s="31" t="n">
-        <f aca="false">I52/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
-        <v>13944.2</v>
-      </c>
-      <c r="J55" s="31" t="n">
-        <f aca="false">J52/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
-        <v>9469.4</v>
-      </c>
-      <c r="K55" s="31" t="n">
-        <f aca="false">K52/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
-        <v>7977.8</v>
-      </c>
-      <c r="L55" s="31" t="n">
-        <f aca="false">L52/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
-        <v>6486.2</v>
-      </c>
-      <c r="M55" s="31" t="n">
-        <f aca="false">M52/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
-        <v>5740.4</v>
-      </c>
-      <c r="N55" s="31" t="n">
-        <f aca="false">N52/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
-        <v>4994.6</v>
-      </c>
-    </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="0" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D56" s="31" t="n">
+        <f aca="false">D53/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
+        <v>7977.8</v>
+      </c>
+      <c r="E56" s="31" t="n">
+        <f aca="false">E53/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
+        <v>7977.8</v>
+      </c>
+      <c r="F56" s="31" t="n">
+        <f aca="false">F53/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
+        <v>8723.6</v>
+      </c>
+      <c r="G56" s="31" t="n">
+        <f aca="false">G53/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
+        <v>8723.6</v>
+      </c>
+      <c r="I56" s="31" t="n">
+        <f aca="false">I53/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
+        <v>13944.2</v>
+      </c>
+      <c r="J56" s="31" t="n">
+        <f aca="false">J53/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
+        <v>9469.4</v>
+      </c>
+      <c r="K56" s="31" t="n">
+        <f aca="false">K53/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
+        <v>7977.8</v>
+      </c>
+      <c r="L56" s="31" t="n">
+        <f aca="false">L53/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
+        <v>6486.2</v>
+      </c>
+      <c r="M56" s="31" t="n">
+        <f aca="false">M53/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
+        <v>5740.4</v>
+      </c>
+      <c r="N56" s="31" t="n">
+        <f aca="false">N53/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
+        <v>4994.6</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="0" t="s">
+        <v>343</v>
+      </c>
+      <c r="D57" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_hotel*(D51+1)*D40)</f>
         <v>22880</v>
       </c>
-      <c r="E56" s="31" t="n">
+      <c r="E57" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_hotel*(E51+1)*E40)</f>
         <v>22880</v>
       </c>
-      <c r="F56" s="31" t="n">
+      <c r="F57" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_hotel*(F51+1)*F40)</f>
         <v>26000</v>
       </c>
-      <c r="G56" s="31" t="n">
+      <c r="G57" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_hotel*(G51+1)*G40)</f>
         <v>26000</v>
       </c>
-      <c r="I56" s="31" t="n">
+      <c r="I57" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_hotel*(I51+1)*I40)</f>
         <v>21580</v>
       </c>
-      <c r="J56" s="31" t="n">
+      <c r="J57" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_hotel*(J51+1)*J40)</f>
         <v>21840</v>
       </c>
-      <c r="K56" s="31" t="n">
+      <c r="K57" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_hotel*(K51+1)*K40)</f>
         <v>22880</v>
       </c>
-      <c r="L56" s="31" t="n">
+      <c r="L57" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_hotel*(L51+1)*L40)</f>
         <v>22750</v>
       </c>
-      <c r="M56" s="31" t="n">
+      <c r="M57" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_hotel*(M51+1)*M40)</f>
         <v>23400</v>
       </c>
-      <c r="N56" s="31" t="n">
+      <c r="N57" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_hotel*(N51+1)*N40)</f>
         <v>23660</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="0" t="s">
-        <v>345</v>
-      </c>
-      <c r="D57" s="31" t="n">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="0" t="s">
+        <v>344</v>
+      </c>
+      <c r="D58" s="31" t="n">
         <f aca="false">in_tir_cena*in_tir</f>
         <v>12000</v>
       </c>
-      <c r="E57" s="31" t="n">
+      <c r="E58" s="31" t="n">
         <f aca="false">in_tir_cena*in_tir</f>
         <v>12000</v>
       </c>
-      <c r="F57" s="31" t="n">
+      <c r="F58" s="31" t="n">
         <f aca="false">in_tir_cena*in_tir</f>
         <v>12000</v>
       </c>
-      <c r="G57" s="31" t="n">
+      <c r="G58" s="31" t="n">
         <f aca="false">in_tir_cena*in_tir</f>
         <v>12000</v>
       </c>
-      <c r="I57" s="31" t="n">
+      <c r="I58" s="31" t="n">
         <f aca="false">in_tir_cena*in_tir</f>
         <v>12000</v>
       </c>
-      <c r="J57" s="31" t="n">
+      <c r="J58" s="31" t="n">
         <f aca="false">in_tir_cena*in_tir</f>
         <v>12000</v>
       </c>
-      <c r="K57" s="31" t="n">
+      <c r="K58" s="31" t="n">
         <f aca="false">in_tir_cena*in_tir</f>
         <v>12000</v>
       </c>
-      <c r="L57" s="31" t="n">
+      <c r="L58" s="31" t="n">
         <f aca="false">in_tir_cena*in_tir</f>
         <v>12000</v>
       </c>
-      <c r="M57" s="31" t="n">
+      <c r="M58" s="31" t="n">
         <f aca="false">in_tir_cena*in_tir</f>
         <v>12000</v>
       </c>
-      <c r="N57" s="31" t="n">
+      <c r="N58" s="31" t="n">
         <f aca="false">in_tir_cena*in_tir</f>
         <v>12000</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="0" t="s">
-        <v>346</v>
-      </c>
-      <c r="D58" s="31" t="n">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="0" t="s">
+        <v>345</v>
+      </c>
+      <c r="D59" s="31" t="n">
         <f aca="false">c_dzwig*e_dzw_dni</f>
         <v>7200</v>
       </c>
-      <c r="E58" s="31" t="n">
+      <c r="E59" s="31" t="n">
         <f aca="false">c_dzwig*e_dzw_dni</f>
         <v>7200</v>
       </c>
-      <c r="F58" s="31" t="n">
+      <c r="F59" s="31" t="n">
         <f aca="false">c_dzwig*e_dzw_dni</f>
         <v>7200</v>
       </c>
-      <c r="G58" s="31" t="n">
+      <c r="G59" s="31" t="n">
         <f aca="false">c_dzwig*e_dzw_dni</f>
         <v>7200</v>
       </c>
-      <c r="I58" s="31" t="n">
+      <c r="I59" s="31" t="n">
         <f aca="false">c_dzwig*e_dzw_dni</f>
         <v>7200</v>
       </c>
-      <c r="J58" s="31" t="n">
+      <c r="J59" s="31" t="n">
         <f aca="false">c_dzwig*e_dzw_dni</f>
         <v>7200</v>
       </c>
-      <c r="K58" s="31" t="n">
+      <c r="K59" s="31" t="n">
         <f aca="false">c_dzwig*e_dzw_dni</f>
         <v>7200</v>
       </c>
-      <c r="L58" s="31" t="n">
+      <c r="L59" s="31" t="n">
         <f aca="false">c_dzwig*e_dzw_dni</f>
         <v>7200</v>
       </c>
-      <c r="M58" s="31" t="n">
+      <c r="M59" s="31" t="n">
         <f aca="false">c_dzwig*e_dzw_dni</f>
         <v>7200</v>
       </c>
-      <c r="N58" s="31" t="n">
+      <c r="N59" s="31" t="n">
         <f aca="false">c_dzwig*e_dzw_dni</f>
         <v>7200</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="0" t="s">
-        <v>347</v>
-      </c>
-      <c r="D59" s="31" t="n">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="D60" s="31" t="n">
         <f aca="false">in_rozl_cena*in_tir</f>
         <v>5100</v>
       </c>
-      <c r="E59" s="31" t="n">
+      <c r="E60" s="31" t="n">
         <f aca="false">in_rozl_cena*in_tir</f>
         <v>5100</v>
       </c>
-      <c r="F59" s="31" t="n">
+      <c r="F60" s="31" t="n">
         <f aca="false">in_rozl_cena*in_tir</f>
         <v>5100</v>
       </c>
-      <c r="G59" s="31" t="n">
+      <c r="G60" s="31" t="n">
         <f aca="false">in_rozl_cena*in_tir</f>
         <v>5100</v>
       </c>
-      <c r="I59" s="31" t="n">
+      <c r="I60" s="31" t="n">
         <f aca="false">in_rozl_cena*in_tir</f>
         <v>5100</v>
       </c>
-      <c r="J59" s="31" t="n">
+      <c r="J60" s="31" t="n">
         <f aca="false">in_rozl_cena*in_tir</f>
         <v>5100</v>
       </c>
-      <c r="K59" s="31" t="n">
+      <c r="K60" s="31" t="n">
         <f aca="false">in_rozl_cena*in_tir</f>
         <v>5100</v>
       </c>
-      <c r="L59" s="31" t="n">
+      <c r="L60" s="31" t="n">
         <f aca="false">in_rozl_cena*in_tir</f>
         <v>5100</v>
       </c>
-      <c r="M59" s="31" t="n">
+      <c r="M60" s="31" t="n">
         <f aca="false">in_rozl_cena*in_tir</f>
         <v>5100</v>
       </c>
-      <c r="N59" s="31" t="n">
+      <c r="N60" s="31" t="n">
         <f aca="false">in_rozl_cena*in_tir</f>
         <v>5100</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="0" t="s">
-        <v>348</v>
-      </c>
-      <c r="D60" s="31" t="n">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="0" t="s">
+        <v>347</v>
+      </c>
+      <c r="D61" s="31" t="n">
         <f aca="false">D41*e_rozl_dni*D40</f>
         <v>2400</v>
       </c>
-      <c r="E60" s="31" t="n">
+      <c r="E61" s="31" t="n">
         <f aca="false">E41*e_rozl_dni*E40</f>
         <v>2400</v>
       </c>
-      <c r="F60" s="31" t="n">
+      <c r="F61" s="31" t="n">
         <f aca="false">F41*e_rozl_dni*F40</f>
         <v>2400</v>
       </c>
-      <c r="G60" s="31" t="n">
+      <c r="G61" s="31" t="n">
         <f aca="false">G41*e_rozl_dni*G40</f>
         <v>2400</v>
       </c>
-      <c r="I60" s="31" t="n">
+      <c r="I61" s="31" t="n">
         <f aca="false">I41*e_rozl_dni*I40</f>
         <v>1350</v>
       </c>
-      <c r="J60" s="31" t="n">
+      <c r="J61" s="31" t="n">
         <f aca="false">J41*e_rozl_dni*J40</f>
         <v>1875</v>
       </c>
-      <c r="K60" s="31" t="n">
+      <c r="K61" s="31" t="n">
         <f aca="false">K41*e_rozl_dni*K40</f>
         <v>2400</v>
       </c>
-      <c r="L60" s="31" t="n">
+      <c r="L61" s="31" t="n">
         <f aca="false">L41*e_rozl_dni*L40</f>
         <v>2925</v>
       </c>
-      <c r="M60" s="31" t="n">
+      <c r="M61" s="31" t="n">
         <f aca="false">M41*e_rozl_dni*M40</f>
         <v>3450</v>
       </c>
-      <c r="N60" s="31" t="n">
+      <c r="N61" s="31" t="n">
         <f aca="false">N41*e_rozl_dni*N40</f>
         <v>3975</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="0" t="s">
-        <v>349</v>
-      </c>
-      <c r="D61" s="31" t="n">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="0" t="s">
+        <v>348</v>
+      </c>
+      <c r="D62" s="31" t="n">
         <f aca="false">D41*(D49-D40*e_rozl_dni)</f>
         <v>14992.32</v>
       </c>
-      <c r="E61" s="31" t="n">
+      <c r="E62" s="31" t="n">
         <f aca="false">E41*(E49-E40*e_rozl_dni)</f>
         <v>14992.32</v>
       </c>
-      <c r="F61" s="31" t="n">
+      <c r="F62" s="31" t="n">
         <f aca="false">F41*(F49-F40*e_rozl_dni)</f>
         <v>16544.64</v>
       </c>
-      <c r="G61" s="31" t="n">
+      <c r="G62" s="31" t="n">
         <f aca="false">G41*(G49-G40*e_rozl_dni)</f>
         <v>16544.64</v>
       </c>
-      <c r="I61" s="31" t="n">
+      <c r="I62" s="31" t="n">
         <f aca="false">I41*(I49-I40*e_rozl_dni)</f>
         <v>15993.18</v>
       </c>
-      <c r="J61" s="31" t="n">
+      <c r="J62" s="31" t="n">
         <f aca="false">J41*(J49-J40*e_rozl_dni)</f>
         <v>14404.25</v>
       </c>
-      <c r="K61" s="31" t="n">
+      <c r="K62" s="31" t="n">
         <f aca="false">K41*(K49-K40*e_rozl_dni)</f>
         <v>14992.32</v>
       </c>
-      <c r="L61" s="31" t="n">
+      <c r="L62" s="31" t="n">
         <f aca="false">L41*(L49-L40*e_rozl_dni)</f>
         <v>14239.134</v>
       </c>
-      <c r="M61" s="31" t="n">
+      <c r="M62" s="31" t="n">
         <f aca="false">M41*(M49-M40*e_rozl_dni)</f>
         <v>14367.64</v>
       </c>
-      <c r="N61" s="31" t="n">
+      <c r="N62" s="31" t="n">
         <f aca="false">N41*(N49-N40*e_rozl_dni)</f>
         <v>13821.87</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="0" t="s">
-        <v>350</v>
-      </c>
-      <c r="D62" s="31" t="n">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="0" t="s">
+        <v>349</v>
+      </c>
+      <c r="D63" s="31" t="n">
         <f aca="false">IF(D48&gt;0,D41*D42,0)</f>
         <v>50000</v>
       </c>
-      <c r="E62" s="31" t="n">
+      <c r="E63" s="31" t="n">
         <f aca="false">IF(E48&gt;0,E41*E42,0)</f>
         <v>50000</v>
       </c>
-      <c r="F62" s="31" t="n">
+      <c r="F63" s="31" t="n">
         <f aca="false">IF(F48&gt;0,F41*F42,0)</f>
         <v>58880</v>
       </c>
-      <c r="G62" s="31" t="n">
+      <c r="G63" s="31" t="n">
         <f aca="false">IF(G48&gt;0,G41*G42,0)</f>
         <v>58880</v>
       </c>
-      <c r="I62" s="31" t="n">
+      <c r="I63" s="31" t="n">
         <f aca="false">IF(I48&gt;0,I41*I42,0)</f>
         <v>56250</v>
       </c>
-      <c r="J62" s="31" t="n">
+      <c r="J63" s="31" t="n">
         <f aca="false">IF(J48&gt;0,J41*J42,0)</f>
         <v>52083.3333333333</v>
       </c>
-      <c r="K62" s="31" t="n">
+      <c r="K63" s="31" t="n">
         <f aca="false">IF(K48&gt;0,K41*K42,0)</f>
         <v>50000</v>
       </c>
-      <c r="L62" s="31" t="n">
+      <c r="L63" s="31" t="n">
         <f aca="false">IF(L48&gt;0,L41*L42,0)</f>
         <v>48750</v>
       </c>
-      <c r="M62" s="31" t="n">
+      <c r="M63" s="31" t="n">
         <f aca="false">IF(M48&gt;0,M41*M42,0)</f>
         <v>47916.6666666667</v>
       </c>
-      <c r="N62" s="31" t="n">
+      <c r="N63" s="31" t="n">
         <f aca="false">IF(N48&gt;0,N41*N42,0)</f>
         <v>47321.4285714286</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="0" t="s">
-        <v>351</v>
-      </c>
-      <c r="D63" s="31" t="n">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="0" t="s">
+        <v>350</v>
+      </c>
+      <c r="D64" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_dieta*D50)</f>
         <v>7581.636</v>
       </c>
-      <c r="E63" s="31" t="n">
+      <c r="E64" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_dieta*E50)</f>
         <v>7581.636</v>
       </c>
-      <c r="F63" s="31" t="n">
+      <c r="F64" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_dieta*F50)</f>
         <v>8755.272</v>
       </c>
-      <c r="G63" s="31" t="n">
+      <c r="G64" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_dieta*G50)</f>
         <v>8755.272</v>
       </c>
-      <c r="I63" s="31" t="n">
+      <c r="I64" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_dieta*I50)</f>
         <v>7359.318</v>
       </c>
-      <c r="J63" s="31" t="n">
+      <c r="J64" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_dieta*J50)</f>
         <v>7383.159</v>
       </c>
-      <c r="K63" s="31" t="n">
+      <c r="K64" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_dieta*K50)</f>
         <v>7581.636</v>
       </c>
-      <c r="L63" s="31" t="n">
+      <c r="L64" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_dieta*L50)</f>
         <v>7605.477</v>
       </c>
-      <c r="M63" s="31" t="n">
+      <c r="M64" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_dieta*M50)</f>
         <v>7716.636</v>
       </c>
-      <c r="N63" s="31" t="n">
+      <c r="N64" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_dieta*N50)</f>
         <v>7740.477</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="D64" s="33" t="n">
-        <f aca="false">SUM(D53:D63)</f>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="D65" s="33" t="n">
+        <f aca="false">SUM(D54:D64)</f>
         <v>779191.356</v>
       </c>
-      <c r="E64" s="33" t="n">
-        <f aca="false">SUM(E53:E63)</f>
+      <c r="E65" s="33" t="n">
+        <f aca="false">SUM(E54:E64)</f>
         <v>818134.932</v>
       </c>
-      <c r="F64" s="33" t="n">
-        <f aca="false">SUM(F53:F63)</f>
+      <c r="F65" s="33" t="n">
+        <f aca="false">SUM(F54:F64)</f>
         <v>896663.112</v>
       </c>
-      <c r="G64" s="33" t="n">
-        <f aca="false">SUM(G53:G63)</f>
+      <c r="G65" s="33" t="n">
+        <f aca="false">SUM(G54:G64)</f>
         <v>935606.688</v>
       </c>
-      <c r="I64" s="33" t="n">
-        <f aca="false">SUM(I53:I63)</f>
+      <c r="I65" s="33" t="n">
+        <f aca="false">SUM(I54:I64)</f>
         <v>789836.298</v>
       </c>
-      <c r="J64" s="33" t="n">
-        <f aca="false">SUM(J53:J63)</f>
+      <c r="J65" s="33" t="n">
+        <f aca="false">SUM(J54:J64)</f>
         <v>780414.742333333</v>
       </c>
-      <c r="K64" s="33" t="n">
-        <f aca="false">SUM(K53:K63)</f>
+      <c r="K65" s="33" t="n">
+        <f aca="false">SUM(K54:K64)</f>
         <v>779191.356</v>
       </c>
-      <c r="L64" s="33" t="n">
-        <f aca="false">SUM(L53:L63)</f>
+      <c r="L65" s="33" t="n">
+        <f aca="false">SUM(L54:L64)</f>
         <v>776115.411</v>
       </c>
-      <c r="M64" s="33" t="n">
-        <f aca="false">SUM(M53:M63)</f>
+      <c r="M65" s="33" t="n">
+        <f aca="false">SUM(M54:M64)</f>
         <v>775950.942666667</v>
       </c>
-      <c r="N64" s="33" t="n">
-        <f aca="false">SUM(N53:N63)</f>
+      <c r="N65" s="33" t="n">
+        <f aca="false">SUM(N54:N64)</f>
         <v>774872.975571429</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="0" t="s">
-        <v>353</v>
-      </c>
-      <c r="D65" s="31" t="n">
-        <f aca="false">D64/(1-(c_kob+c_gdw+in_zysk))</f>
-        <v>922119.947928994</v>
-      </c>
-      <c r="E65" s="31" t="n">
-        <f aca="false">E64/(1-(c_kob+c_gdw+in_zysk))</f>
-        <v>968207.020118343</v>
-      </c>
-      <c r="F65" s="31" t="n">
-        <f aca="false">F64/(1-(c_kob+c_gdw+in_zysk))</f>
-        <v>1061139.77751479</v>
-      </c>
-      <c r="G65" s="31" t="n">
-        <f aca="false">G64/(1-(c_kob+c_gdw+in_zysk))</f>
-        <v>1107226.84970414</v>
-      </c>
-      <c r="I65" s="31" t="n">
-        <f aca="false">I64/(1-(c_kob+c_gdw+in_zysk))</f>
-        <v>934717.512426036</v>
-      </c>
-      <c r="J65" s="31" t="n">
-        <f aca="false">J64/(1-(c_kob+c_gdw+in_zysk))</f>
-        <v>923567.742406312</v>
-      </c>
-      <c r="K65" s="31" t="n">
-        <f aca="false">K64/(1-(c_kob+c_gdw+in_zysk))</f>
-        <v>922119.947928994</v>
-      </c>
-      <c r="L65" s="31" t="n">
-        <f aca="false">L64/(1-(c_kob+c_gdw+in_zysk))</f>
-        <v>918479.776331361</v>
-      </c>
-      <c r="M65" s="31" t="n">
-        <f aca="false">M64/(1-(c_kob+c_gdw+in_zysk))</f>
-        <v>918285.139250493</v>
-      </c>
-      <c r="N65" s="31" t="n">
-        <f aca="false">N64/(1-(c_kob+c_gdw+in_zysk))</f>
-        <v>917009.438546069</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="0" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D66" s="31" t="n">
-        <f aca="false">D65*c_kob</f>
-        <v>4610.59973964497</v>
+        <f aca="false">D65/(1-(c_kob+c_gdw+in_zysk))</f>
+        <v>922119.947928994</v>
       </c>
       <c r="E66" s="31" t="n">
-        <f aca="false">E65*c_kob</f>
-        <v>4841.03510059172</v>
+        <f aca="false">E65/(1-(c_kob+c_gdw+in_zysk))</f>
+        <v>968207.020118343</v>
       </c>
       <c r="F66" s="31" t="n">
-        <f aca="false">F65*c_kob</f>
-        <v>5305.69888757397</v>
+        <f aca="false">F65/(1-(c_kob+c_gdw+in_zysk))</f>
+        <v>1061139.77751479</v>
       </c>
       <c r="G66" s="31" t="n">
-        <f aca="false">G65*c_kob</f>
-        <v>5536.13424852071</v>
+        <f aca="false">G65/(1-(c_kob+c_gdw+in_zysk))</f>
+        <v>1107226.84970414</v>
       </c>
       <c r="I66" s="31" t="n">
-        <f aca="false">I65*c_kob</f>
-        <v>4673.58756213018</v>
+        <f aca="false">I65/(1-(c_kob+c_gdw+in_zysk))</f>
+        <v>934717.512426036</v>
       </c>
       <c r="J66" s="31" t="n">
-        <f aca="false">J65*c_kob</f>
-        <v>4617.83871203156</v>
+        <f aca="false">J65/(1-(c_kob+c_gdw+in_zysk))</f>
+        <v>923567.742406312</v>
       </c>
       <c r="K66" s="31" t="n">
-        <f aca="false">K65*c_kob</f>
-        <v>4610.59973964497</v>
+        <f aca="false">K65/(1-(c_kob+c_gdw+in_zysk))</f>
+        <v>922119.947928994</v>
       </c>
       <c r="L66" s="31" t="n">
-        <f aca="false">L65*c_kob</f>
-        <v>4592.3988816568</v>
+        <f aca="false">L65/(1-(c_kob+c_gdw+in_zysk))</f>
+        <v>918479.776331361</v>
       </c>
       <c r="M66" s="31" t="n">
-        <f aca="false">M65*c_kob</f>
-        <v>4591.42569625247</v>
+        <f aca="false">M65/(1-(c_kob+c_gdw+in_zysk))</f>
+        <v>918285.139250493</v>
       </c>
       <c r="N66" s="31" t="n">
-        <f aca="false">N65*c_kob</f>
-        <v>4585.04719273035</v>
+        <f aca="false">N65/(1-(c_kob+c_gdw+in_zysk))</f>
+        <v>917009.438546069</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="0" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D67" s="31" t="n">
-        <f aca="false">D65*c_gdw</f>
-        <v>23052.9986982249</v>
+        <f aca="false">D66*c_kob</f>
+        <v>4610.59973964497</v>
       </c>
       <c r="E67" s="31" t="n">
-        <f aca="false">E65*c_gdw</f>
-        <v>24205.1755029586</v>
+        <f aca="false">E66*c_kob</f>
+        <v>4841.03510059172</v>
       </c>
       <c r="F67" s="31" t="n">
-        <f aca="false">F65*c_gdw</f>
-        <v>26528.4944378698</v>
+        <f aca="false">F66*c_kob</f>
+        <v>5305.69888757397</v>
       </c>
       <c r="G67" s="31" t="n">
-        <f aca="false">G65*c_gdw</f>
-        <v>27680.6712426036</v>
+        <f aca="false">G66*c_kob</f>
+        <v>5536.13424852071</v>
       </c>
       <c r="I67" s="31" t="n">
-        <f aca="false">I65*c_gdw</f>
-        <v>23367.9378106509</v>
+        <f aca="false">I66*c_kob</f>
+        <v>4673.58756213018</v>
       </c>
       <c r="J67" s="31" t="n">
-        <f aca="false">J65*c_gdw</f>
-        <v>23089.1935601578</v>
+        <f aca="false">J66*c_kob</f>
+        <v>4617.83871203156</v>
       </c>
       <c r="K67" s="31" t="n">
-        <f aca="false">K65*c_gdw</f>
-        <v>23052.9986982249</v>
+        <f aca="false">K66*c_kob</f>
+        <v>4610.59973964497</v>
       </c>
       <c r="L67" s="31" t="n">
-        <f aca="false">L65*c_gdw</f>
-        <v>22961.994408284</v>
+        <f aca="false">L66*c_kob</f>
+        <v>4592.3988816568</v>
       </c>
       <c r="M67" s="31" t="n">
-        <f aca="false">M65*c_gdw</f>
-        <v>22957.1284812623</v>
+        <f aca="false">M66*c_kob</f>
+        <v>4591.42569625247</v>
       </c>
       <c r="N67" s="31" t="n">
-        <f aca="false">N65*c_gdw</f>
-        <v>22925.2359636517</v>
+        <f aca="false">N66*c_kob</f>
+        <v>4585.04719273035</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="0" t="s">
-        <v>84</v>
+        <v>354</v>
       </c>
       <c r="D68" s="31" t="n">
-        <f aca="false">D65*in_zysk</f>
-        <v>115264.993491124</v>
+        <f aca="false">D66*c_gdw</f>
+        <v>23052.9986982249</v>
       </c>
       <c r="E68" s="31" t="n">
-        <f aca="false">E65*in_zysk</f>
-        <v>121025.877514793</v>
+        <f aca="false">E66*c_gdw</f>
+        <v>24205.1755029586</v>
       </c>
       <c r="F68" s="31" t="n">
-        <f aca="false">F65*in_zysk</f>
-        <v>132642.472189349</v>
+        <f aca="false">F66*c_gdw</f>
+        <v>26528.4944378698</v>
       </c>
       <c r="G68" s="31" t="n">
-        <f aca="false">G65*in_zysk</f>
-        <v>138403.356213018</v>
+        <f aca="false">G66*c_gdw</f>
+        <v>27680.6712426036</v>
       </c>
       <c r="I68" s="31" t="n">
-        <f aca="false">I65*in_zysk</f>
-        <v>116839.689053254</v>
+        <f aca="false">I66*c_gdw</f>
+        <v>23367.9378106509</v>
       </c>
       <c r="J68" s="31" t="n">
-        <f aca="false">J65*in_zysk</f>
-        <v>115445.967800789</v>
+        <f aca="false">J66*c_gdw</f>
+        <v>23089.1935601578</v>
       </c>
       <c r="K68" s="31" t="n">
-        <f aca="false">K65*in_zysk</f>
-        <v>115264.993491124</v>
+        <f aca="false">K66*c_gdw</f>
+        <v>23052.9986982249</v>
       </c>
       <c r="L68" s="31" t="n">
-        <f aca="false">L65*in_zysk</f>
-        <v>114809.97204142</v>
+        <f aca="false">L66*c_gdw</f>
+        <v>22961.994408284</v>
       </c>
       <c r="M68" s="31" t="n">
-        <f aca="false">M65*in_zysk</f>
-        <v>114785.642406312</v>
+        <f aca="false">M66*c_gdw</f>
+        <v>22957.1284812623</v>
       </c>
       <c r="N68" s="31" t="n">
-        <f aca="false">N65*in_zysk</f>
-        <v>114626.179818259</v>
+        <f aca="false">N66*c_gdw</f>
+        <v>22925.2359636517</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <f aca="false">D66*in_zysk</f>
+        <v>115264.993491124</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <f aca="false">E66*in_zysk</f>
+        <v>121025.877514793</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <f aca="false">F66*in_zysk</f>
+        <v>132642.472189349</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <f aca="false">G66*in_zysk</f>
+        <v>138403.356213018</v>
+      </c>
+      <c r="I69" s="31" t="n">
+        <f aca="false">I66*in_zysk</f>
+        <v>116839.689053254</v>
+      </c>
+      <c r="J69" s="31" t="n">
+        <f aca="false">J66*in_zysk</f>
+        <v>115445.967800789</v>
+      </c>
+      <c r="K69" s="31" t="n">
+        <f aca="false">K66*in_zysk</f>
+        <v>115264.993491124</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <f aca="false">L66*in_zysk</f>
+        <v>114809.97204142</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <f aca="false">M66*in_zysk</f>
+        <v>114785.642406312</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <f aca="false">N66*in_zysk</f>
+        <v>114626.179818259</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="D69" s="31" t="n">
-        <f aca="false">c_podatek*(D60+D61+D62+D63+D67+D68)</f>
+      <c r="D70" s="31" t="n">
+        <f aca="false">c_podatek*(D61+D62+D63+D64+D68+D69)</f>
         <v>29860.8727465089</v>
       </c>
-      <c r="E69" s="31" t="n">
-        <f aca="false">c_podatek*(E60+E61+E62+E63+E67+E68)</f>
+      <c r="E70" s="31" t="n">
+        <f aca="false">c_podatek*(E61+E62+E63+E64+E68+E69)</f>
         <v>30828.7012624852</v>
       </c>
-      <c r="F69" s="31" t="n">
-        <f aca="false">c_podatek*(F60+F61+F62+F63+F67+F68)</f>
+      <c r="F70" s="31" t="n">
+        <f aca="false">c_podatek*(F61+F62+F63+F64+F68+F69)</f>
         <v>34405.1230078107</v>
       </c>
-      <c r="G69" s="31" t="n">
-        <f aca="false">c_podatek*(G60+G61+G62+G63+G67+G68)</f>
+      <c r="G70" s="31" t="n">
+        <f aca="false">c_podatek*(G61+G62+G63+G64+G68+G69)</f>
         <v>35372.951523787</v>
       </c>
-      <c r="I69" s="31" t="n">
-        <f aca="false">c_podatek*(I60+I61+I62+I63+I67+I68)</f>
+      <c r="I70" s="31" t="n">
+        <f aca="false">c_podatek*(I61+I62+I63+I64+I68+I69)</f>
         <v>30962.4174809467</v>
       </c>
-      <c r="J69" s="31" t="n">
-        <f aca="false">c_podatek*(J60+J61+J62+J63+J67+J68)</f>
+      <c r="J70" s="31" t="n">
+        <f aca="false">c_podatek*(J61+J62+J63+J64+J68+J69)</f>
         <v>29999.3265171992</v>
       </c>
-      <c r="K69" s="31" t="n">
-        <f aca="false">c_podatek*(K60+K61+K62+K63+K67+K68)</f>
+      <c r="K70" s="31" t="n">
+        <f aca="false">c_podatek*(K61+K62+K63+K64+K68+K69)</f>
         <v>29860.8727465089</v>
       </c>
-      <c r="L69" s="31" t="n">
-        <f aca="false">c_podatek*(L60+L61+L62+L63+L67+L68)</f>
+      <c r="L70" s="31" t="n">
+        <f aca="false">c_podatek*(L61+L62+L63+L64+L68+L69)</f>
         <v>29580.8208429586</v>
       </c>
-      <c r="M69" s="31" t="n">
-        <f aca="false">c_podatek*(M60+M61+M62+M63+M67+M68)</f>
+      <c r="M70" s="31" t="n">
+        <f aca="false">c_podatek*(M61+M62+M63+M64+M68+M69)</f>
         <v>29567.1198975937</v>
       </c>
-      <c r="N69" s="31" t="n">
-        <f aca="false">c_podatek*(N60+N61+N62+N63+N67+N68)</f>
+      <c r="N70" s="31" t="n">
+        <f aca="false">c_podatek*(N61+N62+N63+N64+N68+N69)</f>
         <v>29457.4267894675</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="11" t="s">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="D70" s="33" t="n">
-        <f aca="false">D65+D69</f>
+      <c r="D71" s="33" t="n">
+        <f aca="false">D66+D70</f>
         <v>951980.820675503</v>
       </c>
-      <c r="E70" s="33" t="n">
-        <f aca="false">E65+E69</f>
+      <c r="E71" s="33" t="n">
+        <f aca="false">E66+E70</f>
         <v>999035.721380829</v>
       </c>
-      <c r="F70" s="33" t="n">
-        <f aca="false">F65+F69</f>
+      <c r="F71" s="33" t="n">
+        <f aca="false">F66+F70</f>
         <v>1095544.9005226</v>
       </c>
-      <c r="G70" s="33" t="n">
-        <f aca="false">G65+G69</f>
+      <c r="G71" s="33" t="n">
+        <f aca="false">G66+G70</f>
         <v>1142599.80122793</v>
       </c>
-      <c r="I70" s="33" t="n">
-        <f aca="false">I65+I69</f>
+      <c r="I71" s="33" t="n">
+        <f aca="false">I66+I70</f>
         <v>965679.929906982</v>
       </c>
-      <c r="J70" s="33" t="n">
-        <f aca="false">J65+J69</f>
+      <c r="J71" s="33" t="n">
+        <f aca="false">J66+J70</f>
         <v>953567.068923511</v>
       </c>
-      <c r="K70" s="33" t="n">
-        <f aca="false">K65+K69</f>
+      <c r="K71" s="33" t="n">
+        <f aca="false">K66+K70</f>
         <v>951980.820675503</v>
       </c>
-      <c r="L70" s="33" t="n">
-        <f aca="false">L65+L69</f>
+      <c r="L71" s="33" t="n">
+        <f aca="false">L66+L70</f>
         <v>948060.597174319</v>
       </c>
-      <c r="M70" s="33" t="n">
-        <f aca="false">M65+M69</f>
+      <c r="M71" s="33" t="n">
+        <f aca="false">M66+M70</f>
         <v>947852.259148087</v>
       </c>
-      <c r="N70" s="33" t="n">
-        <f aca="false">N65+N69</f>
+      <c r="N71" s="33" t="n">
+        <f aca="false">N66+N70</f>
         <v>946466.865335537</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="0" t="s">
-        <v>358</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <f aca="false">D70-D68</f>
-        <v>836715.827184379</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <f aca="false">E70-E68</f>
-        <v>878009.843866036</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <f aca="false">F70-F68</f>
-        <v>962902.428333255</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <f aca="false">G70-G68</f>
-        <v>1004196.44501491</v>
-      </c>
-      <c r="I71" s="31" t="n">
-        <f aca="false">I70-I68</f>
-        <v>848840.240853728</v>
-      </c>
-      <c r="J71" s="31" t="n">
-        <f aca="false">J70-J68</f>
-        <v>838121.101122722</v>
-      </c>
-      <c r="K71" s="31" t="n">
-        <f aca="false">K70-K68</f>
-        <v>836715.827184379</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <f aca="false">L70-L68</f>
-        <v>833250.625132899</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <f aca="false">M70-M68</f>
-        <v>833066.616741775</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <f aca="false">N70-N68</f>
-        <v>831840.685517278</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="0" t="s">
-        <v>109</v>
+        <v>358</v>
       </c>
       <c r="D72" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,D70/m_MP,0)</f>
-        <v>15866.3470112584</v>
+        <f aca="false">D71-D69</f>
+        <v>836715.827184379</v>
       </c>
       <c r="E72" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,E70/m_MP,0)</f>
-        <v>16650.5953563471</v>
+        <f aca="false">E71-E69</f>
+        <v>878009.843866036</v>
       </c>
       <c r="F72" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,F70/m_MP,0)</f>
-        <v>18259.0816753767</v>
+        <f aca="false">F71-F69</f>
+        <v>962902.428333255</v>
       </c>
       <c r="G72" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,G70/m_MP,0)</f>
-        <v>19043.3300204655</v>
+        <f aca="false">G71-G69</f>
+        <v>1004196.44501491</v>
       </c>
       <c r="I72" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,I70/m_MP,0)</f>
-        <v>16094.6654984497</v>
+        <f aca="false">I71-I69</f>
+        <v>848840.240853728</v>
       </c>
       <c r="J72" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,J70/m_MP,0)</f>
-        <v>15892.7844820585</v>
+        <f aca="false">J71-J69</f>
+        <v>838121.101122722</v>
       </c>
       <c r="K72" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,K70/m_MP,0)</f>
-        <v>15866.3470112584</v>
+        <f aca="false">K71-K69</f>
+        <v>836715.827184379</v>
       </c>
       <c r="L72" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,L70/m_MP,0)</f>
-        <v>15801.0099529053</v>
+        <f aca="false">L71-L69</f>
+        <v>833250.625132899</v>
       </c>
       <c r="M72" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,M70/m_MP,0)</f>
-        <v>15797.5376524681</v>
+        <f aca="false">M71-M69</f>
+        <v>833066.616741775</v>
       </c>
       <c r="N72" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,N70/m_MP,0)</f>
-        <v>15774.4477555923</v>
+        <f aca="false">N71-N69</f>
+        <v>831840.685517278</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D73" s="39" t="n">
-        <f aca="false">D72/in_eur</f>
-        <v>3668.51954017535</v>
-      </c>
-      <c r="E73" s="39" t="n">
-        <f aca="false">E72/in_eur</f>
-        <v>3849.8486373057</v>
-      </c>
-      <c r="F73" s="39" t="n">
-        <f aca="false">F72/in_eur</f>
-        <v>4221.75298852641</v>
-      </c>
-      <c r="G73" s="39" t="n">
-        <f aca="false">G72/in_eur</f>
-        <v>4403.08208565676</v>
-      </c>
-      <c r="I73" s="39" t="n">
-        <f aca="false">I72/in_eur</f>
-        <v>3721.30994183808</v>
-      </c>
-      <c r="J73" s="39" t="n">
-        <f aca="false">J72/in_eur</f>
-        <v>3674.63225018694</v>
-      </c>
-      <c r="K73" s="39" t="n">
-        <f aca="false">K72/in_eur</f>
-        <v>3668.51954017535</v>
-      </c>
-      <c r="L73" s="39" t="n">
-        <f aca="false">L72/in_eur</f>
-        <v>3653.41270587406</v>
-      </c>
-      <c r="M73" s="39" t="n">
-        <f aca="false">M72/in_eur</f>
-        <v>3652.60986184234</v>
-      </c>
-      <c r="N73" s="39" t="n">
-        <f aca="false">N72/in_eur</f>
-        <v>3647.27115736238</v>
+        <v>109</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,D71/m_MP,0)</f>
+        <v>15866.3470112584</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,E71/m_MP,0)</f>
+        <v>16650.5953563471</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,F71/m_MP,0)</f>
+        <v>18259.0816753767</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,G71/m_MP,0)</f>
+        <v>19043.3300204655</v>
+      </c>
+      <c r="I73" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,I71/m_MP,0)</f>
+        <v>16094.6654984497</v>
+      </c>
+      <c r="J73" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,J71/m_MP,0)</f>
+        <v>15892.7844820585</v>
+      </c>
+      <c r="K73" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,K71/m_MP,0)</f>
+        <v>15866.3470112584</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,L71/m_MP,0)</f>
+        <v>15801.0099529053</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,M71/m_MP,0)</f>
+        <v>15797.5376524681</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,N71/m_MP,0)</f>
+        <v>15774.4477555923</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="0" t="s">
         <v>359</v>
       </c>
-      <c r="D74" s="31" t="n">
-        <f aca="false">(D64-D58+c_dzwig_alt*e_dzw_dni)/(1-(c_kob+c_gdw+in_zysk_min))</f>
-        <v>894242.937931035</v>
-      </c>
-      <c r="E74" s="31" t="n">
-        <f aca="false">(E64-E58+c_dzwig_alt*e_dzw_dni)/(1-(c_kob+c_gdw+in_zysk_min))</f>
-        <v>939005.668965517</v>
-      </c>
-      <c r="F74" s="31" t="n">
-        <f aca="false">(F64-F58+c_dzwig_alt*e_dzw_dni)/(1-(c_kob+c_gdw+in_zysk_min))</f>
-        <v>1029267.94482759</v>
-      </c>
-      <c r="G74" s="31" t="n">
-        <f aca="false">(G64-G58+c_dzwig_alt*e_dzw_dni)/(1-(c_kob+c_gdw+in_zysk_min))</f>
-        <v>1074030.67586207</v>
-      </c>
-      <c r="I74" s="31" t="n">
-        <f aca="false">(I64-I58+c_dzwig_alt*e_dzw_dni)/(1-(c_kob+c_gdw+in_zysk_min))</f>
-        <v>906478.503448276</v>
-      </c>
-      <c r="J74" s="31" t="n">
-        <f aca="false">(J64-J58+c_dzwig_alt*e_dzw_dni)/(1-(c_kob+c_gdw+in_zysk_min))</f>
-        <v>895649.129118774</v>
-      </c>
-      <c r="K74" s="31" t="n">
-        <f aca="false">(K64-K58+c_dzwig_alt*e_dzw_dni)/(1-(c_kob+c_gdw+in_zysk_min))</f>
-        <v>894242.937931035</v>
-      </c>
-      <c r="L74" s="31" t="n">
-        <f aca="false">(L64-L58+c_dzwig_alt*e_dzw_dni)/(1-(c_kob+c_gdw+in_zysk_min))</f>
-        <v>890707.368965517</v>
-      </c>
-      <c r="M74" s="31" t="n">
-        <f aca="false">(M64-M58+c_dzwig_alt*e_dzw_dni)/(1-(c_kob+c_gdw+in_zysk_min))</f>
-        <v>890518.324904215</v>
-      </c>
-      <c r="N74" s="31" t="n">
-        <f aca="false">(N64-N58+c_dzwig_alt*e_dzw_dni)/(1-(c_kob+c_gdw+in_zysk_min))</f>
-        <v>889279.28226601</v>
+      <c r="D74" s="39" t="n">
+        <f aca="false">D73/in_eur</f>
+        <v>3668.51954017535</v>
+      </c>
+      <c r="E74" s="39" t="n">
+        <f aca="false">E73/in_eur</f>
+        <v>3849.8486373057</v>
+      </c>
+      <c r="F74" s="39" t="n">
+        <f aca="false">F73/in_eur</f>
+        <v>4221.75298852641</v>
+      </c>
+      <c r="G74" s="39" t="n">
+        <f aca="false">G73/in_eur</f>
+        <v>4403.08208565676</v>
+      </c>
+      <c r="I74" s="39" t="n">
+        <f aca="false">I73/in_eur</f>
+        <v>3721.30994183808</v>
+      </c>
+      <c r="J74" s="39" t="n">
+        <f aca="false">J73/in_eur</f>
+        <v>3674.63225018694</v>
+      </c>
+      <c r="K74" s="39" t="n">
+        <f aca="false">K73/in_eur</f>
+        <v>3668.51954017535</v>
+      </c>
+      <c r="L74" s="39" t="n">
+        <f aca="false">L73/in_eur</f>
+        <v>3653.41270587406</v>
+      </c>
+      <c r="M74" s="39" t="n">
+        <f aca="false">M73/in_eur</f>
+        <v>3652.60986184234</v>
+      </c>
+      <c r="N74" s="39" t="n">
+        <f aca="false">N73/in_eur</f>
+        <v>3647.27115736238</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="0" t="s">
         <v>360</v>
       </c>
-      <c r="D75" s="33" t="n">
-        <f aca="false">D74+c_podatek*(D60+D61+D62+D63+D74*(c_gdw+in_zysk_min))</f>
-        <v>920388.543184828</v>
-      </c>
-      <c r="E75" s="33" t="n">
-        <f aca="false">E74+c_podatek*(E60+E61+E62+E63+E74*(c_gdw+in_zysk_min))</f>
-        <v>965934.622012414</v>
-      </c>
-      <c r="F75" s="33" t="n">
-        <f aca="false">F74+c_podatek*(F60+F61+F62+F63+F74*(c_gdw+in_zysk_min))</f>
-        <v>1059401.32154207</v>
-      </c>
-      <c r="G75" s="33" t="n">
-        <f aca="false">G74+c_podatek*(G60+G61+G62+G63+G74*(c_gdw+in_zysk_min))</f>
-        <v>1104947.40036966</v>
-      </c>
-      <c r="I75" s="33" t="n">
-        <f aca="false">I74+c_podatek*(I60+I61+I62+I63+I74*(c_gdw+in_zysk_min))</f>
-        <v>933675.226978621</v>
-      </c>
-      <c r="J75" s="33" t="n">
-        <f aca="false">J74+c_podatek*(J60+J61+J62+J63+J74*(c_gdw+in_zysk_min))</f>
-        <v>921927.392805019</v>
-      </c>
-      <c r="K75" s="33" t="n">
-        <f aca="false">K74+c_podatek*(K60+K61+K62+K63+K74*(c_gdw+in_zysk_min))</f>
-        <v>920388.543184828</v>
-      </c>
-      <c r="L75" s="33" t="n">
-        <f aca="false">L74+c_podatek*(L60+L61+L62+L63+L74*(c_gdw+in_zysk_min))</f>
-        <v>916587.493462414</v>
-      </c>
-      <c r="M75" s="33" t="n">
-        <f aca="false">M74+c_podatek*(M60+M61+M62+M63+M74*(c_gdw+in_zysk_min))</f>
-        <v>916385.527563372</v>
-      </c>
-      <c r="N75" s="33" t="n">
-        <f aca="false">N74+c_podatek*(N60+N61+N62+N63+N74*(c_gdw+in_zysk_min))</f>
-        <v>915041.898285665</v>
+      <c r="D75" s="31" t="n">
+        <f aca="false">D65/(1-(c_kob+c_gdw+in_zysk2))</f>
+        <v>895622.248275862</v>
+      </c>
+      <c r="E75" s="31" t="n">
+        <f aca="false">E65/(1-(c_kob+c_gdw+in_zysk2))</f>
+        <v>940384.979310345</v>
+      </c>
+      <c r="F75" s="31" t="n">
+        <f aca="false">F65/(1-(c_kob+c_gdw+in_zysk2))</f>
+        <v>1030647.25517241</v>
+      </c>
+      <c r="G75" s="31" t="n">
+        <f aca="false">G65/(1-(c_kob+c_gdw+in_zysk2))</f>
+        <v>1075409.9862069</v>
+      </c>
+      <c r="I75" s="31" t="n">
+        <f aca="false">I65/(1-(c_kob+c_gdw+in_zysk2))</f>
+        <v>907857.813793103</v>
+      </c>
+      <c r="J75" s="31" t="n">
+        <f aca="false">J65/(1-(c_kob+c_gdw+in_zysk2))</f>
+        <v>897028.439463601</v>
+      </c>
+      <c r="K75" s="31" t="n">
+        <f aca="false">K65/(1-(c_kob+c_gdw+in_zysk2))</f>
+        <v>895622.248275862</v>
+      </c>
+      <c r="L75" s="31" t="n">
+        <f aca="false">L65/(1-(c_kob+c_gdw+in_zysk2))</f>
+        <v>892086.679310345</v>
+      </c>
+      <c r="M75" s="31" t="n">
+        <f aca="false">M65/(1-(c_kob+c_gdw+in_zysk2))</f>
+        <v>891897.635249042</v>
+      </c>
+      <c r="N75" s="31" t="n">
+        <f aca="false">N65/(1-(c_kob+c_gdw+in_zysk2))</f>
+        <v>890658.592610837</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="D76" s="31" t="n">
+        <f aca="false">D75*in_zysk2</f>
+        <v>89562.2248275862</v>
+      </c>
+      <c r="E76" s="31" t="n">
+        <f aca="false">E75*in_zysk2</f>
+        <v>94038.4979310345</v>
+      </c>
+      <c r="F76" s="31" t="n">
+        <f aca="false">F75*in_zysk2</f>
+        <v>103064.725517241</v>
+      </c>
+      <c r="G76" s="31" t="n">
+        <f aca="false">G75*in_zysk2</f>
+        <v>107540.99862069</v>
+      </c>
+      <c r="I76" s="31" t="n">
+        <f aca="false">I75*in_zysk2</f>
+        <v>90785.7813793104</v>
+      </c>
+      <c r="J76" s="31" t="n">
+        <f aca="false">J75*in_zysk2</f>
+        <v>89702.8439463602</v>
+      </c>
+      <c r="K76" s="31" t="n">
+        <f aca="false">K75*in_zysk2</f>
+        <v>89562.2248275862</v>
+      </c>
+      <c r="L76" s="31" t="n">
+        <f aca="false">L75*in_zysk2</f>
+        <v>89208.6679310345</v>
+      </c>
+      <c r="M76" s="31" t="n">
+        <f aca="false">M75*in_zysk2</f>
+        <v>89189.7635249042</v>
+      </c>
+      <c r="N76" s="31" t="n">
+        <f aca="false">N75*in_zysk2</f>
+        <v>89065.8592610838</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="D77" s="33" t="n">
+        <f aca="false">D75+c_podatek*(D61+D62+D63+D64+D75*(c_gdw+in_zysk2))</f>
+        <v>921791.99146069</v>
+      </c>
+      <c r="E77" s="33" t="n">
+        <f aca="false">E75+c_podatek*(E61+E62+E63+E64+E75*(c_gdw+in_zysk2))</f>
+        <v>967338.070288276</v>
+      </c>
+      <c r="F77" s="33" t="n">
+        <f aca="false">F75+c_podatek*(F61+F62+F63+F64+F75*(c_gdw+in_zysk2))</f>
+        <v>1060804.76981793</v>
+      </c>
+      <c r="G77" s="33" t="n">
+        <f aca="false">G75+c_podatek*(G61+G62+G63+G64+G75*(c_gdw+in_zysk2))</f>
+        <v>1106350.84864552</v>
+      </c>
+      <c r="I77" s="33" t="n">
+        <f aca="false">I75+c_podatek*(I61+I62+I63+I64+I75*(c_gdw+in_zysk2))</f>
+        <v>935078.675254483</v>
+      </c>
+      <c r="J77" s="33" t="n">
+        <f aca="false">J75+c_podatek*(J61+J62+J63+J64+J75*(c_gdw+in_zysk2))</f>
+        <v>923330.841080881</v>
+      </c>
+      <c r="K77" s="33" t="n">
+        <f aca="false">K75+c_podatek*(K61+K62+K63+K64+K75*(c_gdw+in_zysk2))</f>
+        <v>921791.99146069</v>
+      </c>
+      <c r="L77" s="33" t="n">
+        <f aca="false">L75+c_podatek*(L61+L62+L63+L64+L75*(c_gdw+in_zysk2))</f>
+        <v>917990.941738276</v>
+      </c>
+      <c r="M77" s="33" t="n">
+        <f aca="false">M75+c_podatek*(M61+M62+M63+M64+M75*(c_gdw+in_zysk2))</f>
+        <v>917788.975839234</v>
+      </c>
+      <c r="N77" s="33" t="n">
+        <f aca="false">N75+c_podatek*(N61+N62+N63+N64+N75*(c_gdw+in_zysk2))</f>
+        <v>916445.346561527</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="D78" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,D77/m_MP,0)</f>
+        <v>15363.1998576782</v>
+      </c>
+      <c r="E78" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,E77/m_MP,0)</f>
+        <v>16122.3011714713</v>
+      </c>
+      <c r="F78" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,F77/m_MP,0)</f>
+        <v>17680.0794969655</v>
+      </c>
+      <c r="G78" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,G77/m_MP,0)</f>
+        <v>18439.1808107586</v>
+      </c>
+      <c r="I78" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,I77/m_MP,0)</f>
+        <v>15584.6445875747</v>
+      </c>
+      <c r="J78" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,J77/m_MP,0)</f>
+        <v>15388.847351348</v>
+      </c>
+      <c r="K78" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,K77/m_MP,0)</f>
+        <v>15363.1998576782</v>
+      </c>
+      <c r="L78" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,L77/m_MP,0)</f>
+        <v>15299.8490289713</v>
+      </c>
+      <c r="M78" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,M77/m_MP,0)</f>
+        <v>15296.4829306539</v>
+      </c>
+      <c r="N78" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,N77/m_MP,0)</f>
+        <v>15274.0891093588</v>
       </c>
     </row>
   </sheetData>

--- a/kalkulator-nk38/Kalkulator_NK38_v1_przyklad_WAW.xlsx
+++ b/kalkulator-nk38/Kalkulator_NK38_v1_przyklad_WAW.xlsx
@@ -33,9 +33,6 @@
     <definedName function="false" hidden="false" name="c_km_dzien" vbProcedure="false">Cennik!$C$53</definedName>
     <definedName function="false" hidden="false" name="c_km_krakow" vbProcedure="false">Cennik!$C$52</definedName>
     <definedName function="false" hidden="false" name="c_kob" vbProcedure="false">Cennik!$C$65</definedName>
-    <definedName function="false" hidden="false" name="c_konserw" vbProcedure="false">Cennik!$C$69</definedName>
-    <definedName function="false" hidden="false" name="c_konserw2" vbProcedure="false">Cennik!$C$70</definedName>
-    <definedName function="false" hidden="false" name="c_konserw3" vbProcedure="false">Cennik!$C$71</definedName>
     <definedName function="false" hidden="false" name="c_magistrala" vbProcedure="false">Cennik!$C$26</definedName>
     <definedName function="false" hidden="false" name="c_mal_bar" vbProcedure="false">Cennik!$C$35</definedName>
     <definedName function="false" hidden="false" name="c_mal_D" vbProcedure="false">Cennik!$C$34</definedName>
@@ -80,7 +77,7 @@
     <definedName function="false" hidden="false" name="e_podr_pom" vbProcedure="false">Obliczenia!$C$32</definedName>
     <definedName function="false" hidden="false" name="e_rozl_dni" vbProcedure="false">Obliczenia!$C$31</definedName>
     <definedName function="false" hidden="false" name="in_agregaty" vbProcedure="false">Dane!$C$22</definedName>
-    <definedName function="false" hidden="false" name="in_analiza" vbProcedure="false">Dane!$C$60</definedName>
+    <definedName function="false" hidden="false" name="in_analiza" vbProcedure="false">Dane!$C$62</definedName>
     <definedName function="false" hidden="false" name="in_barierki" vbProcedure="false">Dane!$C$24</definedName>
     <definedName function="false" hidden="false" name="in_D" vbProcedure="false">Dane!$C$20</definedName>
     <definedName function="false" hidden="false" name="in_data" vbProcedure="false">Dane!$C$7</definedName>
@@ -96,6 +93,8 @@
     <definedName function="false" hidden="false" name="in_km" vbProcedure="false">Dane!$C$13</definedName>
     <definedName function="false" hidden="false" name="in_km_mon" vbProcedure="false">Dane!$C$15</definedName>
     <definedName function="false" hidden="false" name="in_km_pom" vbProcedure="false">Dane!$C$14</definedName>
+    <definedName function="false" hidden="false" name="in_konsA" vbProcedure="false">Dane!$C$60</definedName>
+    <definedName function="false" hidden="false" name="in_konsB" vbProcedure="false">Dane!$C$61</definedName>
     <definedName function="false" hidden="false" name="in_lok" vbProcedure="false">Dane!$C$12</definedName>
     <definedName function="false" hidden="false" name="in_magistrala" vbProcedure="false">Dane!$C$23</definedName>
     <definedName function="false" hidden="false" name="in_maskownice" vbProcedure="false">Dane!$C$25</definedName>
@@ -141,12 +140,12 @@
     <definedName function="false" hidden="false" name="m_suma_2500" vbProcedure="false">Obliczenia!$C$22</definedName>
     <definedName function="false" hidden="false" name="m_utr" vbProcedure="false">Obliczenia!$C$25</definedName>
     <definedName function="false" hidden="false" name="m_utr_auto" vbProcedure="false">Obliczenia!$C$24</definedName>
-    <definedName function="false" hidden="false" name="t_gl_doplata" vbProcedure="false">Cennik!$C$75:$C$83</definedName>
-    <definedName function="false" hidden="false" name="t_gl_silownik" vbProcedure="false">Cennik!$D$75:$D$83</definedName>
-    <definedName function="false" hidden="false" name="t_sk_cena" vbProcedure="false">Cennik!$C$87:$C$113</definedName>
-    <definedName function="false" hidden="false" name="t_sk_D" vbProcedure="false">Cennik!$E$87:$E$113</definedName>
-    <definedName function="false" hidden="false" name="t_sk_grupa" vbProcedure="false">Cennik!$F$87:$F$113</definedName>
-    <definedName function="false" hidden="false" name="t_sk_S" vbProcedure="false">Cennik!$D$87:$D$113</definedName>
+    <definedName function="false" hidden="false" name="t_gl_doplata" vbProcedure="false">Cennik!$C$71:$C$79</definedName>
+    <definedName function="false" hidden="false" name="t_gl_silownik" vbProcedure="false">Cennik!$D$71:$D$79</definedName>
+    <definedName function="false" hidden="false" name="t_sk_cena" vbProcedure="false">Cennik!$C$83:$C$109</definedName>
+    <definedName function="false" hidden="false" name="t_sk_D" vbProcedure="false">Cennik!$E$83:$E$109</definedName>
+    <definedName function="false" hidden="false" name="t_sk_grupa" vbProcedure="false">Cennik!$F$83:$F$109</definedName>
+    <definedName function="false" hidden="false" name="t_sk_S" vbProcedure="false">Cennik!$D$83:$D$109</definedName>
     <definedName function="false" hidden="false" name="t_wymiary" vbProcedure="false">Dane!$F$46</definedName>
     <definedName function="false" hidden="false" name="t_zaglebienia" vbProcedure="false">Dane!$F$45</definedName>
   </definedNames>
@@ -160,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="359">
   <si>
     <t xml:space="preserve">KALKULATOR NK38 - DANE WEJŚCIOWE</t>
   </si>
@@ -330,10 +329,10 @@
     <t xml:space="preserve">Orientacyjnie: KRK 1600, WAW/WRO 3300, POZ/ZG 4500</t>
   </si>
   <si>
-    <t xml:space="preserve">Rozładunek - sprzęt / TIR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAW 1700, KRK 500</t>
+    <t xml:space="preserve">Rozładunek - sprzęt (jednorazowo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jednorazowy koszt przyjazdu i wyjazdu wózka</t>
   </si>
   <si>
     <t xml:space="preserve">Nadpisz: dni rozładunku</t>
@@ -378,6 +377,12 @@
     <t xml:space="preserve">Kurs EUR/PLN</t>
   </si>
   <si>
+    <t xml:space="preserve">Konserwacja - cena A [zł / MP / miesiąc]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konserwacja - cena B [zł / MP / miesiąc]</t>
+  </si>
+  <si>
     <t xml:space="preserve">Analiza liczby osób dla wariantu</t>
   </si>
   <si>
@@ -543,7 +548,7 @@
     <t xml:space="preserve">Dopłata Q=2500</t>
   </si>
   <si>
-    <t xml:space="preserve">Konserwacja roczna (40 / 45 / 50 zł/MP/mies.)</t>
+    <t xml:space="preserve">Konserwacja roczna A / B</t>
   </si>
   <si>
     <t xml:space="preserve">Opis / wariant</t>
@@ -567,6 +572,9 @@
     <t xml:space="preserve">• Czas podróży: wzór 'Stary (poprawiony)' = stary dla &lt; 800 km, dla &gt;= 800 km uwzględnia liczbę wyjazdów. 'Uproszczony' = 2 x km / 650 km dziennie na wyjazd.</t>
   </si>
   <si>
+    <t xml:space="preserve">• Rozładunek sprzętu to jednorazowy koszt przyjazdu i wyjazdu wózka (nie mnoży się przez liczbę TIR-ów).</t>
+  </si>
+  <si>
     <t xml:space="preserve">• Zysk B liczony od tych samych kosztów co zysk A (dawna kolumna N, bez zmiany ceny dźwigu).</t>
   </si>
   <si>
@@ -912,27 +920,6 @@
     <t xml:space="preserve">KAL!J37</t>
   </si>
   <si>
-    <t xml:space="preserve">Serwis (informacyjnie)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konserwacja zł / MP / miesiąc (wariant 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!I45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konserwacja zł / MP / miesiąc (wariant 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!L45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konserwacja zł / MP / miesiąc (wariant 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAL!N45</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zagłębienia (standard 170 cm: bez dopłaty, siłownik 1700)</t>
   </si>
   <si>
@@ -1200,7 +1187,7 @@
     <t xml:space="preserve">Spider Crane</t>
   </si>
   <si>
-    <t xml:space="preserve">Rozładunek (sprzęt)</t>
+    <t xml:space="preserve">Rozładunek (sprzęt, jednorazowo)</t>
   </si>
   <si>
     <t xml:space="preserve">Rozładunek (ludzie)</t>
@@ -1838,7 +1825,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:F68"/>
+  <dimension ref="B2:F70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -2323,7 +2310,7 @@
         <v>56</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>1700</v>
+        <v>5100</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>57</v>
@@ -2416,39 +2403,37 @@
       <c r="B60" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="0" t="s">
         <v>73</v>
       </c>
+      <c r="C61" s="13" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="16" t="str">
-        <f aca="false">IF(OR(C39&lt;0,D39&lt;0),"BŁĄD: więcej zagłębień niż platform","ok")</f>
-        <v>ok</v>
-      </c>
-      <c r="C63" s="16"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
+      <c r="C62" s="6" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="16" t="str">
-        <f aca="false">IF(OR(in_szer1_S+in_szer2_S&gt;in_S,in_szer1_D+in_szer2_D&gt;in_D),"BŁĄD: więcej szerokości niż platform","ok")</f>
-        <v>ok</v>
-      </c>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
+      <c r="B64" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="16" t="str">
-        <f aca="false">IF(OR(in_dl500_S+in_dl540_S+in_dl550_S&gt;in_S,in_dl500_D+in_dl540_D+in_dl550_D&gt;in_D),"BŁĄD: więcej długości niż platform","ok")</f>
+        <f aca="false">IF(OR(C39&lt;0,D39&lt;0),"BŁĄD: więcej zagłębień niż platform","ok")</f>
         <v>ok</v>
       </c>
       <c r="C65" s="16"/>
@@ -2457,7 +2442,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="16" t="str">
-        <f aca="false">IF(in_agregaty*6&lt;in_S+in_D+in_NP,"UWAGA: mniej niż 1 agregat na 6 platform","ok")</f>
+        <f aca="false">IF(OR(in_szer1_S+in_szer2_S&gt;in_S,in_szer1_D+in_szer2_D&gt;in_D),"BŁĄD: więcej szerokości niż platform","ok")</f>
         <v>ok</v>
       </c>
       <c r="C66" s="16"/>
@@ -2466,7 +2451,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="16" t="str">
-        <f aca="false">IF(in_S+in_D+in_NP=0,"UWAGA: brak platform",IF(in_tir=0,"UWAGA: brak transportów","ok"))</f>
+        <f aca="false">IF(OR(in_dl500_S+in_dl540_S+in_dl550_S&gt;in_S,in_dl500_D+in_dl540_D+in_dl550_D&gt;in_D),"BŁĄD: więcej długości niż platform","ok")</f>
         <v>ok</v>
       </c>
       <c r="C67" s="16"/>
@@ -2475,25 +2460,43 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="16" t="str">
-        <f aca="false">IF(AND(in_lok="Poza Krakowem",in_km=0),"UWAGA: brak odległości od Krakowa","ok")</f>
+        <f aca="false">IF(in_agregaty*6&lt;in_S+in_D+in_NP,"UWAGA: mniej niż 1 agregat na 6 platform","ok")</f>
         <v>ok</v>
       </c>
       <c r="C68" s="16"/>
       <c r="D68" s="16"/>
       <c r="E68" s="16"/>
     </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="16" t="str">
+        <f aca="false">IF(in_S+in_D+in_NP=0,"UWAGA: brak platform",IF(in_tir=0,"UWAGA: brak transportów","ok"))</f>
+        <v>ok</v>
+      </c>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="16" t="str">
+        <f aca="false">IF(AND(in_lok="Poza Krakowem",in_km=0),"UWAGA: brak odległości od Krakowa","ok")</f>
+        <v>ok</v>
+      </c>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B64:E64"/>
     <mergeCell ref="B65:E65"/>
     <mergeCell ref="B66:E66"/>
     <mergeCell ref="B67:E67"/>
     <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B70:E70"/>
   </mergeCells>
-  <conditionalFormatting sqref="B63:B68">
+  <conditionalFormatting sqref="B65:B70">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>B63&lt;&gt;"ok"</formula>
+      <formula>B65&lt;&gt;"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -2509,7 +2512,7 @@
       <formula1>"Stary (poprawiony),Uproszczony"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C60" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C62" type="list">
       <formula1>"2000 kg,2500 kg,2000 kg + słupki,2500 kg + słupki"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2537,7 +2540,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:H68"/>
+  <dimension ref="B2:H69"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -2548,7 +2551,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2571,19 +2574,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2632,7 +2635,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C9" s="19" t="n">
         <f aca="false">Obliczenia!D73</f>
@@ -2653,7 +2656,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C10" s="19" t="n">
         <f aca="false">Obliczenia!D78</f>
@@ -2674,7 +2677,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C11" s="20" t="n">
         <f aca="false">Obliczenia!D74</f>
@@ -2695,7 +2698,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C12" s="19" t="n">
         <f aca="false">Obliczenia!D69</f>
@@ -2716,7 +2719,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C13" s="19" t="n">
         <f aca="false">Obliczenia!D76</f>
@@ -2737,7 +2740,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C14" s="19" t="n">
         <f aca="false">Obliczenia!D72</f>
@@ -2758,7 +2761,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C16" s="19" t="n">
         <f aca="false">Obliczenia!D54</f>
@@ -2779,7 +2782,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">Obliczenia!D55</f>
@@ -2800,7 +2803,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C18" s="19" t="n">
         <f aca="false">Obliczenia!D58+Obliczenia!D59+Obliczenia!D60</f>
@@ -2821,7 +2824,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C19" s="19" t="n">
         <f aca="false">Obliczenia!D63+Obliczenia!D61+Obliczenia!D62</f>
@@ -2842,7 +2845,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C20" s="19" t="n">
         <f aca="false">Obliczenia!D57+Obliczenia!D64+Obliczenia!D56</f>
@@ -2863,7 +2866,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C21" s="19" t="n">
         <f aca="false">Obliczenia!D67+Obliczenia!D68+Obliczenia!D70</f>
@@ -2884,7 +2887,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C23" s="21" t="n">
         <f aca="false">Obliczenia!D51</f>
@@ -2905,7 +2908,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C24" s="21" t="n">
         <f aca="false">Obliczenia!D52</f>
@@ -2926,7 +2929,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C25" s="22" t="n">
         <f aca="false">Obliczenia!D50</f>
@@ -2947,18 +2950,18 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C28" s="19" t="n">
         <f aca="false">Obliczenia!F71-Obliczenia!D71</f>
@@ -2971,7 +2974,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C29" s="19" t="n">
         <f aca="false">Obliczenia!F71-Obliczenia!D71+(c_slupek22-c_slupek)*m_MP*e_mnoznik</f>
@@ -2984,7 +2987,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C30" s="19" t="n">
         <f aca="false">m_malowanie*e_mnoznik</f>
@@ -3003,30 +3006,30 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C34" s="19" t="n">
         <f aca="false">Obliczenia!I71</f>
@@ -3055,7 +3058,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C35" s="19" t="n">
         <f aca="false">Obliczenia!I73</f>
@@ -3084,7 +3087,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C36" s="23" t="n">
         <f aca="false">Obliczenia!I51</f>
@@ -3113,7 +3116,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="0" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C37" s="23" t="n">
         <f aca="false">Obliczenia!I48</f>
@@ -3142,7 +3145,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C38" s="19" t="n">
         <f aca="false">Obliczenia!I57+Obliczenia!I64</f>
@@ -3171,12 +3174,12 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -3185,7 +3188,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C42" s="16" t="str">
         <f aca="false">in_typ&amp;": "&amp;IF(in_S&gt;0,in_S&amp;" x S (2 MP)  ","")&amp;IF(in_D&gt;0,in_D&amp;" x D (4 MP)  ","")&amp;IF(in_NP&gt;0,in_NP&amp;" x N.P.  ","")&amp;"= "&amp;m_MP&amp;" MP"</f>
@@ -3213,7 +3216,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C44" s="16" t="str">
         <f aca="false">IF(t_zaglebienia="","standard 170 cm",t_zaglebienia)</f>
@@ -3227,7 +3230,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C45" s="16" t="str">
         <f aca="false">IF(t_wymiary="","standard",t_wymiary)</f>
@@ -3241,7 +3244,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C46" s="16" t="str">
         <f aca="false">in_magistrala&amp;" x 6 m  /  "&amp;in_barierki&amp;" szt.  /  "&amp;in_maskownice&amp;" szt."</f>
@@ -3255,7 +3258,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C47" s="16" t="str">
         <f aca="false">m_utr&amp;" (z magistrali i barierek "&amp;m_utr_auto&amp;", ręcznie "&amp;in_utr_dod&amp;")"</f>
@@ -3283,7 +3286,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C49" s="16" t="str">
         <f aca="false">e_km_pom&amp;" / "&amp;e_km_mon&amp;" km"</f>
@@ -3297,11 +3300,11 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="0" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C50" s="16" t="str">
-        <f aca="false">in_tir&amp;" TIR x "&amp;TEXT(in_tir_cena,"#,##0")&amp;" zł, rozładunek "&amp;TEXT(in_rozl_cena,"#,##0")&amp;" zł/TIR, "&amp;e_rozl_dni&amp;" dni"</f>
-        <v>3 TIR x 4,000 zł, rozładunek 1,700 zł/TIR, 1.5 dni</v>
+        <f aca="false">in_tir&amp;" TIR x "&amp;TEXT(in_tir_cena,"#,##0")&amp;" zł, rozładunek sprzętu "&amp;TEXT(in_rozl_cena,"#,##0")&amp;" zł jednorazowo, "&amp;e_rozl_dni&amp;" dni"</f>
+        <v>3 TIR x 4,000 zł, rozładunek sprzętu 5,100 zł jednorazowo, 1.5 dni</v>
       </c>
       <c r="D50" s="16"/>
       <c r="E50" s="16"/>
@@ -3311,7 +3314,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C51" s="16" t="str">
         <f aca="false">in_osoby&amp;" osób, średnia stawka "&amp;TEXT(Obliczenia!D41,"#,##0")&amp;" zł/dzień"</f>
@@ -3325,7 +3328,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C52" s="16" t="str">
         <f aca="false">e_dzw_dni&amp;" dni"</f>
@@ -3339,7 +3342,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C53" s="16" t="str">
         <f aca="false">Obliczenia!D51&amp;" dni pracy = "&amp;Obliczenia!D48&amp;IF(e_krk," dni"," tyg.")&amp;", "&amp;TEXT(Obliczenia!D50,"0.0")&amp;" osobodni"</f>
@@ -3353,7 +3356,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C54" s="16" t="str">
         <f aca="false">Obliczenia!F51&amp;" dni pracy = "&amp;Obliczenia!F48&amp;IF(e_krk," dni"," tyg.")&amp;", "&amp;TEXT(Obliczenia!F50,"0.0")&amp;" osobodni"</f>
@@ -3367,7 +3370,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C55" s="16" t="str">
         <f aca="false">TEXT(in_zysk,"0.0%")&amp;" / "&amp;TEXT(in_zysk2,"0.0%")</f>
@@ -3381,7 +3384,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C56" s="16" t="str">
         <f aca="false">TEXT(in_q2500,"0.0%")</f>
@@ -3409,11 +3412,11 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C58" s="16" t="str">
-        <f aca="false">TEXT(c_konserw*m_MP*12,"#,##0")&amp;" / "&amp;TEXT(c_konserw2*m_MP*12,"#,##0")&amp;" / "&amp;TEXT(c_konserw3*m_MP*12,"#,##0")&amp;" zł"</f>
-        <v>28,800 / 32,400 / 36,000 zł</v>
+        <f aca="false">TEXT(in_konsA*m_MP*12,"#,##0")&amp;" / "&amp;TEXT(in_konsB*m_MP*12,"#,##0")&amp;" zł  (przegląd półroczny "&amp;TEXT(in_konsA*m_MP*6,"#,##0")&amp;" / "&amp;TEXT(in_konsB*m_MP*6,"#,##0")&amp;" zł)"</f>
+        <v>28,800 / 36,000 zł  (przegląd półroczny 14,400 / 18,000 zł)</v>
       </c>
       <c r="D58" s="16"/>
       <c r="E58" s="16"/>
@@ -3423,7 +3426,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C59" s="16" t="str">
         <f aca="false">in_opis&amp;""</f>
@@ -3437,16 +3440,16 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C61" s="0" t="str">
-        <f aca="false">IF(COUNTIF(Dane!B63:B68,"ok")=6,"wszystko ok","sprawdź arkusz Dane")</f>
+        <f aca="false">IF(COUNTIF(Dane!B65:B70,"ok")=6,"wszystko ok","sprawdź arkusz Dane")</f>
         <v>wszystko ok</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
@@ -3457,7 +3460,7 @@
     </row>
     <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="24" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C64" s="24"/>
       <c r="D64" s="24"/>
@@ -3468,7 +3471,7 @@
     </row>
     <row r="65" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="24" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C65" s="24"/>
       <c r="D65" s="24"/>
@@ -3479,7 +3482,7 @@
     </row>
     <row r="66" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="24" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C66" s="24"/>
       <c r="D66" s="24"/>
@@ -3490,7 +3493,7 @@
     </row>
     <row r="67" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="24" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C67" s="24"/>
       <c r="D67" s="24"/>
@@ -3501,7 +3504,7 @@
     </row>
     <row r="68" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="24" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C68" s="24"/>
       <c r="D68" s="24"/>
@@ -3510,8 +3513,19 @@
       <c r="G68" s="24"/>
       <c r="H68" s="24"/>
     </row>
+    <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B69" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+    </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="C43:H43"/>
     <mergeCell ref="C44:H44"/>
@@ -3535,6 +3549,7 @@
     <mergeCell ref="B66:H66"/>
     <mergeCell ref="B67:H67"/>
     <mergeCell ref="B68:H68"/>
+    <mergeCell ref="B69:H69"/>
   </mergeCells>
   <conditionalFormatting sqref="C34:H34">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
@@ -3561,7 +3576,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:F113"/>
+  <dimension ref="B2:F109"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -3573,7 +3588,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -3582,12 +3597,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -3595,90 +3610,90 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>32500</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>700</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C8" s="14" t="n">
         <v>0.61</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>0.85</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>1170</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>1560</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>1820</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>3110</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3689,34 +3704,34 @@
         <v>2340</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C15" s="25" t="n">
         <v>0.00127</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C16" s="14" t="n">
         <v>0.07</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -3724,107 +3739,107 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>6500</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>1500</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>200</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>500</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>50</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>1080</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>1175</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>1250</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="0" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C26" s="26" t="n">
         <f aca="false">0.2*11+0.4*11+2*14+6*11+6*5+6*10</f>
         <v>190.6</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -3832,51 +3847,51 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>600</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>700</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>1000</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="0" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1800</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -3884,73 +3899,73 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="0" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>6400</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>13500</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="0" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>200</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="0" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>1700</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="0" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>6300</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>0.37</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -3958,117 +3973,117 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="0" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>5.5</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="0" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C41" s="9" t="n">
         <v>7</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="0" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>7</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="0" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="0" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C44" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="0" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C45" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="0" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C46" s="13" t="n">
         <v>2400</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="0" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>5</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="0" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="0" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>5</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="4" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
@@ -4076,84 +4091,84 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="0" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>50</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="0" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>20</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="0" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>650</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="0" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>12</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="0" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C55" s="26" t="n">
         <v>9.4</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="0" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="0" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C57" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
@@ -4161,62 +4176,62 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="0" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C59" s="13" t="n">
         <v>500</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="0" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>400</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="0" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C61" s="13" t="n">
         <v>350</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C62" s="13" t="n">
         <v>45</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="0" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C63" s="13" t="n">
         <v>130</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
@@ -4224,103 +4239,106 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="0" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C65" s="14" t="n">
         <v>0.005</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="0" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C66" s="14" t="n">
         <v>0.025</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="0" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C67" s="14" t="n">
         <v>0.14</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
+        <v>252</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="0" t="s">
-        <v>251</v>
-      </c>
-      <c r="C69" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>252</v>
-      </c>
+      <c r="B69" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="C70" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="E70" s="8" t="s">
+      <c r="B70" s="11" t="s">
         <v>254</v>
       </c>
+      <c r="C70" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="0" t="s">
-        <v>255</v>
-      </c>
-      <c r="C71" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>256</v>
+      <c r="B71" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="C71" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="28" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="C72" s="27" t="n">
+        <v>500</v>
+      </c>
+      <c r="D72" s="28" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
+      <c r="B73" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="C73" s="27" t="n">
+        <v>550</v>
+      </c>
+      <c r="D73" s="28" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="D74" s="11" t="s">
-        <v>260</v>
+      <c r="B74" s="0" t="n">
+        <v>190</v>
+      </c>
+      <c r="C74" s="27" t="n">
+        <v>600</v>
+      </c>
+      <c r="D74" s="28" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="0" t="n">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="C75" s="27" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="D75" s="28" t="n">
         <v>2000</v>
@@ -4328,10 +4346,10 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="0" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C76" s="27" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="D76" s="28" t="n">
         <v>2000</v>
@@ -4339,122 +4357,146 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="0" t="n">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="C77" s="27" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
       <c r="D77" s="28" t="n">
-        <v>2000</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="0" t="n">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="C78" s="27" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="D78" s="28" t="n">
-        <v>2000</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="0" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="C79" s="27" t="n">
-        <v>650</v>
+        <v>850</v>
       </c>
       <c r="D79" s="28" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="C80" s="27" t="n">
-        <v>700</v>
-      </c>
-      <c r="D80" s="28" t="n">
-        <v>2000</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="0" t="n">
-        <v>210</v>
-      </c>
-      <c r="C81" s="27" t="n">
-        <v>750</v>
-      </c>
-      <c r="D81" s="28" t="n">
-        <v>2250</v>
-      </c>
+      <c r="B81" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="0" t="n">
-        <v>220</v>
-      </c>
-      <c r="C82" s="27" t="n">
-        <v>800</v>
-      </c>
-      <c r="D82" s="28" t="n">
-        <v>2250</v>
+      <c r="B82" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="0" t="n">
-        <v>225</v>
-      </c>
-      <c r="C83" s="27" t="n">
-        <v>850</v>
+      <c r="B83" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="C83" s="29" t="n">
+        <v>45</v>
       </c>
       <c r="D83" s="28" t="n">
-        <v>2250</v>
+        <v>9.6</v>
+      </c>
+      <c r="E83" s="28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F83" s="30" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="C84" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D84" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E84" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F84" s="30" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
+      <c r="B85" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C85" s="29" t="n">
+        <v>36</v>
+      </c>
+      <c r="D85" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" s="30" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="D86" s="11" t="s">
+      <c r="B86" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C86" s="29" t="n">
+        <v>90</v>
+      </c>
+      <c r="D86" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" s="30" t="s">
         <v>264</v>
-      </c>
-      <c r="E86" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="F86" s="11" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C87" s="29" t="n">
-        <v>45</v>
+        <v>207.28</v>
       </c>
       <c r="D87" s="28" t="n">
-        <v>9.6</v>
+        <v>2</v>
       </c>
       <c r="E87" s="28" t="n">
-        <v>9.6</v>
+        <v>2</v>
       </c>
       <c r="F87" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4462,16 +4504,16 @@
         <v>269</v>
       </c>
       <c r="C88" s="29" t="n">
-        <v>8</v>
+        <v>40.14</v>
       </c>
       <c r="D88" s="28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E88" s="28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F88" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4479,7 +4521,7 @@
         <v>270</v>
       </c>
       <c r="C89" s="29" t="n">
-        <v>36</v>
+        <v>3.3</v>
       </c>
       <c r="D89" s="28" t="n">
         <v>2</v>
@@ -4488,7 +4530,7 @@
         <v>2</v>
       </c>
       <c r="F89" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4496,7 +4538,7 @@
         <v>271</v>
       </c>
       <c r="C90" s="29" t="n">
-        <v>90</v>
+        <v>10.8</v>
       </c>
       <c r="D90" s="28" t="n">
         <v>2</v>
@@ -4505,7 +4547,7 @@
         <v>2</v>
       </c>
       <c r="F90" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4513,7 +4555,7 @@
         <v>272</v>
       </c>
       <c r="C91" s="29" t="n">
-        <v>207.28</v>
+        <v>10.95</v>
       </c>
       <c r="D91" s="28" t="n">
         <v>2</v>
@@ -4522,7 +4564,7 @@
         <v>2</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4530,7 +4572,7 @@
         <v>273</v>
       </c>
       <c r="C92" s="29" t="n">
-        <v>40.14</v>
+        <v>3.81</v>
       </c>
       <c r="D92" s="28" t="n">
         <v>2</v>
@@ -4539,7 +4581,7 @@
         <v>2</v>
       </c>
       <c r="F92" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4547,16 +4589,16 @@
         <v>274</v>
       </c>
       <c r="C93" s="29" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="D93" s="28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E93" s="28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F93" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4564,16 +4606,16 @@
         <v>275</v>
       </c>
       <c r="C94" s="29" t="n">
-        <v>10.8</v>
+        <v>4.4</v>
       </c>
       <c r="D94" s="28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E94" s="28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4581,16 +4623,17 @@
         <v>276</v>
       </c>
       <c r="C95" s="29" t="n">
-        <v>10.95</v>
+        <f aca="false">2*25.71+2*22.85</f>
+        <v>97.12</v>
       </c>
       <c r="D95" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4598,16 +4641,16 @@
         <v>277</v>
       </c>
       <c r="C96" s="29" t="n">
-        <v>3.81</v>
+        <v>345</v>
       </c>
       <c r="D96" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" s="28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F96" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4615,16 +4658,16 @@
         <v>278</v>
       </c>
       <c r="C97" s="29" t="n">
-        <v>2.84</v>
+        <v>546</v>
       </c>
       <c r="D97" s="28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E97" s="28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F97" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4632,16 +4675,16 @@
         <v>279</v>
       </c>
       <c r="C98" s="29" t="n">
-        <v>4.4</v>
+        <v>2.98</v>
       </c>
       <c r="D98" s="28" t="n">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="E98" s="28" t="n">
-        <v>4</v>
+        <v>208</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4649,17 +4692,17 @@
         <v>280</v>
       </c>
       <c r="C99" s="29" t="n">
-        <f aca="false">2*25.71+2*22.85</f>
-        <v>97.12</v>
+        <f aca="false">3.09+4.99</f>
+        <v>8.08</v>
       </c>
       <c r="D99" s="28" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E99" s="28" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4667,16 +4710,16 @@
         <v>281</v>
       </c>
       <c r="C100" s="29" t="n">
-        <v>345</v>
+        <v>5.4</v>
       </c>
       <c r="D100" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E100" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4684,16 +4727,16 @@
         <v>282</v>
       </c>
       <c r="C101" s="29" t="n">
-        <v>546</v>
+        <v>300</v>
       </c>
       <c r="D101" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" s="28" t="n">
         <v>1</v>
       </c>
       <c r="F101" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4701,16 +4744,16 @@
         <v>283</v>
       </c>
       <c r="C102" s="29" t="n">
-        <v>2.98</v>
+        <v>40</v>
       </c>
       <c r="D102" s="28" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="E102" s="28" t="n">
-        <v>208</v>
+        <v>1</v>
       </c>
       <c r="F102" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4718,17 +4761,16 @@
         <v>284</v>
       </c>
       <c r="C103" s="29" t="n">
-        <f aca="false">3.09+4.99</f>
-        <v>8.08</v>
+        <v>172</v>
       </c>
       <c r="D103" s="28" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E103" s="28" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>268</v>
+        <v>163</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4736,16 +4778,16 @@
         <v>285</v>
       </c>
       <c r="C104" s="29" t="n">
-        <v>5.4</v>
+        <v>207</v>
       </c>
       <c r="D104" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104" s="28" t="n">
         <v>1</v>
       </c>
       <c r="F104" s="30" t="s">
-        <v>268</v>
+        <v>163</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4753,7 +4795,8 @@
         <v>286</v>
       </c>
       <c r="C105" s="29" t="n">
-        <v>300</v>
+        <f aca="false">120+55+65</f>
+        <v>240</v>
       </c>
       <c r="D105" s="28" t="n">
         <v>1</v>
@@ -4762,7 +4805,7 @@
         <v>1</v>
       </c>
       <c r="F105" s="30" t="s">
-        <v>268</v>
+        <v>163</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4770,7 +4813,8 @@
         <v>287</v>
       </c>
       <c r="C106" s="29" t="n">
-        <v>40</v>
+        <f aca="false">50+40</f>
+        <v>90</v>
       </c>
       <c r="D106" s="28" t="n">
         <v>1</v>
@@ -4779,15 +4823,16 @@
         <v>1</v>
       </c>
       <c r="F106" s="30" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C107" s="29" t="n">
-        <v>172</v>
+        <f aca="false">14+9+25+5+9+30</f>
+        <v>92</v>
       </c>
       <c r="D107" s="28" t="n">
         <v>1</v>
@@ -4796,15 +4841,16 @@
         <v>0</v>
       </c>
       <c r="F107" s="30" t="s">
-        <v>160</v>
+        <v>288</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C108" s="29" t="n">
-        <v>207</v>
+        <f aca="false">14+18+25+7+18+30</f>
+        <v>112</v>
       </c>
       <c r="D108" s="28" t="n">
         <v>0</v>
@@ -4813,16 +4859,16 @@
         <v>1</v>
       </c>
       <c r="F108" s="30" t="s">
-        <v>160</v>
+        <v>288</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C109" s="29" t="n">
-        <f aca="false">120+55+65</f>
-        <v>240</v>
+        <f aca="false">70+14+34+32+20</f>
+        <v>170</v>
       </c>
       <c r="D109" s="28" t="n">
         <v>1</v>
@@ -4831,79 +4877,7 @@
         <v>1</v>
       </c>
       <c r="F109" s="30" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="0" t="s">
-        <v>291</v>
-      </c>
-      <c r="C110" s="29" t="n">
-        <f aca="false">50+40</f>
-        <v>90</v>
-      </c>
-      <c r="D110" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F110" s="30" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="0" t="s">
-        <v>293</v>
-      </c>
-      <c r="C111" s="29" t="n">
-        <f aca="false">14+9+25+5+9+30</f>
-        <v>92</v>
-      </c>
-      <c r="D111" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" s="30" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="0" t="s">
-        <v>294</v>
-      </c>
-      <c r="C112" s="29" t="n">
-        <f aca="false">14+18+25+7+18+30</f>
-        <v>112</v>
-      </c>
-      <c r="D112" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F112" s="30" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="0" t="s">
-        <v>295</v>
-      </c>
-      <c r="C113" s="29" t="n">
-        <f aca="false">70+14+34+32+20</f>
-        <v>170</v>
-      </c>
-      <c r="D113" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E113" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="30" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -4934,7 +4908,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -4951,13 +4925,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C5" s="31" t="n">
         <f aca="false">c_cena_D+IF(in_typ="NK37",c_doplata_NK37,0)</f>
@@ -4966,7 +4940,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C6" s="31" t="n">
         <f aca="false">c_wsp_S*m_cena_D</f>
@@ -4975,7 +4949,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C7" s="31" t="n">
         <f aca="false">c_wsp_NP*m_cena_D</f>
@@ -4984,7 +4958,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C8" s="32" t="n">
         <f aca="false">in_D+in_NP</f>
@@ -4993,7 +4967,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C9" s="32" t="n">
         <f aca="false">in_S+in_D+in_NP</f>
@@ -5002,7 +4976,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C10" s="32" t="n">
         <f aca="false">2*in_S+2*in_NP+4*in_D</f>
@@ -5011,7 +4985,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C11" s="31" t="n">
         <f aca="false">m_cena_S*in_S+c_szer_260*in_szer1_S+c_szer_270*in_szer2_S+SUMPRODUCT(in_gl_S,t_gl_doplata)+c_dl_500*in_dl500_S+CEILING(m_cena_S*c_dl_wsp*10,100)*in_dl540_S+CEILING(m_cena_S*c_dl_wsp*20,100)*in_dl550_S</f>
@@ -5020,7 +4994,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C12" s="31" t="n">
         <f aca="false">m_cena_D*in_D+c_szer_520*in_szer1_D+c_szer_540*in_szer2_D+SUMPRODUCT(in_gl_D,t_gl_doplata)+c_dl_500*in_dl500_D+m_cena_D*c_dl_wsp*10*in_dl540_D+m_cena_D*c_dl_wsp*20*in_dl550_D</f>
@@ -5029,7 +5003,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C13" s="31" t="n">
         <f aca="false">m_cena_NP*in_NP</f>
@@ -5038,7 +5012,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C14" s="32" t="n">
         <f aca="false">SUMPRODUCT((t_gl_silownik=2000)*(in_gl_S+in_gl_D))</f>
@@ -5047,7 +5021,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C15" s="32" t="n">
         <f aca="false">SUMPRODUCT((t_gl_silownik=2250)*(in_gl_S+in_gl_D))</f>
@@ -5056,7 +5030,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C16" s="32" t="n">
         <f aca="false">m_platformy-m_sil_2000-m_sil_2250</f>
@@ -5065,7 +5039,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C17" s="31" t="n">
         <f aca="false">in_agregaty*(c_agregat+c_hydr_drobne+c_olej+c_transp_agregatu)+m_platformy*c_transp_silownikow+2*(c_sil_1700*m_sil_std+c_sil_2000*m_sil_2000+c_sil_2250*m_sil_2250)+in_magistrala*c_magistrala+SUMPRODUCT((t_sk_grupa="Hydraulika")*t_sk_cena*(t_sk_S*in_S+t_sk_D*m_DN))</f>
@@ -5074,7 +5048,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C18" s="31" t="n">
         <f aca="false">in_barierki*c_barierka+in_maskownice*c_maskownica</f>
@@ -5083,7 +5057,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C19" s="31" t="n">
         <f aca="false">in_agregaty*c_skrzynka_zasil+SUMPRODUCT((t_sk_grupa="Elektryka")*t_sk_cena*(t_sk_S*in_S+t_sk_D*m_DN))</f>
@@ -5092,7 +5066,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C20" s="31" t="n">
         <f aca="false">in_agregaty*c_admin+SUMPRODUCT((t_sk_grupa="Mechanika")*t_sk_cena*(t_sk_S*in_S+t_sk_D*m_DN))</f>
@@ -5101,7 +5075,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="11" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C21" s="33" t="n">
         <f aca="false">m_plat_S+m_plat_D+m_plat_NP+m_hydraulika+m_barierki+m_elektryka+m_mechanika</f>
@@ -5110,7 +5084,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="11" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C22" s="33" t="n">
         <f aca="false">m_suma_2000*(1+in_q2500)</f>
@@ -5119,7 +5093,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C23" s="31" t="n">
         <f aca="false">c_mal_S*in_S+c_mal_D*m_DN+c_mal_bar*in_barierki</f>
@@ -5128,7 +5102,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C24" s="34" t="n">
         <f aca="false">ROUNDUP(in_magistrala*c_osd_magistrala+(in_barierki+in_maskownice)*c_osd_barierka,0)</f>
@@ -5137,7 +5111,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C25" s="34" t="n">
         <f aca="false">m_utr_auto+in_utr_dod</f>
@@ -5146,13 +5120,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C28" s="35" t="b">
         <f aca="false">in_lok="Kraków"</f>
@@ -5161,7 +5135,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C29" s="34" t="n">
         <f aca="false">IF(ISBLANK(in_km_pom),IF(e_krk,c_km_krakow,in_km),in_km_pom)</f>
@@ -5170,7 +5144,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C30" s="34" t="n">
         <f aca="false">IF(ISBLANK(in_km_mon),IF(e_krk,c_km_krakow,in_km+c_km_dodatek),in_km_mon)</f>
@@ -5179,7 +5153,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="0" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C31" s="34" t="n">
         <f aca="false">IF(ISBLANK(in_rozl_dni),c_rozl_TIR*in_tir,in_rozl_dni)</f>
@@ -5188,7 +5162,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="0" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C32" s="34" t="n">
         <f aca="false">(c_pomiary_osoby+c_odbiory_osoby)*IF(in_wzor="Uproszczony",2*e_km_pom/c_km_dzien*1,(1+0.1*MAX(0,800-e_km_pom)/100)*e_km_pom*1/500)</f>
@@ -5197,7 +5171,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="0" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">ROUNDUP(m_DN/c_dzwig_D+in_S*c_dzwig_wspS/c_dzwig_D,0)</f>
@@ -5206,7 +5180,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C34" s="36" t="n">
         <f aca="false">(1+c_podatek*(c_gdw+in_zysk))/(1-(c_kob+c_gdw+in_zysk))</f>
@@ -5215,7 +5189,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -5224,7 +5198,7 @@
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
@@ -5234,42 +5208,42 @@
     </row>
     <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="11" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D37" s="37" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E37" s="37" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J37" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K37" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L37" s="37" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M37" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N37" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D38" s="32" t="n">
         <v>0</v>
@@ -5310,7 +5284,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="0" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D39" s="32" t="n">
         <v>0</v>
@@ -5351,7 +5325,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="0" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D40" s="32" t="n">
         <f aca="false">in_osoby</f>
@@ -5390,7 +5364,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="0" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D41" s="31" t="n">
         <f aca="false">(c_stawka_1+IF(D40&gt;=2,c_stawka_2,0)+MAX(0,D40-2)*c_stawka_n)/D40</f>
@@ -5435,7 +5409,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="0" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D42" s="34" t="n">
         <f aca="false">c_osd_S*in_S+c_osd_D*in_D+c_osd_NP*in_NP+m_utr+D39*c_slupek_rbd*m_MP</f>
@@ -5480,7 +5454,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="0" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D43" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*1,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*1/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*1,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*1/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5525,7 +5499,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="0" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D44" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D43,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D43/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D43,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D43/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5570,7 +5544,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="0" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D45" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D44,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D44/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D44,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D44/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5615,7 +5589,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="0" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D46" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D45,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D45/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D45,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D45/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5660,7 +5634,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="0" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D47" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D46,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D46/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D46,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D46/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5705,7 +5679,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="11" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D48" s="38" t="n">
         <f aca="false">IF(ISBLANK(in_wyjazdy),D47,in_wyjazdy)</f>
@@ -5750,7 +5724,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="0" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D49" s="34" t="n">
         <f aca="false">(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D48,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D48/500)))</f>
@@ -5795,7 +5769,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D50" s="34" t="n">
         <f aca="false">D42+D49</f>
@@ -5840,7 +5814,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="11" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D51" s="38" t="n">
         <f aca="false">CEILING(D50/D40,1)</f>
@@ -5885,7 +5859,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="11" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D52" s="38" t="n">
         <f aca="false">IF(e_krk,CEILING(D51/c_dni_tydzien,1),D48)</f>
@@ -5930,7 +5904,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="0" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D53" s="34" t="n">
         <f aca="false">2*(e_km_mon*D48+2*e_km_pom)</f>
@@ -5975,7 +5949,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D54" s="31" t="n">
         <f aca="false">IF(D38=1,m_suma_2500,m_suma_2000)</f>
@@ -6020,7 +5994,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D55" s="31" t="n">
         <f aca="false">D39*c_slupek*m_MP</f>
@@ -6065,7 +6039,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="0" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D56" s="31" t="n">
         <f aca="false">D53/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
@@ -6110,7 +6084,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="0" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D57" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_hotel*(D51+1)*D40)</f>
@@ -6155,7 +6129,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="0" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D58" s="31" t="n">
         <f aca="false">in_tir_cena*in_tir</f>
@@ -6200,7 +6174,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="0" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D59" s="31" t="n">
         <f aca="false">c_dzwig*e_dzw_dni</f>
@@ -6245,52 +6219,52 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="0" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D60" s="31" t="n">
-        <f aca="false">in_rozl_cena*in_tir</f>
+        <f aca="false">in_rozl_cena</f>
         <v>5100</v>
       </c>
       <c r="E60" s="31" t="n">
-        <f aca="false">in_rozl_cena*in_tir</f>
+        <f aca="false">in_rozl_cena</f>
         <v>5100</v>
       </c>
       <c r="F60" s="31" t="n">
-        <f aca="false">in_rozl_cena*in_tir</f>
+        <f aca="false">in_rozl_cena</f>
         <v>5100</v>
       </c>
       <c r="G60" s="31" t="n">
-        <f aca="false">in_rozl_cena*in_tir</f>
+        <f aca="false">in_rozl_cena</f>
         <v>5100</v>
       </c>
       <c r="I60" s="31" t="n">
-        <f aca="false">in_rozl_cena*in_tir</f>
+        <f aca="false">in_rozl_cena</f>
         <v>5100</v>
       </c>
       <c r="J60" s="31" t="n">
-        <f aca="false">in_rozl_cena*in_tir</f>
+        <f aca="false">in_rozl_cena</f>
         <v>5100</v>
       </c>
       <c r="K60" s="31" t="n">
-        <f aca="false">in_rozl_cena*in_tir</f>
+        <f aca="false">in_rozl_cena</f>
         <v>5100</v>
       </c>
       <c r="L60" s="31" t="n">
-        <f aca="false">in_rozl_cena*in_tir</f>
+        <f aca="false">in_rozl_cena</f>
         <v>5100</v>
       </c>
       <c r="M60" s="31" t="n">
-        <f aca="false">in_rozl_cena*in_tir</f>
+        <f aca="false">in_rozl_cena</f>
         <v>5100</v>
       </c>
       <c r="N60" s="31" t="n">
-        <f aca="false">in_rozl_cena*in_tir</f>
+        <f aca="false">in_rozl_cena</f>
         <v>5100</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="0" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D61" s="31" t="n">
         <f aca="false">D41*e_rozl_dni*D40</f>
@@ -6335,7 +6309,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="0" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D62" s="31" t="n">
         <f aca="false">D41*(D49-D40*e_rozl_dni)</f>
@@ -6380,7 +6354,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="0" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D63" s="31" t="n">
         <f aca="false">IF(D48&gt;0,D41*D42,0)</f>
@@ -6425,7 +6399,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="0" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D64" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_dieta*D50)</f>
@@ -6470,7 +6444,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D65" s="33" t="n">
         <f aca="false">SUM(D54:D64)</f>
@@ -6515,7 +6489,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="0" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D66" s="31" t="n">
         <f aca="false">D65/(1-(c_kob+c_gdw+in_zysk))</f>
@@ -6560,7 +6534,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="0" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D67" s="31" t="n">
         <f aca="false">D66*c_kob</f>
@@ -6605,7 +6579,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="0" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D68" s="31" t="n">
         <f aca="false">D66*c_gdw</f>
@@ -6650,7 +6624,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="0" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D69" s="31" t="n">
         <f aca="false">D66*in_zysk</f>
@@ -6695,7 +6669,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="0" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D70" s="31" t="n">
         <f aca="false">c_podatek*(D61+D62+D63+D64+D68+D69)</f>
@@ -6740,7 +6714,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="11" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D71" s="33" t="n">
         <f aca="false">D66+D70</f>
@@ -6785,7 +6759,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="0" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D72" s="31" t="n">
         <f aca="false">D71-D69</f>
@@ -6830,7 +6804,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D73" s="31" t="n">
         <f aca="false">IF(m_MP&gt;0,D71/m_MP,0)</f>
@@ -6875,7 +6849,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="0" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D74" s="39" t="n">
         <f aca="false">D73/in_eur</f>
@@ -6920,7 +6894,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="0" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D75" s="31" t="n">
         <f aca="false">D65/(1-(c_kob+c_gdw+in_zysk2))</f>
@@ -6965,7 +6939,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="0" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D76" s="31" t="n">
         <f aca="false">D75*in_zysk2</f>
@@ -7010,7 +6984,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="11" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D77" s="33" t="n">
         <f aca="false">D75+c_podatek*(D61+D62+D63+D64+D75*(c_gdw+in_zysk2))</f>
@@ -7055,7 +7029,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D78" s="31" t="n">
         <f aca="false">IF(m_MP&gt;0,D77/m_MP,0)</f>

--- a/kalkulator-nk38/Kalkulator_NK38_v1_przyklad_WAW.xlsx
+++ b/kalkulator-nk38/Kalkulator_NK38_v1_przyklad_WAW.xlsx
@@ -77,7 +77,7 @@
     <definedName function="false" hidden="false" name="e_podr_pom" vbProcedure="false">Obliczenia!$C$32</definedName>
     <definedName function="false" hidden="false" name="e_rozl_dni" vbProcedure="false">Obliczenia!$C$31</definedName>
     <definedName function="false" hidden="false" name="in_agregaty" vbProcedure="false">Dane!$C$22</definedName>
-    <definedName function="false" hidden="false" name="in_analiza" vbProcedure="false">Dane!$C$62</definedName>
+    <definedName function="false" hidden="false" name="in_analiza" vbProcedure="false">Dane!$C$63</definedName>
     <definedName function="false" hidden="false" name="in_barierki" vbProcedure="false">Dane!$C$24</definedName>
     <definedName function="false" hidden="false" name="in_D" vbProcedure="false">Dane!$C$20</definedName>
     <definedName function="false" hidden="false" name="in_data" vbProcedure="false">Dane!$C$7</definedName>
@@ -87,14 +87,15 @@
     <definedName function="false" hidden="false" name="in_dl540_S" vbProcedure="false">Dane!$C$43</definedName>
     <definedName function="false" hidden="false" name="in_dl550_D" vbProcedure="false">Dane!$D$44</definedName>
     <definedName function="false" hidden="false" name="in_dl550_S" vbProcedure="false">Dane!$C$44</definedName>
-    <definedName function="false" hidden="false" name="in_eur" vbProcedure="false">Dane!$C$59</definedName>
+    <definedName function="false" hidden="false" name="in_dzwig_koszt" vbProcedure="false">Dane!$C$51</definedName>
+    <definedName function="false" hidden="false" name="in_eur" vbProcedure="false">Dane!$C$60</definedName>
     <definedName function="false" hidden="false" name="in_gl_D" vbProcedure="false">Dane!$D$30:$D$38</definedName>
     <definedName function="false" hidden="false" name="in_gl_S" vbProcedure="false">Dane!$C$30:$C$38</definedName>
     <definedName function="false" hidden="false" name="in_km" vbProcedure="false">Dane!$C$13</definedName>
     <definedName function="false" hidden="false" name="in_km_mon" vbProcedure="false">Dane!$C$15</definedName>
     <definedName function="false" hidden="false" name="in_km_pom" vbProcedure="false">Dane!$C$14</definedName>
-    <definedName function="false" hidden="false" name="in_konsA" vbProcedure="false">Dane!$C$60</definedName>
-    <definedName function="false" hidden="false" name="in_konsB" vbProcedure="false">Dane!$C$61</definedName>
+    <definedName function="false" hidden="false" name="in_konsA" vbProcedure="false">Dane!$C$61</definedName>
+    <definedName function="false" hidden="false" name="in_konsB" vbProcedure="false">Dane!$C$62</definedName>
     <definedName function="false" hidden="false" name="in_lok" vbProcedure="false">Dane!$C$12</definedName>
     <definedName function="false" hidden="false" name="in_magistrala" vbProcedure="false">Dane!$C$23</definedName>
     <definedName function="false" hidden="false" name="in_maskownice" vbProcedure="false">Dane!$C$25</definedName>
@@ -102,8 +103,8 @@
     <definedName function="false" hidden="false" name="in_NP" vbProcedure="false">Dane!$C$21</definedName>
     <definedName function="false" hidden="false" name="in_nr" vbProcedure="false">Dane!$C$8</definedName>
     <definedName function="false" hidden="false" name="in_opis" vbProcedure="false">Dane!$C$9</definedName>
-    <definedName function="false" hidden="false" name="in_osoby" vbProcedure="false">Dane!$C$51</definedName>
-    <definedName function="false" hidden="false" name="in_q2500" vbProcedure="false">Dane!$C$58</definedName>
+    <definedName function="false" hidden="false" name="in_osoby" vbProcedure="false">Dane!$C$52</definedName>
+    <definedName function="false" hidden="false" name="in_q2500" vbProcedure="false">Dane!$C$59</definedName>
     <definedName function="false" hidden="false" name="in_rozl_cena" vbProcedure="false">Dane!$C$49</definedName>
     <definedName function="false" hidden="false" name="in_rozl_dni" vbProcedure="false">Dane!$C$50</definedName>
     <definedName function="false" hidden="false" name="in_S" vbProcedure="false">Dane!$C$19</definedName>
@@ -115,10 +116,10 @@
     <definedName function="false" hidden="false" name="in_tir_cena" vbProcedure="false">Dane!$C$48</definedName>
     <definedName function="false" hidden="false" name="in_typ" vbProcedure="false">Dane!$C$18</definedName>
     <definedName function="false" hidden="false" name="in_utr_dod" vbProcedure="false">Dane!$C$26</definedName>
-    <definedName function="false" hidden="false" name="in_wyjazdy" vbProcedure="false">Dane!$C$52</definedName>
-    <definedName function="false" hidden="false" name="in_wzor" vbProcedure="false">Dane!$C$53</definedName>
-    <definedName function="false" hidden="false" name="in_zysk" vbProcedure="false">Dane!$C$56</definedName>
-    <definedName function="false" hidden="false" name="in_zysk2" vbProcedure="false">Dane!$C$57</definedName>
+    <definedName function="false" hidden="false" name="in_wyjazdy" vbProcedure="false">Dane!$C$53</definedName>
+    <definedName function="false" hidden="false" name="in_wzor" vbProcedure="false">Dane!$C$54</definedName>
+    <definedName function="false" hidden="false" name="in_zysk" vbProcedure="false">Dane!$C$57</definedName>
+    <definedName function="false" hidden="false" name="in_zysk2" vbProcedure="false">Dane!$C$58</definedName>
     <definedName function="false" hidden="false" name="m_barierki" vbProcedure="false">Obliczenia!$C$18</definedName>
     <definedName function="false" hidden="false" name="m_cena_D" vbProcedure="false">Obliczenia!$C$5</definedName>
     <definedName function="false" hidden="false" name="m_cena_NP" vbProcedure="false">Obliczenia!$C$7</definedName>
@@ -159,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="361">
   <si>
     <t xml:space="preserve">KALKULATOR NK38 - DANE WEJŚCIOWE</t>
   </si>
@@ -339,6 +340,12 @@
   </si>
   <si>
     <t xml:space="preserve">puste = 0,5 dnia / TIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nadpisz: koszt Spider Crane razem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">puste = cena za dzień x liczba dni</t>
   </si>
   <si>
     <t xml:space="preserve">Liczba osób na montażu</t>
@@ -1825,7 +1832,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:F70"/>
+  <dimension ref="B2:F71"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -2329,9 +2336,7 @@
       <c r="B51" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="C51" s="10" t="n">
-        <v>4</v>
-      </c>
+      <c r="C51" s="13"/>
       <c r="E51" s="8" t="s">
         <v>61</v>
       </c>
@@ -2340,109 +2345,111 @@
       <c r="B52" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="10"/>
+      <c r="C52" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="E52" s="8" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="C53" s="6" t="s">
         <v>64</v>
       </c>
+      <c r="C53" s="10"/>
       <c r="E53" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="0" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="4" t="s">
+      <c r="C54" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
+      <c r="E54" s="8" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="C56" s="14" t="n">
-        <v>0.125</v>
-      </c>
+      <c r="B56" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C57" s="14" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C58" s="14" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>70</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="C59" s="15" t="n">
-        <v>4.325</v>
+      <c r="C59" s="14" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="C60" s="13" t="n">
-        <v>40</v>
+        <v>73</v>
+      </c>
+      <c r="C60" s="15" t="n">
+        <v>4.325</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C61" s="13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="C62" s="6" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="4" t="s">
+      <c r="C62" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
+      <c r="C63" s="6" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="16" t="str">
-        <f aca="false">IF(OR(C39&lt;0,D39&lt;0),"BŁĄD: więcej zagłębień niż platform","ok")</f>
-        <v>ok</v>
-      </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
+      <c r="B65" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="16" t="str">
-        <f aca="false">IF(OR(in_szer1_S+in_szer2_S&gt;in_S,in_szer1_D+in_szer2_D&gt;in_D),"BŁĄD: więcej szerokości niż platform","ok")</f>
+        <f aca="false">IF(OR(C39&lt;0,D39&lt;0),"BŁĄD: więcej zagłębień niż platform","ok")</f>
         <v>ok</v>
       </c>
       <c r="C66" s="16"/>
@@ -2451,7 +2458,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="16" t="str">
-        <f aca="false">IF(OR(in_dl500_S+in_dl540_S+in_dl550_S&gt;in_S,in_dl500_D+in_dl540_D+in_dl550_D&gt;in_D),"BŁĄD: więcej długości niż platform","ok")</f>
+        <f aca="false">IF(OR(in_szer1_S+in_szer2_S&gt;in_S,in_szer1_D+in_szer2_D&gt;in_D),"BŁĄD: więcej szerokości niż platform","ok")</f>
         <v>ok</v>
       </c>
       <c r="C67" s="16"/>
@@ -2460,7 +2467,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="16" t="str">
-        <f aca="false">IF(in_agregaty*6&lt;in_S+in_D+in_NP,"UWAGA: mniej niż 1 agregat na 6 platform","ok")</f>
+        <f aca="false">IF(OR(in_dl500_S+in_dl540_S+in_dl550_S&gt;in_S,in_dl500_D+in_dl540_D+in_dl550_D&gt;in_D),"BŁĄD: więcej długości niż platform","ok")</f>
         <v>ok</v>
       </c>
       <c r="C68" s="16"/>
@@ -2469,7 +2476,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="16" t="str">
-        <f aca="false">IF(in_S+in_D+in_NP=0,"UWAGA: brak platform",IF(in_tir=0,"UWAGA: brak transportów","ok"))</f>
+        <f aca="false">IF(in_agregaty*6&lt;in_S+in_D+in_NP,"UWAGA: mniej niż 1 agregat na 6 platform","ok")</f>
         <v>ok</v>
       </c>
       <c r="C69" s="16"/>
@@ -2478,25 +2485,34 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="16" t="str">
-        <f aca="false">IF(AND(in_lok="Poza Krakowem",in_km=0),"UWAGA: brak odległości od Krakowa","ok")</f>
+        <f aca="false">IF(in_S+in_D+in_NP=0,"UWAGA: brak platform",IF(in_tir=0,"UWAGA: brak transportów","ok"))</f>
         <v>ok</v>
       </c>
       <c r="C70" s="16"/>
       <c r="D70" s="16"/>
       <c r="E70" s="16"/>
     </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="16" t="str">
+        <f aca="false">IF(AND(in_lok="Poza Krakowem",in_km=0),"UWAGA: brak odległości od Krakowa","ok")</f>
+        <v>ok</v>
+      </c>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B65:E65"/>
     <mergeCell ref="B66:E66"/>
     <mergeCell ref="B67:E67"/>
     <mergeCell ref="B68:E68"/>
     <mergeCell ref="B69:E69"/>
     <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B71:E71"/>
   </mergeCells>
-  <conditionalFormatting sqref="B65:B70">
+  <conditionalFormatting sqref="B66:B71">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>B65&lt;&gt;"ok"</formula>
+      <formula>B66&lt;&gt;"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -2508,11 +2524,11 @@
       <formula1>"NK38,NK37"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C53" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C54" type="list">
       <formula1>"Stary (poprawiony),Uproszczony"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C62" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C63" type="list">
       <formula1>"2000 kg,2500 kg,2000 kg + słupki,2500 kg + słupki"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2520,7 +2536,7 @@
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C51" type="whole">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C52" type="whole">
       <formula1>1</formula1>
       <formula2>12</formula2>
     </dataValidation>
@@ -2551,7 +2567,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2574,19 +2590,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2635,7 +2651,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C9" s="19" t="n">
         <f aca="false">Obliczenia!D73</f>
@@ -2656,7 +2672,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" s="19" t="n">
         <f aca="false">Obliczenia!D78</f>
@@ -2677,7 +2693,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C11" s="20" t="n">
         <f aca="false">Obliczenia!D74</f>
@@ -2698,7 +2714,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C12" s="19" t="n">
         <f aca="false">Obliczenia!D69</f>
@@ -2719,7 +2735,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C13" s="19" t="n">
         <f aca="false">Obliczenia!D76</f>
@@ -2740,7 +2756,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C14" s="19" t="n">
         <f aca="false">Obliczenia!D72</f>
@@ -2761,7 +2777,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C16" s="19" t="n">
         <f aca="false">Obliczenia!D54</f>
@@ -2782,7 +2798,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">Obliczenia!D55</f>
@@ -2803,7 +2819,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C18" s="19" t="n">
         <f aca="false">Obliczenia!D58+Obliczenia!D59+Obliczenia!D60</f>
@@ -2824,7 +2840,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C19" s="19" t="n">
         <f aca="false">Obliczenia!D63+Obliczenia!D61+Obliczenia!D62</f>
@@ -2845,7 +2861,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C20" s="19" t="n">
         <f aca="false">Obliczenia!D57+Obliczenia!D64+Obliczenia!D56</f>
@@ -2866,7 +2882,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C21" s="19" t="n">
         <f aca="false">Obliczenia!D67+Obliczenia!D68+Obliczenia!D70</f>
@@ -2887,7 +2903,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C23" s="21" t="n">
         <f aca="false">Obliczenia!D51</f>
@@ -2908,7 +2924,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C24" s="21" t="n">
         <f aca="false">Obliczenia!D52</f>
@@ -2929,7 +2945,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C25" s="22" t="n">
         <f aca="false">Obliczenia!D50</f>
@@ -2950,18 +2966,18 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C28" s="19" t="n">
         <f aca="false">Obliczenia!F71-Obliczenia!D71</f>
@@ -2974,7 +2990,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C29" s="19" t="n">
         <f aca="false">Obliczenia!F71-Obliczenia!D71+(c_slupek22-c_slupek)*m_MP*e_mnoznik</f>
@@ -2987,7 +3003,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C30" s="19" t="n">
         <f aca="false">m_malowanie*e_mnoznik</f>
@@ -3006,30 +3022,30 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C34" s="19" t="n">
         <f aca="false">Obliczenia!I71</f>
@@ -3058,7 +3074,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C35" s="19" t="n">
         <f aca="false">Obliczenia!I73</f>
@@ -3087,7 +3103,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C36" s="23" t="n">
         <f aca="false">Obliczenia!I51</f>
@@ -3116,7 +3132,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C37" s="23" t="n">
         <f aca="false">Obliczenia!I48</f>
@@ -3145,7 +3161,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C38" s="19" t="n">
         <f aca="false">Obliczenia!I57+Obliczenia!I64</f>
@@ -3174,12 +3190,12 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -3188,7 +3204,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C42" s="16" t="str">
         <f aca="false">in_typ&amp;": "&amp;IF(in_S&gt;0,in_S&amp;" x S (2 MP)  ","")&amp;IF(in_D&gt;0,in_D&amp;" x D (4 MP)  ","")&amp;IF(in_NP&gt;0,in_NP&amp;" x N.P.  ","")&amp;"= "&amp;m_MP&amp;" MP"</f>
@@ -3216,7 +3232,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C44" s="16" t="str">
         <f aca="false">IF(t_zaglebienia="","standard 170 cm",t_zaglebienia)</f>
@@ -3230,7 +3246,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C45" s="16" t="str">
         <f aca="false">IF(t_wymiary="","standard",t_wymiary)</f>
@@ -3244,7 +3260,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C46" s="16" t="str">
         <f aca="false">in_magistrala&amp;" x 6 m  /  "&amp;in_barierki&amp;" szt.  /  "&amp;in_maskownice&amp;" szt."</f>
@@ -3258,7 +3274,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="0" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C47" s="16" t="str">
         <f aca="false">m_utr&amp;" (z magistrali i barierek "&amp;m_utr_auto&amp;", ręcznie "&amp;in_utr_dod&amp;")"</f>
@@ -3286,7 +3302,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C49" s="16" t="str">
         <f aca="false">e_km_pom&amp;" / "&amp;e_km_mon&amp;" km"</f>
@@ -3300,7 +3316,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C50" s="16" t="str">
         <f aca="false">in_tir&amp;" TIR x "&amp;TEXT(in_tir_cena,"#,##0")&amp;" zł, rozładunek sprzętu "&amp;TEXT(in_rozl_cena,"#,##0")&amp;" zł jednorazowo, "&amp;e_rozl_dni&amp;" dni"</f>
@@ -3314,7 +3330,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C51" s="16" t="str">
         <f aca="false">in_osoby&amp;" osób, średnia stawka "&amp;TEXT(Obliczenia!D41,"#,##0")&amp;" zł/dzień"</f>
@@ -3328,7 +3344,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C52" s="16" t="str">
         <f aca="false">e_dzw_dni&amp;" dni"</f>
@@ -3342,7 +3358,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C53" s="16" t="str">
         <f aca="false">Obliczenia!D51&amp;" dni pracy = "&amp;Obliczenia!D48&amp;IF(e_krk," dni"," tyg.")&amp;", "&amp;TEXT(Obliczenia!D50,"0.0")&amp;" osobodni"</f>
@@ -3356,7 +3372,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C54" s="16" t="str">
         <f aca="false">Obliczenia!F51&amp;" dni pracy = "&amp;Obliczenia!F48&amp;IF(e_krk," dni"," tyg.")&amp;", "&amp;TEXT(Obliczenia!F50,"0.0")&amp;" osobodni"</f>
@@ -3370,7 +3386,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C55" s="16" t="str">
         <f aca="false">TEXT(in_zysk,"0.0%")&amp;" / "&amp;TEXT(in_zysk2,"0.0%")</f>
@@ -3384,7 +3400,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C56" s="16" t="str">
         <f aca="false">TEXT(in_q2500,"0.0%")</f>
@@ -3398,7 +3414,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="0" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C57" s="16" t="str">
         <f aca="false">in_wzor</f>
@@ -3412,7 +3428,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C58" s="16" t="str">
         <f aca="false">TEXT(in_konsA*m_MP*12,"#,##0")&amp;" / "&amp;TEXT(in_konsB*m_MP*12,"#,##0")&amp;" zł  (przegląd półroczny "&amp;TEXT(in_konsA*m_MP*6,"#,##0")&amp;" / "&amp;TEXT(in_konsB*m_MP*6,"#,##0")&amp;" zł)"</f>
@@ -3426,7 +3442,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C59" s="16" t="str">
         <f aca="false">in_opis&amp;""</f>
@@ -3440,16 +3456,16 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C61" s="0" t="str">
-        <f aca="false">IF(COUNTIF(Dane!B65:B70,"ok")=6,"wszystko ok","sprawdź arkusz Dane")</f>
+        <f aca="false">IF(COUNTIF(Dane!B66:B71,"ok")=6,"wszystko ok","sprawdź arkusz Dane")</f>
         <v>wszystko ok</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
@@ -3460,7 +3476,7 @@
     </row>
     <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="24" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C64" s="24"/>
       <c r="D64" s="24"/>
@@ -3471,7 +3487,7 @@
     </row>
     <row r="65" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="24" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C65" s="24"/>
       <c r="D65" s="24"/>
@@ -3482,7 +3498,7 @@
     </row>
     <row r="66" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="24" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C66" s="24"/>
       <c r="D66" s="24"/>
@@ -3493,7 +3509,7 @@
     </row>
     <row r="67" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="24" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C67" s="24"/>
       <c r="D67" s="24"/>
@@ -3504,7 +3520,7 @@
     </row>
     <row r="68" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="24" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C68" s="24"/>
       <c r="D68" s="24"/>
@@ -3515,7 +3531,7 @@
     </row>
     <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="24" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C69" s="24"/>
       <c r="D69" s="24"/>
@@ -3588,7 +3604,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -3597,12 +3613,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -3610,90 +3626,90 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>32500</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>700</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C8" s="14" t="n">
         <v>0.61</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>0.85</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>1170</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>1560</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>1820</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>3110</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3704,34 +3720,34 @@
         <v>2340</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C15" s="25" t="n">
         <v>0.00127</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C16" s="14" t="n">
         <v>0.07</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -3739,107 +3755,107 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>6500</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>1500</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>200</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>500</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>50</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>1080</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>1175</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>1250</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C26" s="26" t="n">
         <f aca="false">0.2*11+0.4*11+2*14+6*11+6*5+6*10</f>
         <v>190.6</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -3847,51 +3863,51 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>600</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>700</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>1000</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="0" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1800</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -3899,73 +3915,73 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>6400</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>13500</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="0" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>200</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="0" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>1700</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>6300</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>0.37</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -3973,117 +3989,117 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="0" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>5.5</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C41" s="9" t="n">
         <v>7</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>7</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C44" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C45" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C46" s="13" t="n">
         <v>2400</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>5</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>5</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
@@ -4091,84 +4107,84 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="0" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>50</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="0" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>20</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="0" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>650</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="0" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>12</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C55" s="26" t="n">
         <v>9.4</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="0" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C57" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
@@ -4176,62 +4192,62 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="0" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C59" s="13" t="n">
         <v>500</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="0" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>400</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C61" s="13" t="n">
         <v>350</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C62" s="13" t="n">
         <v>45</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="0" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C63" s="13" t="n">
         <v>130</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
@@ -4239,40 +4255,40 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="0" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C65" s="14" t="n">
         <v>0.005</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="0" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C66" s="14" t="n">
         <v>0.025</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="0" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C67" s="14" t="n">
         <v>0.14</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
@@ -4280,13 +4296,13 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4390,7 +4406,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
@@ -4399,24 +4415,24 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="0" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C83" s="29" t="n">
         <v>45</v>
@@ -4428,12 +4444,12 @@
         <v>9.6</v>
       </c>
       <c r="F83" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="0" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C84" s="29" t="n">
         <v>8</v>
@@ -4445,12 +4461,12 @@
         <v>4</v>
       </c>
       <c r="F84" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="0" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C85" s="29" t="n">
         <v>36</v>
@@ -4462,12 +4478,12 @@
         <v>2</v>
       </c>
       <c r="F85" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="0" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C86" s="29" t="n">
         <v>90</v>
@@ -4479,12 +4495,12 @@
         <v>2</v>
       </c>
       <c r="F86" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="0" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C87" s="29" t="n">
         <v>207.28</v>
@@ -4496,12 +4512,12 @@
         <v>2</v>
       </c>
       <c r="F87" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="0" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C88" s="29" t="n">
         <v>40.14</v>
@@ -4513,12 +4529,12 @@
         <v>2</v>
       </c>
       <c r="F88" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="0" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C89" s="29" t="n">
         <v>3.3</v>
@@ -4530,12 +4546,12 @@
         <v>2</v>
       </c>
       <c r="F89" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="0" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C90" s="29" t="n">
         <v>10.8</v>
@@ -4547,12 +4563,12 @@
         <v>2</v>
       </c>
       <c r="F90" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="0" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C91" s="29" t="n">
         <v>10.95</v>
@@ -4564,12 +4580,12 @@
         <v>2</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="0" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C92" s="29" t="n">
         <v>3.81</v>
@@ -4581,12 +4597,12 @@
         <v>2</v>
       </c>
       <c r="F92" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="0" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C93" s="29" t="n">
         <v>2.84</v>
@@ -4598,12 +4614,12 @@
         <v>4</v>
       </c>
       <c r="F93" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="0" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C94" s="29" t="n">
         <v>4.4</v>
@@ -4615,12 +4631,12 @@
         <v>4</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="0" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C95" s="29" t="n">
         <f aca="false">2*25.71+2*22.85</f>
@@ -4633,12 +4649,12 @@
         <v>1</v>
       </c>
       <c r="F95" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="0" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C96" s="29" t="n">
         <v>345</v>
@@ -4650,12 +4666,12 @@
         <v>0</v>
       </c>
       <c r="F96" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C97" s="29" t="n">
         <v>546</v>
@@ -4667,12 +4683,12 @@
         <v>1</v>
       </c>
       <c r="F97" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C98" s="29" t="n">
         <v>2.98</v>
@@ -4684,12 +4700,12 @@
         <v>208</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="0" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C99" s="29" t="n">
         <f aca="false">3.09+4.99</f>
@@ -4702,12 +4718,12 @@
         <v>20</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C100" s="29" t="n">
         <v>5.4</v>
@@ -4719,12 +4735,12 @@
         <v>1</v>
       </c>
       <c r="F100" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="0" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C101" s="29" t="n">
         <v>300</v>
@@ -4736,12 +4752,12 @@
         <v>1</v>
       </c>
       <c r="F101" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="0" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C102" s="29" t="n">
         <v>40</v>
@@ -4753,12 +4769,12 @@
         <v>1</v>
       </c>
       <c r="F102" s="30" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="0" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C103" s="29" t="n">
         <v>172</v>
@@ -4770,12 +4786,12 @@
         <v>0</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="0" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C104" s="29" t="n">
         <v>207</v>
@@ -4787,12 +4803,12 @@
         <v>1</v>
       </c>
       <c r="F104" s="30" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="0" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C105" s="29" t="n">
         <f aca="false">120+55+65</f>
@@ -4805,12 +4821,12 @@
         <v>1</v>
       </c>
       <c r="F105" s="30" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="0" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C106" s="29" t="n">
         <f aca="false">50+40</f>
@@ -4823,12 +4839,12 @@
         <v>1</v>
       </c>
       <c r="F106" s="30" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C107" s="29" t="n">
         <f aca="false">14+9+25+5+9+30</f>
@@ -4841,12 +4857,12 @@
         <v>0</v>
       </c>
       <c r="F107" s="30" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C108" s="29" t="n">
         <f aca="false">14+18+25+7+18+30</f>
@@ -4859,12 +4875,12 @@
         <v>1</v>
       </c>
       <c r="F108" s="30" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C109" s="29" t="n">
         <f aca="false">70+14+34+32+20</f>
@@ -4877,7 +4893,7 @@
         <v>1</v>
       </c>
       <c r="F109" s="30" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -4908,7 +4924,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -4925,13 +4941,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C5" s="31" t="n">
         <f aca="false">c_cena_D+IF(in_typ="NK37",c_doplata_NK37,0)</f>
@@ -4940,7 +4956,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C6" s="31" t="n">
         <f aca="false">c_wsp_S*m_cena_D</f>
@@ -4949,7 +4965,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C7" s="31" t="n">
         <f aca="false">c_wsp_NP*m_cena_D</f>
@@ -4958,7 +4974,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C8" s="32" t="n">
         <f aca="false">in_D+in_NP</f>
@@ -4967,7 +4983,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C9" s="32" t="n">
         <f aca="false">in_S+in_D+in_NP</f>
@@ -4976,7 +4992,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C10" s="32" t="n">
         <f aca="false">2*in_S+2*in_NP+4*in_D</f>
@@ -4985,7 +5001,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C11" s="31" t="n">
         <f aca="false">m_cena_S*in_S+c_szer_260*in_szer1_S+c_szer_270*in_szer2_S+SUMPRODUCT(in_gl_S,t_gl_doplata)+c_dl_500*in_dl500_S+CEILING(m_cena_S*c_dl_wsp*10,100)*in_dl540_S+CEILING(m_cena_S*c_dl_wsp*20,100)*in_dl550_S</f>
@@ -4994,7 +5010,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C12" s="31" t="n">
         <f aca="false">m_cena_D*in_D+c_szer_520*in_szer1_D+c_szer_540*in_szer2_D+SUMPRODUCT(in_gl_D,t_gl_doplata)+c_dl_500*in_dl500_D+m_cena_D*c_dl_wsp*10*in_dl540_D+m_cena_D*c_dl_wsp*20*in_dl550_D</f>
@@ -5003,7 +5019,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C13" s="31" t="n">
         <f aca="false">m_cena_NP*in_NP</f>
@@ -5012,7 +5028,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C14" s="32" t="n">
         <f aca="false">SUMPRODUCT((t_gl_silownik=2000)*(in_gl_S+in_gl_D))</f>
@@ -5021,7 +5037,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C15" s="32" t="n">
         <f aca="false">SUMPRODUCT((t_gl_silownik=2250)*(in_gl_S+in_gl_D))</f>
@@ -5030,7 +5046,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C16" s="32" t="n">
         <f aca="false">m_platformy-m_sil_2000-m_sil_2250</f>
@@ -5039,7 +5055,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C17" s="31" t="n">
         <f aca="false">in_agregaty*(c_agregat+c_hydr_drobne+c_olej+c_transp_agregatu)+m_platformy*c_transp_silownikow+2*(c_sil_1700*m_sil_std+c_sil_2000*m_sil_2000+c_sil_2250*m_sil_2250)+in_magistrala*c_magistrala+SUMPRODUCT((t_sk_grupa="Hydraulika")*t_sk_cena*(t_sk_S*in_S+t_sk_D*m_DN))</f>
@@ -5048,7 +5064,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C18" s="31" t="n">
         <f aca="false">in_barierki*c_barierka+in_maskownice*c_maskownica</f>
@@ -5057,7 +5073,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C19" s="31" t="n">
         <f aca="false">in_agregaty*c_skrzynka_zasil+SUMPRODUCT((t_sk_grupa="Elektryka")*t_sk_cena*(t_sk_S*in_S+t_sk_D*m_DN))</f>
@@ -5066,7 +5082,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C20" s="31" t="n">
         <f aca="false">in_agregaty*c_admin+SUMPRODUCT((t_sk_grupa="Mechanika")*t_sk_cena*(t_sk_S*in_S+t_sk_D*m_DN))</f>
@@ -5075,7 +5091,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="11" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C21" s="33" t="n">
         <f aca="false">m_plat_S+m_plat_D+m_plat_NP+m_hydraulika+m_barierki+m_elektryka+m_mechanika</f>
@@ -5084,7 +5100,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="11" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C22" s="33" t="n">
         <f aca="false">m_suma_2000*(1+in_q2500)</f>
@@ -5093,7 +5109,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C23" s="31" t="n">
         <f aca="false">c_mal_S*in_S+c_mal_D*m_DN+c_mal_bar*in_barierki</f>
@@ -5102,7 +5118,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C24" s="34" t="n">
         <f aca="false">ROUNDUP(in_magistrala*c_osd_magistrala+(in_barierki+in_maskownice)*c_osd_barierka,0)</f>
@@ -5111,7 +5127,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C25" s="34" t="n">
         <f aca="false">m_utr_auto+in_utr_dod</f>
@@ -5120,13 +5136,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C28" s="35" t="b">
         <f aca="false">in_lok="Kraków"</f>
@@ -5135,7 +5151,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C29" s="34" t="n">
         <f aca="false">IF(ISBLANK(in_km_pom),IF(e_krk,c_km_krakow,in_km),in_km_pom)</f>
@@ -5144,7 +5160,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C30" s="34" t="n">
         <f aca="false">IF(ISBLANK(in_km_mon),IF(e_krk,c_km_krakow,in_km+c_km_dodatek),in_km_mon)</f>
@@ -5153,7 +5169,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C31" s="34" t="n">
         <f aca="false">IF(ISBLANK(in_rozl_dni),c_rozl_TIR*in_tir,in_rozl_dni)</f>
@@ -5162,7 +5178,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="0" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C32" s="34" t="n">
         <f aca="false">(c_pomiary_osoby+c_odbiory_osoby)*IF(in_wzor="Uproszczony",2*e_km_pom/c_km_dzien*1,(1+0.1*MAX(0,800-e_km_pom)/100)*e_km_pom*1/500)</f>
@@ -5171,7 +5187,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">ROUNDUP(m_DN/c_dzwig_D+in_S*c_dzwig_wspS/c_dzwig_D,0)</f>
@@ -5180,7 +5196,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C34" s="36" t="n">
         <f aca="false">(1+c_podatek*(c_gdw+in_zysk))/(1-(c_kob+c_gdw+in_zysk))</f>
@@ -5189,7 +5205,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -5198,7 +5214,7 @@
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
@@ -5208,42 +5224,42 @@
     </row>
     <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="11" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D37" s="37" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E37" s="37" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J37" s="37" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K37" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L37" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M37" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N37" s="37" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D38" s="32" t="n">
         <v>0</v>
@@ -5284,7 +5300,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="0" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D39" s="32" t="n">
         <v>0</v>
@@ -5325,7 +5341,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D40" s="32" t="n">
         <f aca="false">in_osoby</f>
@@ -5364,7 +5380,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D41" s="31" t="n">
         <f aca="false">(c_stawka_1+IF(D40&gt;=2,c_stawka_2,0)+MAX(0,D40-2)*c_stawka_n)/D40</f>
@@ -5409,7 +5425,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="0" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D42" s="34" t="n">
         <f aca="false">c_osd_S*in_S+c_osd_D*in_D+c_osd_NP*in_NP+m_utr+D39*c_slupek_rbd*m_MP</f>
@@ -5454,7 +5470,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="0" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D43" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*1,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*1/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*1,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*1/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5499,7 +5515,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="0" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D44" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D43,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D43/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D43,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D43/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5544,7 +5560,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="0" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D45" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D44,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D44/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D44,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D44/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5589,7 +5605,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="0" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D46" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D45,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D45/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D45,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D45/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5634,7 +5650,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="0" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D47" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D46,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D46/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D46,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D46/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5679,7 +5695,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="11" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D48" s="38" t="n">
         <f aca="false">IF(ISBLANK(in_wyjazdy),D47,in_wyjazdy)</f>
@@ -5724,7 +5740,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="0" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D49" s="34" t="n">
         <f aca="false">(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D48,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D48/500)))</f>
@@ -5769,7 +5785,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D50" s="34" t="n">
         <f aca="false">D42+D49</f>
@@ -5814,7 +5830,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="11" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D51" s="38" t="n">
         <f aca="false">CEILING(D50/D40,1)</f>
@@ -5859,7 +5875,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D52" s="38" t="n">
         <f aca="false">IF(e_krk,CEILING(D51/c_dni_tydzien,1),D48)</f>
@@ -5904,7 +5920,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="0" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D53" s="34" t="n">
         <f aca="false">2*(e_km_mon*D48+2*e_km_pom)</f>
@@ -5949,7 +5965,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D54" s="31" t="n">
         <f aca="false">IF(D38=1,m_suma_2500,m_suma_2000)</f>
@@ -5994,7 +6010,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D55" s="31" t="n">
         <f aca="false">D39*c_slupek*m_MP</f>
@@ -6039,7 +6055,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="0" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D56" s="31" t="n">
         <f aca="false">D53/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
@@ -6084,7 +6100,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="0" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D57" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_hotel*(D51+1)*D40)</f>
@@ -6129,7 +6145,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="0" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D58" s="31" t="n">
         <f aca="false">in_tir_cena*in_tir</f>
@@ -6174,52 +6190,52 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="0" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D59" s="31" t="n">
-        <f aca="false">c_dzwig*e_dzw_dni</f>
+        <f aca="false">IF(ISBLANK(in_dzwig_koszt),c_dzwig*e_dzw_dni,in_dzwig_koszt)</f>
         <v>7200</v>
       </c>
       <c r="E59" s="31" t="n">
-        <f aca="false">c_dzwig*e_dzw_dni</f>
+        <f aca="false">IF(ISBLANK(in_dzwig_koszt),c_dzwig*e_dzw_dni,in_dzwig_koszt)</f>
         <v>7200</v>
       </c>
       <c r="F59" s="31" t="n">
-        <f aca="false">c_dzwig*e_dzw_dni</f>
+        <f aca="false">IF(ISBLANK(in_dzwig_koszt),c_dzwig*e_dzw_dni,in_dzwig_koszt)</f>
         <v>7200</v>
       </c>
       <c r="G59" s="31" t="n">
-        <f aca="false">c_dzwig*e_dzw_dni</f>
+        <f aca="false">IF(ISBLANK(in_dzwig_koszt),c_dzwig*e_dzw_dni,in_dzwig_koszt)</f>
         <v>7200</v>
       </c>
       <c r="I59" s="31" t="n">
-        <f aca="false">c_dzwig*e_dzw_dni</f>
+        <f aca="false">IF(ISBLANK(in_dzwig_koszt),c_dzwig*e_dzw_dni,in_dzwig_koszt)</f>
         <v>7200</v>
       </c>
       <c r="J59" s="31" t="n">
-        <f aca="false">c_dzwig*e_dzw_dni</f>
+        <f aca="false">IF(ISBLANK(in_dzwig_koszt),c_dzwig*e_dzw_dni,in_dzwig_koszt)</f>
         <v>7200</v>
       </c>
       <c r="K59" s="31" t="n">
-        <f aca="false">c_dzwig*e_dzw_dni</f>
+        <f aca="false">IF(ISBLANK(in_dzwig_koszt),c_dzwig*e_dzw_dni,in_dzwig_koszt)</f>
         <v>7200</v>
       </c>
       <c r="L59" s="31" t="n">
-        <f aca="false">c_dzwig*e_dzw_dni</f>
+        <f aca="false">IF(ISBLANK(in_dzwig_koszt),c_dzwig*e_dzw_dni,in_dzwig_koszt)</f>
         <v>7200</v>
       </c>
       <c r="M59" s="31" t="n">
-        <f aca="false">c_dzwig*e_dzw_dni</f>
+        <f aca="false">IF(ISBLANK(in_dzwig_koszt),c_dzwig*e_dzw_dni,in_dzwig_koszt)</f>
         <v>7200</v>
       </c>
       <c r="N59" s="31" t="n">
-        <f aca="false">c_dzwig*e_dzw_dni</f>
+        <f aca="false">IF(ISBLANK(in_dzwig_koszt),c_dzwig*e_dzw_dni,in_dzwig_koszt)</f>
         <v>7200</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="0" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D60" s="31" t="n">
         <f aca="false">in_rozl_cena</f>
@@ -6264,7 +6280,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="0" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D61" s="31" t="n">
         <f aca="false">D41*e_rozl_dni*D40</f>
@@ -6309,7 +6325,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D62" s="31" t="n">
         <f aca="false">D41*(D49-D40*e_rozl_dni)</f>
@@ -6354,7 +6370,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D63" s="31" t="n">
         <f aca="false">IF(D48&gt;0,D41*D42,0)</f>
@@ -6399,7 +6415,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D64" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_dieta*D50)</f>
@@ -6444,7 +6460,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D65" s="33" t="n">
         <f aca="false">SUM(D54:D64)</f>
@@ -6489,7 +6505,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D66" s="31" t="n">
         <f aca="false">D65/(1-(c_kob+c_gdw+in_zysk))</f>
@@ -6534,7 +6550,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="0" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D67" s="31" t="n">
         <f aca="false">D66*c_kob</f>
@@ -6579,7 +6595,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="0" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D68" s="31" t="n">
         <f aca="false">D66*c_gdw</f>
@@ -6624,7 +6640,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="0" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D69" s="31" t="n">
         <f aca="false">D66*in_zysk</f>
@@ -6669,7 +6685,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="0" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D70" s="31" t="n">
         <f aca="false">c_podatek*(D61+D62+D63+D64+D68+D69)</f>
@@ -6714,7 +6730,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D71" s="33" t="n">
         <f aca="false">D66+D70</f>
@@ -6759,7 +6775,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="0" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D72" s="31" t="n">
         <f aca="false">D71-D69</f>
@@ -6804,7 +6820,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D73" s="31" t="n">
         <f aca="false">IF(m_MP&gt;0,D71/m_MP,0)</f>
@@ -6849,7 +6865,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="0" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D74" s="39" t="n">
         <f aca="false">D73/in_eur</f>
@@ -6894,7 +6910,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D75" s="31" t="n">
         <f aca="false">D65/(1-(c_kob+c_gdw+in_zysk2))</f>
@@ -6939,7 +6955,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="0" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D76" s="31" t="n">
         <f aca="false">D75*in_zysk2</f>
@@ -6984,7 +7000,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="11" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D77" s="33" t="n">
         <f aca="false">D75+c_podatek*(D61+D62+D63+D64+D75*(c_gdw+in_zysk2))</f>
@@ -7029,7 +7045,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D78" s="31" t="n">
         <f aca="false">IF(m_MP&gt;0,D77/m_MP,0)</f>

--- a/kalkulator-nk38/Kalkulator_NK38_v1_przyklad_WAW.xlsx
+++ b/kalkulator-nk38/Kalkulator_NK38_v1_przyklad_WAW.xlsx
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="363">
   <si>
     <t xml:space="preserve">KALKULATOR NK38 - DANE WEJŚCIOWE</t>
   </si>
@@ -423,6 +423,9 @@
     <t xml:space="preserve">Cena za MP [EUR] - zysk A</t>
   </si>
   <si>
+    <t xml:space="preserve">Zysk z narzutem A [zł]</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zysk A [zł]</t>
   </si>
   <si>
@@ -1231,6 +1234,9 @@
   </si>
   <si>
     <t xml:space="preserve">Koszt rzeczywisty (dawne K43)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zysk z narzutem (dawne J44 = zysk + GDW)</t>
   </si>
   <si>
     <t xml:space="preserve">Cena za MP [EUR]</t>
@@ -2556,7 +2562,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:H69"/>
+  <dimension ref="B2:H70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -2633,19 +2639,19 @@
         <v>CENA NETTO - ZYSK B 10.0%</v>
       </c>
       <c r="C8" s="18" t="n">
-        <f aca="false">Obliczenia!D77</f>
+        <f aca="false">Obliczenia!D78</f>
         <v>921791.99146069</v>
       </c>
       <c r="D8" s="18" t="n">
-        <f aca="false">Obliczenia!E77</f>
+        <f aca="false">Obliczenia!E78</f>
         <v>967338.070288276</v>
       </c>
       <c r="E8" s="18" t="n">
-        <f aca="false">Obliczenia!F77</f>
+        <f aca="false">Obliczenia!F78</f>
         <v>1060804.76981793</v>
       </c>
       <c r="F8" s="18" t="n">
-        <f aca="false">Obliczenia!G77</f>
+        <f aca="false">Obliczenia!G78</f>
         <v>1106350.84864552</v>
       </c>
     </row>
@@ -2654,19 +2660,19 @@
         <v>84</v>
       </c>
       <c r="C9" s="19" t="n">
-        <f aca="false">Obliczenia!D73</f>
+        <f aca="false">Obliczenia!D74</f>
         <v>15866.3470112584</v>
       </c>
       <c r="D9" s="19" t="n">
-        <f aca="false">Obliczenia!E73</f>
+        <f aca="false">Obliczenia!E74</f>
         <v>16650.5953563471</v>
       </c>
       <c r="E9" s="19" t="n">
-        <f aca="false">Obliczenia!F73</f>
+        <f aca="false">Obliczenia!F74</f>
         <v>18259.0816753767</v>
       </c>
       <c r="F9" s="19" t="n">
-        <f aca="false">Obliczenia!G73</f>
+        <f aca="false">Obliczenia!G74</f>
         <v>19043.3300204655</v>
       </c>
     </row>
@@ -2675,19 +2681,19 @@
         <v>85</v>
       </c>
       <c r="C10" s="19" t="n">
-        <f aca="false">Obliczenia!D78</f>
+        <f aca="false">Obliczenia!D79</f>
         <v>15363.1998576782</v>
       </c>
       <c r="D10" s="19" t="n">
-        <f aca="false">Obliczenia!E78</f>
+        <f aca="false">Obliczenia!E79</f>
         <v>16122.3011714713</v>
       </c>
       <c r="E10" s="19" t="n">
-        <f aca="false">Obliczenia!F78</f>
+        <f aca="false">Obliczenia!F79</f>
         <v>17680.0794969655</v>
       </c>
       <c r="F10" s="19" t="n">
-        <f aca="false">Obliczenia!G78</f>
+        <f aca="false">Obliczenia!G79</f>
         <v>18439.1808107586</v>
       </c>
     </row>
@@ -2696,19 +2702,19 @@
         <v>86</v>
       </c>
       <c r="C11" s="20" t="n">
-        <f aca="false">Obliczenia!D74</f>
+        <f aca="false">Obliczenia!D75</f>
         <v>3668.51954017535</v>
       </c>
       <c r="D11" s="20" t="n">
-        <f aca="false">Obliczenia!E74</f>
+        <f aca="false">Obliczenia!E75</f>
         <v>3849.8486373057</v>
       </c>
       <c r="E11" s="20" t="n">
-        <f aca="false">Obliczenia!F74</f>
+        <f aca="false">Obliczenia!F75</f>
         <v>4221.75298852641</v>
       </c>
       <c r="F11" s="20" t="n">
-        <f aca="false">Obliczenia!G74</f>
+        <f aca="false">Obliczenia!G75</f>
         <v>4403.08208565676</v>
       </c>
     </row>
@@ -2717,20 +2723,20 @@
         <v>87</v>
       </c>
       <c r="C12" s="19" t="n">
-        <f aca="false">Obliczenia!D69</f>
-        <v>115264.993491124</v>
+        <f aca="false">Obliczenia!D73</f>
+        <v>138317.992189349</v>
       </c>
       <c r="D12" s="19" t="n">
-        <f aca="false">Obliczenia!E69</f>
-        <v>121025.877514793</v>
+        <f aca="false">Obliczenia!E73</f>
+        <v>145231.053017752</v>
       </c>
       <c r="E12" s="19" t="n">
-        <f aca="false">Obliczenia!F69</f>
-        <v>132642.472189349</v>
+        <f aca="false">Obliczenia!F73</f>
+        <v>159170.966627219</v>
       </c>
       <c r="F12" s="19" t="n">
-        <f aca="false">Obliczenia!G69</f>
-        <v>138403.356213018</v>
+        <f aca="false">Obliczenia!G73</f>
+        <v>166084.027455621</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2738,20 +2744,20 @@
         <v>88</v>
       </c>
       <c r="C13" s="19" t="n">
-        <f aca="false">Obliczenia!D76</f>
-        <v>89562.2248275862</v>
+        <f aca="false">Obliczenia!D69</f>
+        <v>115264.993491124</v>
       </c>
       <c r="D13" s="19" t="n">
-        <f aca="false">Obliczenia!E76</f>
-        <v>94038.4979310345</v>
+        <f aca="false">Obliczenia!E69</f>
+        <v>121025.877514793</v>
       </c>
       <c r="E13" s="19" t="n">
-        <f aca="false">Obliczenia!F76</f>
-        <v>103064.725517241</v>
+        <f aca="false">Obliczenia!F69</f>
+        <v>132642.472189349</v>
       </c>
       <c r="F13" s="19" t="n">
-        <f aca="false">Obliczenia!G76</f>
-        <v>107540.99862069</v>
+        <f aca="false">Obliczenia!G69</f>
+        <v>138403.356213018</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2759,41 +2765,41 @@
         <v>89</v>
       </c>
       <c r="C14" s="19" t="n">
+        <f aca="false">Obliczenia!D77</f>
+        <v>89562.2248275862</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <f aca="false">Obliczenia!E77</f>
+        <v>94038.4979310345</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <f aca="false">Obliczenia!F77</f>
+        <v>103064.725517241</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <f aca="false">Obliczenia!G77</f>
+        <v>107540.99862069</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="19" t="n">
         <f aca="false">Obliczenia!D72</f>
-        <v>836715.827184379</v>
-      </c>
-      <c r="D14" s="19" t="n">
+        <v>813662.828486154</v>
+      </c>
+      <c r="D15" s="19" t="n">
         <f aca="false">Obliczenia!E72</f>
-        <v>878009.843866036</v>
-      </c>
-      <c r="E14" s="19" t="n">
+        <v>853804.668363077</v>
+      </c>
+      <c r="E15" s="19" t="n">
         <f aca="false">Obliczenia!F72</f>
-        <v>962902.428333255</v>
-      </c>
-      <c r="F14" s="19" t="n">
+        <v>936373.933895385</v>
+      </c>
+      <c r="F15" s="19" t="n">
         <f aca="false">Obliczenia!G72</f>
-        <v>1004196.44501491</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="19" t="n">
-        <f aca="false">Obliczenia!D54</f>
-        <v>649059.6</v>
-      </c>
-      <c r="D16" s="19" t="n">
-        <f aca="false">Obliczenia!E54</f>
-        <v>688003.176</v>
-      </c>
-      <c r="E16" s="19" t="n">
-        <f aca="false">Obliczenia!F54</f>
-        <v>649059.6</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <f aca="false">Obliczenia!G54</f>
-        <v>688003.176</v>
+        <v>976515.773772308</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2801,20 +2807,20 @@
         <v>91</v>
       </c>
       <c r="C17" s="19" t="n">
-        <f aca="false">Obliczenia!D55</f>
-        <v>0</v>
+        <f aca="false">Obliczenia!D54</f>
+        <v>649059.6</v>
       </c>
       <c r="D17" s="19" t="n">
-        <f aca="false">Obliczenia!E55</f>
-        <v>0</v>
+        <f aca="false">Obliczenia!E54</f>
+        <v>688003.176</v>
       </c>
       <c r="E17" s="19" t="n">
-        <f aca="false">Obliczenia!F55</f>
-        <v>102000</v>
+        <f aca="false">Obliczenia!F54</f>
+        <v>649059.6</v>
       </c>
       <c r="F17" s="19" t="n">
-        <f aca="false">Obliczenia!G55</f>
-        <v>102000</v>
+        <f aca="false">Obliczenia!G54</f>
+        <v>688003.176</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2822,20 +2828,20 @@
         <v>92</v>
       </c>
       <c r="C18" s="19" t="n">
-        <f aca="false">Obliczenia!D58+Obliczenia!D59+Obliczenia!D60</f>
-        <v>24300</v>
+        <f aca="false">Obliczenia!D55</f>
+        <v>0</v>
       </c>
       <c r="D18" s="19" t="n">
-        <f aca="false">Obliczenia!E58+Obliczenia!E59+Obliczenia!E60</f>
-        <v>24300</v>
+        <f aca="false">Obliczenia!E55</f>
+        <v>0</v>
       </c>
       <c r="E18" s="19" t="n">
-        <f aca="false">Obliczenia!F58+Obliczenia!F59+Obliczenia!F60</f>
-        <v>24300</v>
+        <f aca="false">Obliczenia!F55</f>
+        <v>102000</v>
       </c>
       <c r="F18" s="19" t="n">
-        <f aca="false">Obliczenia!G58+Obliczenia!G59+Obliczenia!G60</f>
-        <v>24300</v>
+        <f aca="false">Obliczenia!G55</f>
+        <v>102000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2843,20 +2849,20 @@
         <v>93</v>
       </c>
       <c r="C19" s="19" t="n">
-        <f aca="false">Obliczenia!D63+Obliczenia!D61+Obliczenia!D62</f>
-        <v>67392.32</v>
+        <f aca="false">Obliczenia!D58+Obliczenia!D59+Obliczenia!D60</f>
+        <v>24300</v>
       </c>
       <c r="D19" s="19" t="n">
-        <f aca="false">Obliczenia!E63+Obliczenia!E61+Obliczenia!E62</f>
-        <v>67392.32</v>
+        <f aca="false">Obliczenia!E58+Obliczenia!E59+Obliczenia!E60</f>
+        <v>24300</v>
       </c>
       <c r="E19" s="19" t="n">
-        <f aca="false">Obliczenia!F63+Obliczenia!F61+Obliczenia!F62</f>
-        <v>77824.64</v>
+        <f aca="false">Obliczenia!F58+Obliczenia!F59+Obliczenia!F60</f>
+        <v>24300</v>
       </c>
       <c r="F19" s="19" t="n">
-        <f aca="false">Obliczenia!G63+Obliczenia!G61+Obliczenia!G62</f>
-        <v>77824.64</v>
+        <f aca="false">Obliczenia!G58+Obliczenia!G59+Obliczenia!G60</f>
+        <v>24300</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2864,20 +2870,20 @@
         <v>94</v>
       </c>
       <c r="C20" s="19" t="n">
-        <f aca="false">Obliczenia!D57+Obliczenia!D64+Obliczenia!D56</f>
-        <v>38439.436</v>
+        <f aca="false">Obliczenia!D63+Obliczenia!D61+Obliczenia!D62</f>
+        <v>67392.32</v>
       </c>
       <c r="D20" s="19" t="n">
-        <f aca="false">Obliczenia!E57+Obliczenia!E64+Obliczenia!E56</f>
-        <v>38439.436</v>
+        <f aca="false">Obliczenia!E63+Obliczenia!E61+Obliczenia!E62</f>
+        <v>67392.32</v>
       </c>
       <c r="E20" s="19" t="n">
-        <f aca="false">Obliczenia!F57+Obliczenia!F64+Obliczenia!F56</f>
-        <v>43478.872</v>
+        <f aca="false">Obliczenia!F63+Obliczenia!F61+Obliczenia!F62</f>
+        <v>77824.64</v>
       </c>
       <c r="F20" s="19" t="n">
-        <f aca="false">Obliczenia!G57+Obliczenia!G64+Obliczenia!G56</f>
-        <v>43478.872</v>
+        <f aca="false">Obliczenia!G63+Obliczenia!G61+Obliczenia!G62</f>
+        <v>77824.64</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2885,41 +2891,41 @@
         <v>95</v>
       </c>
       <c r="C21" s="19" t="n">
+        <f aca="false">Obliczenia!D57+Obliczenia!D64+Obliczenia!D56</f>
+        <v>38439.436</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <f aca="false">Obliczenia!E57+Obliczenia!E64+Obliczenia!E56</f>
+        <v>38439.436</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <f aca="false">Obliczenia!F57+Obliczenia!F64+Obliczenia!F56</f>
+        <v>43478.872</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <f aca="false">Obliczenia!G57+Obliczenia!G64+Obliczenia!G56</f>
+        <v>43478.872</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="19" t="n">
         <f aca="false">Obliczenia!D67+Obliczenia!D68+Obliczenia!D70</f>
         <v>57524.4711843787</v>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D22" s="19" t="n">
         <f aca="false">Obliczenia!E67+Obliczenia!E68+Obliczenia!E70</f>
         <v>59874.9118660355</v>
       </c>
-      <c r="E21" s="19" t="n">
+      <c r="E22" s="19" t="n">
         <f aca="false">Obliczenia!F67+Obliczenia!F68+Obliczenia!F70</f>
         <v>66239.3163332545</v>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F22" s="19" t="n">
         <f aca="false">Obliczenia!G67+Obliczenia!G68+Obliczenia!G70</f>
         <v>68589.7570149112</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="21" t="n">
-        <f aca="false">Obliczenia!D51</f>
-        <v>43</v>
-      </c>
-      <c r="D23" s="21" t="n">
-        <f aca="false">Obliczenia!E51</f>
-        <v>43</v>
-      </c>
-      <c r="E23" s="21" t="n">
-        <f aca="false">Obliczenia!F51</f>
-        <v>49</v>
-      </c>
-      <c r="F23" s="21" t="n">
-        <f aca="false">Obliczenia!G51</f>
-        <v>49</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2927,65 +2933,73 @@
         <v>97</v>
       </c>
       <c r="C24" s="21" t="n">
+        <f aca="false">Obliczenia!D51</f>
+        <v>43</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <f aca="false">Obliczenia!E51</f>
+        <v>43</v>
+      </c>
+      <c r="E24" s="21" t="n">
+        <f aca="false">Obliczenia!F51</f>
+        <v>49</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <f aca="false">Obliczenia!G51</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="21" t="n">
         <f aca="false">Obliczenia!D52</f>
         <v>9</v>
       </c>
-      <c r="D24" s="21" t="n">
+      <c r="D25" s="21" t="n">
         <f aca="false">Obliczenia!E52</f>
         <v>9</v>
       </c>
-      <c r="E24" s="21" t="n">
+      <c r="E25" s="21" t="n">
         <f aca="false">Obliczenia!F52</f>
         <v>10</v>
       </c>
-      <c r="F24" s="21" t="n">
+      <c r="F25" s="21" t="n">
         <f aca="false">Obliczenia!G52</f>
         <v>10</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" s="22" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="22" t="n">
         <f aca="false">Obliczenia!D50</f>
         <v>168.4808</v>
       </c>
-      <c r="D25" s="22" t="n">
+      <c r="D26" s="22" t="n">
         <f aca="false">Obliczenia!E50</f>
         <v>168.4808</v>
       </c>
-      <c r="E25" s="22" t="n">
+      <c r="E26" s="22" t="n">
         <f aca="false">Obliczenia!F50</f>
         <v>194.5616</v>
       </c>
-      <c r="F25" s="22" t="n">
+      <c r="F26" s="22" t="n">
         <f aca="false">Obliczenia!G50</f>
         <v>194.5616</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C27" s="4" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="C28" s="4" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="0" t="s">
+      <c r="D28" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="C28" s="19" t="n">
-        <f aca="false">Obliczenia!F71-Obliczenia!D71</f>
-        <v>143564.079847101</v>
-      </c>
-      <c r="D28" s="19" t="n">
-        <f aca="false">Obliczenia!G71-Obliczenia!E71</f>
-        <v>143564.0798471</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2993,12 +3007,12 @@
         <v>103</v>
       </c>
       <c r="C29" s="19" t="n">
-        <f aca="false">Obliczenia!F71-Obliczenia!D71+(c_slupek22-c_slupek)*m_MP*e_mnoznik</f>
-        <v>477050.470379645</v>
+        <f aca="false">Obliczenia!F71-Obliczenia!D71</f>
+        <v>143564.079847101</v>
       </c>
       <c r="D29" s="19" t="n">
-        <f aca="false">Obliczenia!G71-Obliczenia!E71+(c_slupek22-c_slupek)*m_MP*e_mnoznik</f>
-        <v>477050.470379645</v>
+        <f aca="false">Obliczenia!G71-Obliczenia!E71</f>
+        <v>143564.0798471</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3006,70 +3020,54 @@
         <v>104</v>
       </c>
       <c r="C30" s="19" t="n">
+        <f aca="false">Obliczenia!F71-Obliczenia!D71+(c_slupek22-c_slupek)*m_MP*e_mnoznik</f>
+        <v>477050.470379645</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <f aca="false">Obliczenia!G71-Obliczenia!E71+(c_slupek22-c_slupek)*m_MP*e_mnoznik</f>
+        <v>477050.470379645</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="19" t="n">
         <f aca="false">m_malowanie*e_mnoznik</f>
         <v>251927.218934911</v>
       </c>
-      <c r="D30" s="19" t="n">
+      <c r="D31" s="19" t="n">
         <f aca="false">m_malowanie*e_mnoznik</f>
         <v>251927.218934911</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="11" t="str">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="11" t="str">
         <f aca="false">"Analiza liczby osób - wariant: "&amp;in_analiza</f>
         <v>Analiza liczby osób - wariant: 2000 kg</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C33" s="17" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="C34" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="D34" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="E34" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="G33" s="17" t="s">
+      <c r="F34" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="H33" s="17" t="s">
+      <c r="G34" s="17" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="0" t="s">
+      <c r="H34" s="17" t="s">
         <v>112</v>
-      </c>
-      <c r="C34" s="19" t="n">
-        <f aca="false">Obliczenia!I71</f>
-        <v>965679.929906982</v>
-      </c>
-      <c r="D34" s="19" t="n">
-        <f aca="false">Obliczenia!J71</f>
-        <v>953567.068923511</v>
-      </c>
-      <c r="E34" s="19" t="n">
-        <f aca="false">Obliczenia!K71</f>
-        <v>951980.820675503</v>
-      </c>
-      <c r="F34" s="19" t="n">
-        <f aca="false">Obliczenia!L71</f>
-        <v>948060.597174319</v>
-      </c>
-      <c r="G34" s="19" t="n">
-        <f aca="false">Obliczenia!M71</f>
-        <v>947852.259148087</v>
-      </c>
-      <c r="H34" s="19" t="n">
-        <f aca="false">Obliczenia!N71</f>
-        <v>946466.865335537</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3077,152 +3075,167 @@
         <v>113</v>
       </c>
       <c r="C35" s="19" t="n">
-        <f aca="false">Obliczenia!I73</f>
-        <v>16094.6654984497</v>
+        <f aca="false">Obliczenia!I71</f>
+        <v>965679.929906982</v>
       </c>
       <c r="D35" s="19" t="n">
-        <f aca="false">Obliczenia!J73</f>
-        <v>15892.7844820585</v>
+        <f aca="false">Obliczenia!J71</f>
+        <v>953567.068923511</v>
       </c>
       <c r="E35" s="19" t="n">
-        <f aca="false">Obliczenia!K73</f>
-        <v>15866.3470112584</v>
+        <f aca="false">Obliczenia!K71</f>
+        <v>951980.820675503</v>
       </c>
       <c r="F35" s="19" t="n">
-        <f aca="false">Obliczenia!L73</f>
-        <v>15801.0099529053</v>
+        <f aca="false">Obliczenia!L71</f>
+        <v>948060.597174319</v>
       </c>
       <c r="G35" s="19" t="n">
-        <f aca="false">Obliczenia!M73</f>
-        <v>15797.5376524681</v>
+        <f aca="false">Obliczenia!M71</f>
+        <v>947852.259148087</v>
       </c>
       <c r="H35" s="19" t="n">
-        <f aca="false">Obliczenia!N73</f>
-        <v>15774.4477555923</v>
+        <f aca="false">Obliczenia!N71</f>
+        <v>946466.865335537</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36" s="23" t="n">
+        <v>114</v>
+      </c>
+      <c r="C36" s="19" t="n">
+        <f aca="false">Obliczenia!I74</f>
+        <v>16094.6654984497</v>
+      </c>
+      <c r="D36" s="19" t="n">
+        <f aca="false">Obliczenia!J74</f>
+        <v>15892.7844820585</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <f aca="false">Obliczenia!K74</f>
+        <v>15866.3470112584</v>
+      </c>
+      <c r="F36" s="19" t="n">
+        <f aca="false">Obliczenia!L74</f>
+        <v>15801.0099529053</v>
+      </c>
+      <c r="G36" s="19" t="n">
+        <f aca="false">Obliczenia!M74</f>
+        <v>15797.5376524681</v>
+      </c>
+      <c r="H36" s="19" t="n">
+        <f aca="false">Obliczenia!N74</f>
+        <v>15774.4477555923</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="23" t="n">
         <f aca="false">Obliczenia!I51</f>
         <v>82</v>
       </c>
-      <c r="D36" s="23" t="n">
+      <c r="D37" s="23" t="n">
         <f aca="false">Obliczenia!J51</f>
         <v>55</v>
       </c>
-      <c r="E36" s="23" t="n">
+      <c r="E37" s="23" t="n">
         <f aca="false">Obliczenia!K51</f>
         <v>43</v>
       </c>
-      <c r="F36" s="23" t="n">
+      <c r="F37" s="23" t="n">
         <f aca="false">Obliczenia!L51</f>
         <v>34</v>
       </c>
-      <c r="G36" s="23" t="n">
+      <c r="G37" s="23" t="n">
         <f aca="false">Obliczenia!M51</f>
         <v>29</v>
       </c>
-      <c r="H36" s="23" t="n">
+      <c r="H37" s="23" t="n">
         <f aca="false">Obliczenia!N51</f>
         <v>25</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="C37" s="23" t="n">
-        <f aca="false">Obliczenia!I48</f>
-        <v>17</v>
-      </c>
-      <c r="D37" s="23" t="n">
-        <f aca="false">Obliczenia!J48</f>
-        <v>11</v>
-      </c>
-      <c r="E37" s="23" t="n">
-        <f aca="false">Obliczenia!K48</f>
-        <v>9</v>
-      </c>
-      <c r="F37" s="23" t="n">
-        <f aca="false">Obliczenia!L48</f>
-        <v>7</v>
-      </c>
-      <c r="G37" s="23" t="n">
-        <f aca="false">Obliczenia!M48</f>
-        <v>6</v>
-      </c>
-      <c r="H37" s="23" t="n">
-        <f aca="false">Obliczenia!N48</f>
-        <v>5</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
         <v>115</v>
       </c>
-      <c r="C38" s="19" t="n">
+      <c r="C38" s="23" t="n">
+        <f aca="false">Obliczenia!I48</f>
+        <v>17</v>
+      </c>
+      <c r="D38" s="23" t="n">
+        <f aca="false">Obliczenia!J48</f>
+        <v>11</v>
+      </c>
+      <c r="E38" s="23" t="n">
+        <f aca="false">Obliczenia!K48</f>
+        <v>9</v>
+      </c>
+      <c r="F38" s="23" t="n">
+        <f aca="false">Obliczenia!L48</f>
+        <v>7</v>
+      </c>
+      <c r="G38" s="23" t="n">
+        <f aca="false">Obliczenia!M48</f>
+        <v>6</v>
+      </c>
+      <c r="H38" s="23" t="n">
+        <f aca="false">Obliczenia!N48</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" s="19" t="n">
         <f aca="false">Obliczenia!I57+Obliczenia!I64</f>
         <v>28939.318</v>
       </c>
-      <c r="D38" s="19" t="n">
+      <c r="D39" s="19" t="n">
         <f aca="false">Obliczenia!J57+Obliczenia!J64</f>
         <v>29223.159</v>
       </c>
-      <c r="E38" s="19" t="n">
+      <c r="E39" s="19" t="n">
         <f aca="false">Obliczenia!K57+Obliczenia!K64</f>
         <v>30461.636</v>
       </c>
-      <c r="F38" s="19" t="n">
+      <c r="F39" s="19" t="n">
         <f aca="false">Obliczenia!L57+Obliczenia!L64</f>
         <v>30355.477</v>
       </c>
-      <c r="G38" s="19" t="n">
+      <c r="G39" s="19" t="n">
         <f aca="false">Obliczenia!M57+Obliczenia!M64</f>
         <v>31116.636</v>
       </c>
-      <c r="H38" s="19" t="n">
+      <c r="H39" s="19" t="n">
         <f aca="false">Obliczenia!N57+Obliczenia!N64</f>
         <v>31400.477</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="4" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C42" s="16" t="str">
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="C43" s="16" t="str">
         <f aca="false">in_typ&amp;": "&amp;IF(in_S&gt;0,in_S&amp;" x S (2 MP)  ","")&amp;IF(in_D&gt;0,in_D&amp;" x D (4 MP)  ","")&amp;IF(in_NP&gt;0,in_NP&amp;" x N.P.  ","")&amp;"= "&amp;m_MP&amp;" MP"</f>
         <v>NK38: 15 x D (4 MP)  = 60 MP</v>
-      </c>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="16" t="str">
-        <f aca="false">in_agregaty&amp;" szt."</f>
-        <v>3 szt.</v>
       </c>
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
@@ -3232,11 +3245,11 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="0" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="C44" s="16" t="str">
-        <f aca="false">IF(t_zaglebienia="","standard 170 cm",t_zaglebienia)</f>
-        <v>200 cm: 15D</v>
+        <f aca="false">in_agregaty&amp;" szt."</f>
+        <v>3 szt.</v>
       </c>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
@@ -3249,8 +3262,8 @@
         <v>120</v>
       </c>
       <c r="C45" s="16" t="str">
-        <f aca="false">IF(t_wymiary="","standard",t_wymiary)</f>
-        <v>standard</v>
+        <f aca="false">IF(t_zaglebienia="","standard 170 cm",t_zaglebienia)</f>
+        <v>200 cm: 15D</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
@@ -3263,8 +3276,8 @@
         <v>121</v>
       </c>
       <c r="C46" s="16" t="str">
-        <f aca="false">in_magistrala&amp;" x 6 m  /  "&amp;in_barierki&amp;" szt.  /  "&amp;in_maskownice&amp;" szt."</f>
-        <v>4 x 6 m  /  30 szt.  /  5 szt.</v>
+        <f aca="false">IF(t_wymiary="","standard",t_wymiary)</f>
+        <v>standard</v>
       </c>
       <c r="D46" s="16"/>
       <c r="E46" s="16"/>
@@ -3277,8 +3290,8 @@
         <v>122</v>
       </c>
       <c r="C47" s="16" t="str">
-        <f aca="false">m_utr&amp;" (z magistrali i barierek "&amp;m_utr_auto&amp;", ręcznie "&amp;in_utr_dod&amp;")"</f>
-        <v>20 (z magistrali i barierek 20, ręcznie 0)</v>
+        <f aca="false">in_magistrala&amp;" x 6 m  /  "&amp;in_barierki&amp;" szt.  /  "&amp;in_maskownice&amp;" szt."</f>
+        <v>4 x 6 m  /  30 szt.  /  5 szt.</v>
       </c>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
@@ -3288,11 +3301,11 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="0" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="C48" s="16" t="str">
-        <f aca="false">in_lok&amp;IF(e_krk,"","  ("&amp;in_km&amp;" km od Krakowa)")</f>
-        <v>Poza Krakowem  (280 km od Krakowa)</v>
+        <f aca="false">m_utr&amp;" (z magistrali i barierek "&amp;m_utr_auto&amp;", ręcznie "&amp;in_utr_dod&amp;")"</f>
+        <v>20 (z magistrali i barierek 20, ręcznie 0)</v>
       </c>
       <c r="D48" s="16"/>
       <c r="E48" s="16"/>
@@ -3302,11 +3315,11 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="0" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="C49" s="16" t="str">
-        <f aca="false">e_km_pom&amp;" / "&amp;e_km_mon&amp;" km"</f>
-        <v>280 / 330 km</v>
+        <f aca="false">in_lok&amp;IF(e_krk,"","  ("&amp;in_km&amp;" km od Krakowa)")</f>
+        <v>Poza Krakowem  (280 km od Krakowa)</v>
       </c>
       <c r="D49" s="16"/>
       <c r="E49" s="16"/>
@@ -3319,8 +3332,8 @@
         <v>124</v>
       </c>
       <c r="C50" s="16" t="str">
-        <f aca="false">in_tir&amp;" TIR x "&amp;TEXT(in_tir_cena,"#,##0")&amp;" zł, rozładunek sprzętu "&amp;TEXT(in_rozl_cena,"#,##0")&amp;" zł jednorazowo, "&amp;e_rozl_dni&amp;" dni"</f>
-        <v>3 TIR x 4,000 zł, rozładunek sprzętu 5,100 zł jednorazowo, 1.5 dni</v>
+        <f aca="false">e_km_pom&amp;" / "&amp;e_km_mon&amp;" km"</f>
+        <v>280 / 330 km</v>
       </c>
       <c r="D50" s="16"/>
       <c r="E50" s="16"/>
@@ -3333,8 +3346,8 @@
         <v>125</v>
       </c>
       <c r="C51" s="16" t="str">
-        <f aca="false">in_osoby&amp;" osób, średnia stawka "&amp;TEXT(Obliczenia!D41,"#,##0")&amp;" zł/dzień"</f>
-        <v>4 osób, średnia stawka 400 zł/dzień</v>
+        <f aca="false">in_tir&amp;" TIR x "&amp;TEXT(in_tir_cena,"#,##0")&amp;" zł, rozładunek sprzętu "&amp;TEXT(in_rozl_cena,"#,##0")&amp;" zł jednorazowo, "&amp;e_rozl_dni&amp;" dni"</f>
+        <v>3 TIR x 4,000 zł, rozładunek sprzętu 5,100 zł jednorazowo, 1.5 dni</v>
       </c>
       <c r="D51" s="16"/>
       <c r="E51" s="16"/>
@@ -3347,8 +3360,8 @@
         <v>126</v>
       </c>
       <c r="C52" s="16" t="str">
-        <f aca="false">e_dzw_dni&amp;" dni"</f>
-        <v>3 dni</v>
+        <f aca="false">in_osoby&amp;" osób, średnia stawka "&amp;TEXT(Obliczenia!D41,"#,##0")&amp;" zł/dzień"</f>
+        <v>4 osób, średnia stawka 400 zł/dzień</v>
       </c>
       <c r="D52" s="16"/>
       <c r="E52" s="16"/>
@@ -3361,8 +3374,8 @@
         <v>127</v>
       </c>
       <c r="C53" s="16" t="str">
-        <f aca="false">Obliczenia!D51&amp;" dni pracy = "&amp;Obliczenia!D48&amp;IF(e_krk," dni"," tyg.")&amp;", "&amp;TEXT(Obliczenia!D50,"0.0")&amp;" osobodni"</f>
-        <v>43 dni pracy = 9 tyg., 168.5 osobodni</v>
+        <f aca="false">e_dzw_dni&amp;" dni"</f>
+        <v>3 dni</v>
       </c>
       <c r="D53" s="16"/>
       <c r="E53" s="16"/>
@@ -3375,8 +3388,8 @@
         <v>128</v>
       </c>
       <c r="C54" s="16" t="str">
-        <f aca="false">Obliczenia!F51&amp;" dni pracy = "&amp;Obliczenia!F48&amp;IF(e_krk," dni"," tyg.")&amp;", "&amp;TEXT(Obliczenia!F50,"0.0")&amp;" osobodni"</f>
-        <v>49 dni pracy = 10 tyg., 194.6 osobodni</v>
+        <f aca="false">Obliczenia!D51&amp;" dni pracy = "&amp;Obliczenia!D48&amp;IF(e_krk," dni"," tyg.")&amp;", "&amp;TEXT(Obliczenia!D50,"0.0")&amp;" osobodni"</f>
+        <v>43 dni pracy = 9 tyg., 168.5 osobodni</v>
       </c>
       <c r="D54" s="16"/>
       <c r="E54" s="16"/>
@@ -3389,8 +3402,8 @@
         <v>129</v>
       </c>
       <c r="C55" s="16" t="str">
-        <f aca="false">TEXT(in_zysk,"0.0%")&amp;" / "&amp;TEXT(in_zysk2,"0.0%")</f>
-        <v>12.5% / 10.0%</v>
+        <f aca="false">Obliczenia!F51&amp;" dni pracy = "&amp;Obliczenia!F48&amp;IF(e_krk," dni"," tyg.")&amp;", "&amp;TEXT(Obliczenia!F50,"0.0")&amp;" osobodni"</f>
+        <v>49 dni pracy = 10 tyg., 194.6 osobodni</v>
       </c>
       <c r="D55" s="16"/>
       <c r="E55" s="16"/>
@@ -3403,8 +3416,8 @@
         <v>130</v>
       </c>
       <c r="C56" s="16" t="str">
-        <f aca="false">TEXT(in_q2500,"0.0%")</f>
-        <v>6.0%</v>
+        <f aca="false">TEXT(in_zysk,"0.0%")&amp;" / "&amp;TEXT(in_zysk2,"0.0%")</f>
+        <v>12.5% / 10.0%</v>
       </c>
       <c r="D56" s="16"/>
       <c r="E56" s="16"/>
@@ -3414,11 +3427,11 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="0" t="s">
-        <v>65</v>
+        <v>131</v>
       </c>
       <c r="C57" s="16" t="str">
-        <f aca="false">in_wzor</f>
-        <v>Stary (poprawiony)</v>
+        <f aca="false">TEXT(in_q2500,"0.0%")</f>
+        <v>6.0%</v>
       </c>
       <c r="D57" s="16"/>
       <c r="E57" s="16"/>
@@ -3428,11 +3441,11 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="0" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="C58" s="16" t="str">
-        <f aca="false">TEXT(in_konsA*m_MP*12,"#,##0")&amp;" / "&amp;TEXT(in_konsB*m_MP*12,"#,##0")&amp;" zł  (przegląd półroczny "&amp;TEXT(in_konsA*m_MP*6,"#,##0")&amp;" / "&amp;TEXT(in_konsB*m_MP*6,"#,##0")&amp;" zł)"</f>
-        <v>28,800 / 36,000 zł  (przegląd półroczny 14,400 / 18,000 zł)</v>
+        <f aca="false">in_wzor</f>
+        <v>Stary (poprawiony)</v>
       </c>
       <c r="D58" s="16"/>
       <c r="E58" s="16"/>
@@ -3445,8 +3458,8 @@
         <v>132</v>
       </c>
       <c r="C59" s="16" t="str">
-        <f aca="false">in_opis&amp;""</f>
-        <v>H-195/202 | L-530-544-584 | P-380 | Hpoj. G-180. D-180 | 1A4+1A5+1A6 | Bok-30 Tył-5 | mgstrl-4</v>
+        <f aca="false">TEXT(in_konsA*m_MP*12,"#,##0")&amp;" / "&amp;TEXT(in_konsB*m_MP*12,"#,##0")&amp;" zł  (przegląd półroczny "&amp;TEXT(in_konsA*m_MP*6,"#,##0")&amp;" / "&amp;TEXT(in_konsB*m_MP*6,"#,##0")&amp;" zł)"</f>
+        <v>28,800 / 36,000 zł  (przegląd półroczny 14,400 / 18,000 zł)</v>
       </c>
       <c r="D59" s="16"/>
       <c r="E59" s="16"/>
@@ -3454,36 +3467,39 @@
       <c r="G59" s="16"/>
       <c r="H59" s="16"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="11" t="s">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="0" t="s">
         <v>133</v>
       </c>
-      <c r="C61" s="0" t="str">
+      <c r="C60" s="16" t="str">
+        <f aca="false">in_opis&amp;""</f>
+        <v>H-195/202 | L-530-544-584 | P-380 | Hpoj. G-180. D-180 | 1A4+1A5+1A6 | Bok-30 Tył-5 | mgstrl-4</v>
+      </c>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="16"/>
+      <c r="H60" s="16"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C62" s="0" t="str">
         <f aca="false">IF(COUNTIF(Dane!B66:B71,"ok")=6,"wszystko ok","sprawdź arkusz Dane")</f>
         <v>wszystko ok</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-    </row>
-    <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B64" s="24" t="s">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C64" s="24"/>
-      <c r="D64" s="24"/>
-      <c r="E64" s="24"/>
-      <c r="F64" s="24"/>
-      <c r="G64" s="24"/>
-      <c r="H64" s="24"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
     </row>
     <row r="65" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="24" t="s">
@@ -3540,9 +3556,19 @@
       <c r="G69" s="24"/>
       <c r="H69" s="24"/>
     </row>
+    <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B70" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C70" s="24"/>
+      <c r="D70" s="24"/>
+      <c r="E70" s="24"/>
+      <c r="F70" s="24"/>
+      <c r="G70" s="24"/>
+      <c r="H70" s="24"/>
+    </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C42:H42"/>
     <mergeCell ref="C43:H43"/>
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="C45:H45"/>
@@ -3560,21 +3586,22 @@
     <mergeCell ref="C57:H57"/>
     <mergeCell ref="C58:H58"/>
     <mergeCell ref="C59:H59"/>
-    <mergeCell ref="B64:H64"/>
+    <mergeCell ref="C60:H60"/>
     <mergeCell ref="B65:H65"/>
     <mergeCell ref="B66:H66"/>
     <mergeCell ref="B67:H67"/>
     <mergeCell ref="B68:H68"/>
     <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B70:H70"/>
   </mergeCells>
-  <conditionalFormatting sqref="C34:H34">
+  <conditionalFormatting sqref="C35:H35">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>C34=MIN($C$34:$H$34)</formula>
+      <formula>C35=MIN($C$35:$H$35)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C61">
+  <conditionalFormatting sqref="C62">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>C61&lt;&gt;"wszystko ok"</formula>
+      <formula>C62&lt;&gt;"wszystko ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3604,7 +3631,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -3613,12 +3640,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -3626,90 +3653,90 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>32500</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>700</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C8" s="14" t="n">
         <v>0.61</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>0.85</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>1170</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>1560</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>1820</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>3110</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3720,34 +3747,34 @@
         <v>2340</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C15" s="25" t="n">
         <v>0.00127</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C16" s="14" t="n">
         <v>0.07</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -3755,107 +3782,107 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>6500</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>1500</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>200</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>500</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>50</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>1080</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>1175</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>1250</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C26" s="26" t="n">
         <f aca="false">0.2*11+0.4*11+2*14+6*11+6*5+6*10</f>
         <v>190.6</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -3863,51 +3890,51 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>600</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>700</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>1000</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1800</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -3915,73 +3942,73 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>6400</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>13500</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>200</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C36" s="13" t="n">
         <v>1700</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>6300</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>0.37</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -3989,117 +4016,117 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>5.5</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C41" s="9" t="n">
         <v>7</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>7</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C44" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C45" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C46" s="13" t="n">
         <v>2400</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>5</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>5</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
@@ -4107,84 +4134,84 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>50</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>20</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>650</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>12</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C55" s="26" t="n">
         <v>9.4</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C57" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
@@ -4192,62 +4219,62 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C59" s="13" t="n">
         <v>500</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>400</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C61" s="13" t="n">
         <v>350</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C62" s="13" t="n">
         <v>45</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C63" s="13" t="n">
         <v>130</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
@@ -4255,40 +4282,40 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C65" s="14" t="n">
         <v>0.005</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C66" s="14" t="n">
         <v>0.025</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C67" s="14" t="n">
         <v>0.14</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
@@ -4296,13 +4323,13 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4406,7 +4433,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
@@ -4415,24 +4442,24 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C83" s="29" t="n">
         <v>45</v>
@@ -4444,12 +4471,12 @@
         <v>9.6</v>
       </c>
       <c r="F83" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C84" s="29" t="n">
         <v>8</v>
@@ -4461,12 +4488,12 @@
         <v>4</v>
       </c>
       <c r="F84" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C85" s="29" t="n">
         <v>36</v>
@@ -4478,12 +4505,12 @@
         <v>2</v>
       </c>
       <c r="F85" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C86" s="29" t="n">
         <v>90</v>
@@ -4495,12 +4522,12 @@
         <v>2</v>
       </c>
       <c r="F86" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C87" s="29" t="n">
         <v>207.28</v>
@@ -4512,12 +4539,12 @@
         <v>2</v>
       </c>
       <c r="F87" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C88" s="29" t="n">
         <v>40.14</v>
@@ -4529,12 +4556,12 @@
         <v>2</v>
       </c>
       <c r="F88" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C89" s="29" t="n">
         <v>3.3</v>
@@ -4546,12 +4573,12 @@
         <v>2</v>
       </c>
       <c r="F89" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C90" s="29" t="n">
         <v>10.8</v>
@@ -4563,12 +4590,12 @@
         <v>2</v>
       </c>
       <c r="F90" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C91" s="29" t="n">
         <v>10.95</v>
@@ -4580,12 +4607,12 @@
         <v>2</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C92" s="29" t="n">
         <v>3.81</v>
@@ -4597,12 +4624,12 @@
         <v>2</v>
       </c>
       <c r="F92" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C93" s="29" t="n">
         <v>2.84</v>
@@ -4614,12 +4641,12 @@
         <v>4</v>
       </c>
       <c r="F93" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C94" s="29" t="n">
         <v>4.4</v>
@@ -4631,12 +4658,12 @@
         <v>4</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C95" s="29" t="n">
         <f aca="false">2*25.71+2*22.85</f>
@@ -4649,12 +4676,12 @@
         <v>1</v>
       </c>
       <c r="F95" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C96" s="29" t="n">
         <v>345</v>
@@ -4666,12 +4693,12 @@
         <v>0</v>
       </c>
       <c r="F96" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C97" s="29" t="n">
         <v>546</v>
@@ -4683,12 +4710,12 @@
         <v>1</v>
       </c>
       <c r="F97" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C98" s="29" t="n">
         <v>2.98</v>
@@ -4700,12 +4727,12 @@
         <v>208</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C99" s="29" t="n">
         <f aca="false">3.09+4.99</f>
@@ -4718,12 +4745,12 @@
         <v>20</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C100" s="29" t="n">
         <v>5.4</v>
@@ -4735,12 +4762,12 @@
         <v>1</v>
       </c>
       <c r="F100" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C101" s="29" t="n">
         <v>300</v>
@@ -4752,12 +4779,12 @@
         <v>1</v>
       </c>
       <c r="F101" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C102" s="29" t="n">
         <v>40</v>
@@ -4769,12 +4796,12 @@
         <v>1</v>
       </c>
       <c r="F102" s="30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C103" s="29" t="n">
         <v>172</v>
@@ -4786,12 +4813,12 @@
         <v>0</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C104" s="29" t="n">
         <v>207</v>
@@ -4803,12 +4830,12 @@
         <v>1</v>
       </c>
       <c r="F104" s="30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C105" s="29" t="n">
         <f aca="false">120+55+65</f>
@@ -4821,12 +4848,12 @@
         <v>1</v>
       </c>
       <c r="F105" s="30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C106" s="29" t="n">
         <f aca="false">50+40</f>
@@ -4839,12 +4866,12 @@
         <v>1</v>
       </c>
       <c r="F106" s="30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C107" s="29" t="n">
         <f aca="false">14+9+25+5+9+30</f>
@@ -4857,12 +4884,12 @@
         <v>0</v>
       </c>
       <c r="F107" s="30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C108" s="29" t="n">
         <f aca="false">14+18+25+7+18+30</f>
@@ -4875,12 +4902,12 @@
         <v>1</v>
       </c>
       <c r="F108" s="30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C109" s="29" t="n">
         <f aca="false">70+14+34+32+20</f>
@@ -4893,7 +4920,7 @@
         <v>1</v>
       </c>
       <c r="F109" s="30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -4912,7 +4939,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:N78"/>
+  <dimension ref="B2:N79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -4924,7 +4951,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -4941,13 +4968,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C5" s="31" t="n">
         <f aca="false">c_cena_D+IF(in_typ="NK37",c_doplata_NK37,0)</f>
@@ -4956,7 +4983,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C6" s="31" t="n">
         <f aca="false">c_wsp_S*m_cena_D</f>
@@ -4965,7 +4992,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C7" s="31" t="n">
         <f aca="false">c_wsp_NP*m_cena_D</f>
@@ -4974,7 +5001,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C8" s="32" t="n">
         <f aca="false">in_D+in_NP</f>
@@ -4983,7 +5010,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C9" s="32" t="n">
         <f aca="false">in_S+in_D+in_NP</f>
@@ -4992,7 +5019,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C10" s="32" t="n">
         <f aca="false">2*in_S+2*in_NP+4*in_D</f>
@@ -5001,7 +5028,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C11" s="31" t="n">
         <f aca="false">m_cena_S*in_S+c_szer_260*in_szer1_S+c_szer_270*in_szer2_S+SUMPRODUCT(in_gl_S,t_gl_doplata)+c_dl_500*in_dl500_S+CEILING(m_cena_S*c_dl_wsp*10,100)*in_dl540_S+CEILING(m_cena_S*c_dl_wsp*20,100)*in_dl550_S</f>
@@ -5010,7 +5037,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C12" s="31" t="n">
         <f aca="false">m_cena_D*in_D+c_szer_520*in_szer1_D+c_szer_540*in_szer2_D+SUMPRODUCT(in_gl_D,t_gl_doplata)+c_dl_500*in_dl500_D+m_cena_D*c_dl_wsp*10*in_dl540_D+m_cena_D*c_dl_wsp*20*in_dl550_D</f>
@@ -5019,7 +5046,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C13" s="31" t="n">
         <f aca="false">m_cena_NP*in_NP</f>
@@ -5028,7 +5055,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C14" s="32" t="n">
         <f aca="false">SUMPRODUCT((t_gl_silownik=2000)*(in_gl_S+in_gl_D))</f>
@@ -5037,7 +5064,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C15" s="32" t="n">
         <f aca="false">SUMPRODUCT((t_gl_silownik=2250)*(in_gl_S+in_gl_D))</f>
@@ -5046,7 +5073,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C16" s="32" t="n">
         <f aca="false">m_platformy-m_sil_2000-m_sil_2250</f>
@@ -5055,7 +5082,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C17" s="31" t="n">
         <f aca="false">in_agregaty*(c_agregat+c_hydr_drobne+c_olej+c_transp_agregatu)+m_platformy*c_transp_silownikow+2*(c_sil_1700*m_sil_std+c_sil_2000*m_sil_2000+c_sil_2250*m_sil_2250)+in_magistrala*c_magistrala+SUMPRODUCT((t_sk_grupa="Hydraulika")*t_sk_cena*(t_sk_S*in_S+t_sk_D*m_DN))</f>
@@ -5064,7 +5091,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C18" s="31" t="n">
         <f aca="false">in_barierki*c_barierka+in_maskownice*c_maskownica</f>
@@ -5073,7 +5100,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C19" s="31" t="n">
         <f aca="false">in_agregaty*c_skrzynka_zasil+SUMPRODUCT((t_sk_grupa="Elektryka")*t_sk_cena*(t_sk_S*in_S+t_sk_D*m_DN))</f>
@@ -5082,7 +5109,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C20" s="31" t="n">
         <f aca="false">in_agregaty*c_admin+SUMPRODUCT((t_sk_grupa="Mechanika")*t_sk_cena*(t_sk_S*in_S+t_sk_D*m_DN))</f>
@@ -5091,7 +5118,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C21" s="33" t="n">
         <f aca="false">m_plat_S+m_plat_D+m_plat_NP+m_hydraulika+m_barierki+m_elektryka+m_mechanika</f>
@@ -5100,7 +5127,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C22" s="33" t="n">
         <f aca="false">m_suma_2000*(1+in_q2500)</f>
@@ -5109,7 +5136,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C23" s="31" t="n">
         <f aca="false">c_mal_S*in_S+c_mal_D*m_DN+c_mal_bar*in_barierki</f>
@@ -5118,7 +5145,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C24" s="34" t="n">
         <f aca="false">ROUNDUP(in_magistrala*c_osd_magistrala+(in_barierki+in_maskownice)*c_osd_barierka,0)</f>
@@ -5127,7 +5154,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C25" s="34" t="n">
         <f aca="false">m_utr_auto+in_utr_dod</f>
@@ -5136,13 +5163,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C28" s="35" t="b">
         <f aca="false">in_lok="Kraków"</f>
@@ -5151,7 +5178,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C29" s="34" t="n">
         <f aca="false">IF(ISBLANK(in_km_pom),IF(e_krk,c_km_krakow,in_km),in_km_pom)</f>
@@ -5160,7 +5187,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C30" s="34" t="n">
         <f aca="false">IF(ISBLANK(in_km_mon),IF(e_krk,c_km_krakow,in_km+c_km_dodatek),in_km_mon)</f>
@@ -5169,7 +5196,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C31" s="34" t="n">
         <f aca="false">IF(ISBLANK(in_rozl_dni),c_rozl_TIR*in_tir,in_rozl_dni)</f>
@@ -5178,7 +5205,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C32" s="34" t="n">
         <f aca="false">(c_pomiary_osoby+c_odbiory_osoby)*IF(in_wzor="Uproszczony",2*e_km_pom/c_km_dzien*1,(1+0.1*MAX(0,800-e_km_pom)/100)*e_km_pom*1/500)</f>
@@ -5187,7 +5214,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">ROUNDUP(m_DN/c_dzwig_D+in_S*c_dzwig_wspS/c_dzwig_D,0)</f>
@@ -5196,7 +5223,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C34" s="36" t="n">
         <f aca="false">(1+c_podatek*(c_gdw+in_zysk))/(1-(c_kob+c_gdw+in_zysk))</f>
@@ -5205,7 +5232,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -5214,7 +5241,7 @@
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
@@ -5224,7 +5251,7 @@
     </row>
     <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D37" s="37" t="s">
         <v>77</v>
@@ -5239,27 +5266,27 @@
         <v>83</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J37" s="37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K37" s="37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L37" s="37" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M37" s="37" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N37" s="37" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D38" s="32" t="n">
         <v>0</v>
@@ -5300,7 +5327,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D39" s="32" t="n">
         <v>0</v>
@@ -5341,7 +5368,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D40" s="32" t="n">
         <f aca="false">in_osoby</f>
@@ -5380,7 +5407,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D41" s="31" t="n">
         <f aca="false">(c_stawka_1+IF(D40&gt;=2,c_stawka_2,0)+MAX(0,D40-2)*c_stawka_n)/D40</f>
@@ -5425,7 +5452,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D42" s="34" t="n">
         <f aca="false">c_osd_S*in_S+c_osd_D*in_D+c_osd_NP*in_NP+m_utr+D39*c_slupek_rbd*m_MP</f>
@@ -5470,7 +5497,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D43" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*1,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*1/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*1,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*1/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5515,7 +5542,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D44" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D43,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D43/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D43,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D43/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5560,7 +5587,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D45" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D44,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D44/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D44,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D44/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5605,7 +5632,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D46" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D45,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D45/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D45,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D45/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5650,7 +5677,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D47" s="32" t="n">
         <f aca="false">IF(e_krk,CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D46,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D46/500))))/D40,1),CEILING(CEILING((D42+(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D46,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D46/500))))/D40,1)/c_dni_tydzien,1))</f>
@@ -5695,7 +5722,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D48" s="38" t="n">
         <f aca="false">IF(ISBLANK(in_wyjazdy),D47,in_wyjazdy)</f>
@@ -5740,7 +5767,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D49" s="34" t="n">
         <f aca="false">(e_podr_pom+D40*(e_rozl_dni+IF(in_wzor="Uproszczony",2*e_km_mon/c_km_dzien*D48,(1+0.1*MAX(0,800-e_km_mon)/100)*e_km_mon*D48/500)))</f>
@@ -5785,7 +5812,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D50" s="34" t="n">
         <f aca="false">D42+D49</f>
@@ -5830,7 +5857,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D51" s="38" t="n">
         <f aca="false">CEILING(D50/D40,1)</f>
@@ -5875,7 +5902,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D52" s="38" t="n">
         <f aca="false">IF(e_krk,CEILING(D51/c_dni_tydzien,1),D48)</f>
@@ -5920,7 +5947,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D53" s="34" t="n">
         <f aca="false">2*(e_km_mon*D48+2*e_km_pom)</f>
@@ -5965,7 +5992,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D54" s="31" t="n">
         <f aca="false">IF(D38=1,m_suma_2500,m_suma_2000)</f>
@@ -6010,7 +6037,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D55" s="31" t="n">
         <f aca="false">D39*c_slupek*m_MP</f>
@@ -6055,7 +6082,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D56" s="31" t="n">
         <f aca="false">D53/100*ROUNDUP(c_spalanie*c_paliwo,0)</f>
@@ -6100,7 +6127,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D57" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_hotel*(D51+1)*D40)</f>
@@ -6145,7 +6172,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D58" s="31" t="n">
         <f aca="false">in_tir_cena*in_tir</f>
@@ -6190,7 +6217,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D59" s="31" t="n">
         <f aca="false">IF(ISBLANK(in_dzwig_koszt),c_dzwig*e_dzw_dni,in_dzwig_koszt)</f>
@@ -6235,7 +6262,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D60" s="31" t="n">
         <f aca="false">in_rozl_cena</f>
@@ -6280,7 +6307,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D61" s="31" t="n">
         <f aca="false">D41*e_rozl_dni*D40</f>
@@ -6325,7 +6352,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D62" s="31" t="n">
         <f aca="false">D41*(D49-D40*e_rozl_dni)</f>
@@ -6370,7 +6397,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D63" s="31" t="n">
         <f aca="false">IF(D48&gt;0,D41*D42,0)</f>
@@ -6415,7 +6442,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D64" s="31" t="n">
         <f aca="false">IF(e_krk,0,c_dieta*D50)</f>
@@ -6460,7 +6487,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D65" s="33" t="n">
         <f aca="false">SUM(D54:D64)</f>
@@ -6505,7 +6532,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D66" s="31" t="n">
         <f aca="false">D65/(1-(c_kob+c_gdw+in_zysk))</f>
@@ -6550,7 +6577,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D67" s="31" t="n">
         <f aca="false">D66*c_kob</f>
@@ -6595,7 +6622,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D68" s="31" t="n">
         <f aca="false">D66*c_gdw</f>
@@ -6640,7 +6667,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D69" s="31" t="n">
         <f aca="false">D66*in_zysk</f>
@@ -6685,7 +6712,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D70" s="31" t="n">
         <f aca="false">c_podatek*(D61+D62+D63+D64+D68+D69)</f>
@@ -6730,7 +6757,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D71" s="33" t="n">
         <f aca="false">D66+D70</f>
@@ -6775,316 +6802,361 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D72" s="31" t="n">
-        <f aca="false">D71-D69</f>
-        <v>836715.827184379</v>
+        <f aca="false">D71-D69-D68</f>
+        <v>813662.828486154</v>
       </c>
       <c r="E72" s="31" t="n">
-        <f aca="false">E71-E69</f>
-        <v>878009.843866036</v>
+        <f aca="false">E71-E69-E68</f>
+        <v>853804.668363077</v>
       </c>
       <c r="F72" s="31" t="n">
-        <f aca="false">F71-F69</f>
-        <v>962902.428333255</v>
+        <f aca="false">F71-F69-F68</f>
+        <v>936373.933895385</v>
       </c>
       <c r="G72" s="31" t="n">
-        <f aca="false">G71-G69</f>
-        <v>1004196.44501491</v>
+        <f aca="false">G71-G69-G68</f>
+        <v>976515.773772308</v>
       </c>
       <c r="I72" s="31" t="n">
-        <f aca="false">I71-I69</f>
-        <v>848840.240853728</v>
+        <f aca="false">I71-I69-I68</f>
+        <v>825472.303043077</v>
       </c>
       <c r="J72" s="31" t="n">
-        <f aca="false">J71-J69</f>
-        <v>838121.101122722</v>
+        <f aca="false">J71-J69-J68</f>
+        <v>815031.907562564</v>
       </c>
       <c r="K72" s="31" t="n">
-        <f aca="false">K71-K69</f>
-        <v>836715.827184379</v>
+        <f aca="false">K71-K69-K68</f>
+        <v>813662.828486154</v>
       </c>
       <c r="L72" s="31" t="n">
-        <f aca="false">L71-L69</f>
-        <v>833250.625132899</v>
+        <f aca="false">L71-L69-L68</f>
+        <v>810288.630724615</v>
       </c>
       <c r="M72" s="31" t="n">
-        <f aca="false">M71-M69</f>
-        <v>833066.616741775</v>
+        <f aca="false">M71-M69-M68</f>
+        <v>810109.488260513</v>
       </c>
       <c r="N72" s="31" t="n">
-        <f aca="false">N71-N69</f>
-        <v>831840.685517278</v>
+        <f aca="false">N71-N69-N68</f>
+        <v>808915.449553626</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="D73" s="31" t="n">
+      <c r="B73" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="D73" s="33" t="n">
+        <f aca="false">D71-D72</f>
+        <v>138317.992189349</v>
+      </c>
+      <c r="E73" s="33" t="n">
+        <f aca="false">E71-E72</f>
+        <v>145231.053017752</v>
+      </c>
+      <c r="F73" s="33" t="n">
+        <f aca="false">F71-F72</f>
+        <v>159170.966627219</v>
+      </c>
+      <c r="G73" s="33" t="n">
+        <f aca="false">G71-G72</f>
+        <v>166084.027455621</v>
+      </c>
+      <c r="I73" s="33" t="n">
+        <f aca="false">I71-I72</f>
+        <v>140207.626863905</v>
+      </c>
+      <c r="J73" s="33" t="n">
+        <f aca="false">J71-J72</f>
+        <v>138535.161360947</v>
+      </c>
+      <c r="K73" s="33" t="n">
+        <f aca="false">K71-K72</f>
+        <v>138317.992189349</v>
+      </c>
+      <c r="L73" s="33" t="n">
+        <f aca="false">L71-L72</f>
+        <v>137771.966449704</v>
+      </c>
+      <c r="M73" s="33" t="n">
+        <f aca="false">M71-M72</f>
+        <v>137742.770887574</v>
+      </c>
+      <c r="N73" s="33" t="n">
+        <f aca="false">N71-N72</f>
+        <v>137551.41578191</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="D74" s="31" t="n">
         <f aca="false">IF(m_MP&gt;0,D71/m_MP,0)</f>
         <v>15866.3470112584</v>
       </c>
-      <c r="E73" s="31" t="n">
+      <c r="E74" s="31" t="n">
         <f aca="false">IF(m_MP&gt;0,E71/m_MP,0)</f>
         <v>16650.5953563471</v>
       </c>
-      <c r="F73" s="31" t="n">
+      <c r="F74" s="31" t="n">
         <f aca="false">IF(m_MP&gt;0,F71/m_MP,0)</f>
         <v>18259.0816753767</v>
       </c>
-      <c r="G73" s="31" t="n">
+      <c r="G74" s="31" t="n">
         <f aca="false">IF(m_MP&gt;0,G71/m_MP,0)</f>
         <v>19043.3300204655</v>
       </c>
-      <c r="I73" s="31" t="n">
+      <c r="I74" s="31" t="n">
         <f aca="false">IF(m_MP&gt;0,I71/m_MP,0)</f>
         <v>16094.6654984497</v>
       </c>
-      <c r="J73" s="31" t="n">
+      <c r="J74" s="31" t="n">
         <f aca="false">IF(m_MP&gt;0,J71/m_MP,0)</f>
         <v>15892.7844820585</v>
       </c>
-      <c r="K73" s="31" t="n">
+      <c r="K74" s="31" t="n">
         <f aca="false">IF(m_MP&gt;0,K71/m_MP,0)</f>
         <v>15866.3470112584</v>
       </c>
-      <c r="L73" s="31" t="n">
+      <c r="L74" s="31" t="n">
         <f aca="false">IF(m_MP&gt;0,L71/m_MP,0)</f>
         <v>15801.0099529053</v>
       </c>
-      <c r="M73" s="31" t="n">
+      <c r="M74" s="31" t="n">
         <f aca="false">IF(m_MP&gt;0,M71/m_MP,0)</f>
         <v>15797.5376524681</v>
       </c>
-      <c r="N73" s="31" t="n">
+      <c r="N74" s="31" t="n">
         <f aca="false">IF(m_MP&gt;0,N71/m_MP,0)</f>
         <v>15774.4477555923</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="0" t="s">
-        <v>357</v>
-      </c>
-      <c r="D74" s="39" t="n">
-        <f aca="false">D73/in_eur</f>
-        <v>3668.51954017535</v>
-      </c>
-      <c r="E74" s="39" t="n">
-        <f aca="false">E73/in_eur</f>
-        <v>3849.8486373057</v>
-      </c>
-      <c r="F74" s="39" t="n">
-        <f aca="false">F73/in_eur</f>
-        <v>4221.75298852641</v>
-      </c>
-      <c r="G74" s="39" t="n">
-        <f aca="false">G73/in_eur</f>
-        <v>4403.08208565676</v>
-      </c>
-      <c r="I74" s="39" t="n">
-        <f aca="false">I73/in_eur</f>
-        <v>3721.30994183808</v>
-      </c>
-      <c r="J74" s="39" t="n">
-        <f aca="false">J73/in_eur</f>
-        <v>3674.63225018694</v>
-      </c>
-      <c r="K74" s="39" t="n">
-        <f aca="false">K73/in_eur</f>
-        <v>3668.51954017535</v>
-      </c>
-      <c r="L74" s="39" t="n">
-        <f aca="false">L73/in_eur</f>
-        <v>3653.41270587406</v>
-      </c>
-      <c r="M74" s="39" t="n">
-        <f aca="false">M73/in_eur</f>
-        <v>3652.60986184234</v>
-      </c>
-      <c r="N74" s="39" t="n">
-        <f aca="false">N73/in_eur</f>
-        <v>3647.27115736238</v>
-      </c>
-    </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="0" t="s">
-        <v>358</v>
-      </c>
-      <c r="D75" s="31" t="n">
+        <v>359</v>
+      </c>
+      <c r="D75" s="39" t="n">
+        <f aca="false">D74/in_eur</f>
+        <v>3668.51954017535</v>
+      </c>
+      <c r="E75" s="39" t="n">
+        <f aca="false">E74/in_eur</f>
+        <v>3849.8486373057</v>
+      </c>
+      <c r="F75" s="39" t="n">
+        <f aca="false">F74/in_eur</f>
+        <v>4221.75298852641</v>
+      </c>
+      <c r="G75" s="39" t="n">
+        <f aca="false">G74/in_eur</f>
+        <v>4403.08208565676</v>
+      </c>
+      <c r="I75" s="39" t="n">
+        <f aca="false">I74/in_eur</f>
+        <v>3721.30994183808</v>
+      </c>
+      <c r="J75" s="39" t="n">
+        <f aca="false">J74/in_eur</f>
+        <v>3674.63225018694</v>
+      </c>
+      <c r="K75" s="39" t="n">
+        <f aca="false">K74/in_eur</f>
+        <v>3668.51954017535</v>
+      </c>
+      <c r="L75" s="39" t="n">
+        <f aca="false">L74/in_eur</f>
+        <v>3653.41270587406</v>
+      </c>
+      <c r="M75" s="39" t="n">
+        <f aca="false">M74/in_eur</f>
+        <v>3652.60986184234</v>
+      </c>
+      <c r="N75" s="39" t="n">
+        <f aca="false">N74/in_eur</f>
+        <v>3647.27115736238</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="0" t="s">
+        <v>360</v>
+      </c>
+      <c r="D76" s="31" t="n">
         <f aca="false">D65/(1-(c_kob+c_gdw+in_zysk2))</f>
         <v>895622.248275862</v>
       </c>
-      <c r="E75" s="31" t="n">
+      <c r="E76" s="31" t="n">
         <f aca="false">E65/(1-(c_kob+c_gdw+in_zysk2))</f>
         <v>940384.979310345</v>
       </c>
-      <c r="F75" s="31" t="n">
+      <c r="F76" s="31" t="n">
         <f aca="false">F65/(1-(c_kob+c_gdw+in_zysk2))</f>
         <v>1030647.25517241</v>
       </c>
-      <c r="G75" s="31" t="n">
+      <c r="G76" s="31" t="n">
         <f aca="false">G65/(1-(c_kob+c_gdw+in_zysk2))</f>
         <v>1075409.9862069</v>
       </c>
-      <c r="I75" s="31" t="n">
+      <c r="I76" s="31" t="n">
         <f aca="false">I65/(1-(c_kob+c_gdw+in_zysk2))</f>
         <v>907857.813793103</v>
       </c>
-      <c r="J75" s="31" t="n">
+      <c r="J76" s="31" t="n">
         <f aca="false">J65/(1-(c_kob+c_gdw+in_zysk2))</f>
         <v>897028.439463601</v>
       </c>
-      <c r="K75" s="31" t="n">
+      <c r="K76" s="31" t="n">
         <f aca="false">K65/(1-(c_kob+c_gdw+in_zysk2))</f>
         <v>895622.248275862</v>
       </c>
-      <c r="L75" s="31" t="n">
+      <c r="L76" s="31" t="n">
         <f aca="false">L65/(1-(c_kob+c_gdw+in_zysk2))</f>
         <v>892086.679310345</v>
       </c>
-      <c r="M75" s="31" t="n">
+      <c r="M76" s="31" t="n">
         <f aca="false">M65/(1-(c_kob+c_gdw+in_zysk2))</f>
         <v>891897.635249042</v>
       </c>
-      <c r="N75" s="31" t="n">
+      <c r="N76" s="31" t="n">
         <f aca="false">N65/(1-(c_kob+c_gdw+in_zysk2))</f>
         <v>890658.592610837</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="0" t="s">
-        <v>359</v>
-      </c>
-      <c r="D76" s="31" t="n">
-        <f aca="false">D75*in_zysk2</f>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <f aca="false">D76*in_zysk2</f>
         <v>89562.2248275862</v>
       </c>
-      <c r="E76" s="31" t="n">
-        <f aca="false">E75*in_zysk2</f>
+      <c r="E77" s="31" t="n">
+        <f aca="false">E76*in_zysk2</f>
         <v>94038.4979310345</v>
       </c>
-      <c r="F76" s="31" t="n">
-        <f aca="false">F75*in_zysk2</f>
+      <c r="F77" s="31" t="n">
+        <f aca="false">F76*in_zysk2</f>
         <v>103064.725517241</v>
       </c>
-      <c r="G76" s="31" t="n">
-        <f aca="false">G75*in_zysk2</f>
+      <c r="G77" s="31" t="n">
+        <f aca="false">G76*in_zysk2</f>
         <v>107540.99862069</v>
       </c>
-      <c r="I76" s="31" t="n">
-        <f aca="false">I75*in_zysk2</f>
+      <c r="I77" s="31" t="n">
+        <f aca="false">I76*in_zysk2</f>
         <v>90785.7813793104</v>
       </c>
-      <c r="J76" s="31" t="n">
-        <f aca="false">J75*in_zysk2</f>
+      <c r="J77" s="31" t="n">
+        <f aca="false">J76*in_zysk2</f>
         <v>89702.8439463602</v>
       </c>
-      <c r="K76" s="31" t="n">
-        <f aca="false">K75*in_zysk2</f>
+      <c r="K77" s="31" t="n">
+        <f aca="false">K76*in_zysk2</f>
         <v>89562.2248275862</v>
       </c>
-      <c r="L76" s="31" t="n">
-        <f aca="false">L75*in_zysk2</f>
+      <c r="L77" s="31" t="n">
+        <f aca="false">L76*in_zysk2</f>
         <v>89208.6679310345</v>
       </c>
-      <c r="M76" s="31" t="n">
-        <f aca="false">M75*in_zysk2</f>
+      <c r="M77" s="31" t="n">
+        <f aca="false">M76*in_zysk2</f>
         <v>89189.7635249042</v>
       </c>
-      <c r="N76" s="31" t="n">
-        <f aca="false">N75*in_zysk2</f>
+      <c r="N77" s="31" t="n">
+        <f aca="false">N76*in_zysk2</f>
         <v>89065.8592610838</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="D77" s="33" t="n">
-        <f aca="false">D75+c_podatek*(D61+D62+D63+D64+D75*(c_gdw+in_zysk2))</f>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="D78" s="33" t="n">
+        <f aca="false">D76+c_podatek*(D61+D62+D63+D64+D76*(c_gdw+in_zysk2))</f>
         <v>921791.99146069</v>
       </c>
-      <c r="E77" s="33" t="n">
-        <f aca="false">E75+c_podatek*(E61+E62+E63+E64+E75*(c_gdw+in_zysk2))</f>
+      <c r="E78" s="33" t="n">
+        <f aca="false">E76+c_podatek*(E61+E62+E63+E64+E76*(c_gdw+in_zysk2))</f>
         <v>967338.070288276</v>
       </c>
-      <c r="F77" s="33" t="n">
-        <f aca="false">F75+c_podatek*(F61+F62+F63+F64+F75*(c_gdw+in_zysk2))</f>
+      <c r="F78" s="33" t="n">
+        <f aca="false">F76+c_podatek*(F61+F62+F63+F64+F76*(c_gdw+in_zysk2))</f>
         <v>1060804.76981793</v>
       </c>
-      <c r="G77" s="33" t="n">
-        <f aca="false">G75+c_podatek*(G61+G62+G63+G64+G75*(c_gdw+in_zysk2))</f>
+      <c r="G78" s="33" t="n">
+        <f aca="false">G76+c_podatek*(G61+G62+G63+G64+G76*(c_gdw+in_zysk2))</f>
         <v>1106350.84864552</v>
       </c>
-      <c r="I77" s="33" t="n">
-        <f aca="false">I75+c_podatek*(I61+I62+I63+I64+I75*(c_gdw+in_zysk2))</f>
+      <c r="I78" s="33" t="n">
+        <f aca="false">I76+c_podatek*(I61+I62+I63+I64+I76*(c_gdw+in_zysk2))</f>
         <v>935078.675254483</v>
       </c>
-      <c r="J77" s="33" t="n">
-        <f aca="false">J75+c_podatek*(J61+J62+J63+J64+J75*(c_gdw+in_zysk2))</f>
+      <c r="J78" s="33" t="n">
+        <f aca="false">J76+c_podatek*(J61+J62+J63+J64+J76*(c_gdw+in_zysk2))</f>
         <v>923330.841080881</v>
       </c>
-      <c r="K77" s="33" t="n">
-        <f aca="false">K75+c_podatek*(K61+K62+K63+K64+K75*(c_gdw+in_zysk2))</f>
+      <c r="K78" s="33" t="n">
+        <f aca="false">K76+c_podatek*(K61+K62+K63+K64+K76*(c_gdw+in_zysk2))</f>
         <v>921791.99146069</v>
       </c>
-      <c r="L77" s="33" t="n">
-        <f aca="false">L75+c_podatek*(L61+L62+L63+L64+L75*(c_gdw+in_zysk2))</f>
+      <c r="L78" s="33" t="n">
+        <f aca="false">L76+c_podatek*(L61+L62+L63+L64+L76*(c_gdw+in_zysk2))</f>
         <v>917990.941738276</v>
       </c>
-      <c r="M77" s="33" t="n">
-        <f aca="false">M75+c_podatek*(M61+M62+M63+M64+M75*(c_gdw+in_zysk2))</f>
+      <c r="M78" s="33" t="n">
+        <f aca="false">M76+c_podatek*(M61+M62+M63+M64+M76*(c_gdw+in_zysk2))</f>
         <v>917788.975839234</v>
       </c>
-      <c r="N77" s="33" t="n">
-        <f aca="false">N75+c_podatek*(N61+N62+N63+N64+N75*(c_gdw+in_zysk2))</f>
+      <c r="N78" s="33" t="n">
+        <f aca="false">N76+c_podatek*(N61+N62+N63+N64+N76*(c_gdw+in_zysk2))</f>
         <v>916445.346561527</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="0" t="s">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="D78" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,D77/m_MP,0)</f>
+      <c r="D79" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,D78/m_MP,0)</f>
         <v>15363.1998576782</v>
       </c>
-      <c r="E78" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,E77/m_MP,0)</f>
+      <c r="E79" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,E78/m_MP,0)</f>
         <v>16122.3011714713</v>
       </c>
-      <c r="F78" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,F77/m_MP,0)</f>
+      <c r="F79" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,F78/m_MP,0)</f>
         <v>17680.0794969655</v>
       </c>
-      <c r="G78" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,G77/m_MP,0)</f>
+      <c r="G79" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,G78/m_MP,0)</f>
         <v>18439.1808107586</v>
       </c>
-      <c r="I78" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,I77/m_MP,0)</f>
+      <c r="I79" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,I78/m_MP,0)</f>
         <v>15584.6445875747</v>
       </c>
-      <c r="J78" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,J77/m_MP,0)</f>
+      <c r="J79" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,J78/m_MP,0)</f>
         <v>15388.847351348</v>
       </c>
-      <c r="K78" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,K77/m_MP,0)</f>
+      <c r="K79" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,K78/m_MP,0)</f>
         <v>15363.1998576782</v>
       </c>
-      <c r="L78" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,L77/m_MP,0)</f>
+      <c r="L79" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,L78/m_MP,0)</f>
         <v>15299.8490289713</v>
       </c>
-      <c r="M78" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,M77/m_MP,0)</f>
+      <c r="M79" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,M78/m_MP,0)</f>
         <v>15296.4829306539</v>
       </c>
-      <c r="N78" s="31" t="n">
-        <f aca="false">IF(m_MP&gt;0,N77/m_MP,0)</f>
+      <c r="N79" s="31" t="n">
+        <f aca="false">IF(m_MP&gt;0,N78/m_MP,0)</f>
         <v>15274.0891093588</v>
       </c>
     </row>
